--- a/model/naca_log_r2_cpu.xlsx
+++ b/model/naca_log_r2_cpu.xlsx
@@ -460,13 +460,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>20.18891679999069</v>
+        <v>10.01056110000354</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4418164207935333</v>
+        <v>0.4418164155483246</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1670339512825012</v>
+        <v>0.1670339441299439</v>
       </c>
       <c r="E2" t="n">
         <v>0.001</v>
@@ -477,13 +477,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>20.2884655000089</v>
+        <v>9.707645299989963</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1272039220333099</v>
+        <v>0.1272039217948913</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1107126325368881</v>
+        <v>0.1107126265764236</v>
       </c>
       <c r="E3" t="n">
         <v>0.001</v>
@@ -494,7 +494,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>20.06869499999448</v>
+        <v>9.513975999987451</v>
       </c>
       <c r="C4" t="n">
         <v>0.1044926842451096</v>
@@ -511,13 +511,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>19.5102021000057</v>
+        <v>9.722024600021541</v>
       </c>
       <c r="C5" t="n">
         <v>0.1021969478130341</v>
       </c>
       <c r="D5" t="n">
-        <v>0.104162849187851</v>
+        <v>0.1041628506779671</v>
       </c>
       <c r="E5" t="n">
         <v>0.001</v>
@@ -528,13 +528,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>18.40957560000243</v>
+        <v>9.475729400001001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1015419265031815</v>
+        <v>0.1015419286489487</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1053929820656776</v>
+        <v>0.1053929868340492</v>
       </c>
       <c r="E6" t="n">
         <v>0.001</v>
@@ -545,10 +545,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>18.27881289999641</v>
+        <v>9.490697400004137</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1018983254432678</v>
+        <v>0.1018983243703842</v>
       </c>
       <c r="D7" t="n">
         <v>0.105897071659565</v>
@@ -562,13 +562,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>18.02455019998888</v>
+        <v>9.292352000018582</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1016631553769112</v>
+        <v>0.1016631549596786</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1045833960175514</v>
+        <v>0.1045833957195282</v>
       </c>
       <c r="E8" t="n">
         <v>0.001</v>
@@ -579,13 +579,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>18.0896431000001</v>
+        <v>9.421953199984273</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1014786610007286</v>
+        <v>0.1014786605834961</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1046404030919075</v>
+        <v>0.1046404039859772</v>
       </c>
       <c r="E9" t="n">
         <v>0.001</v>
@@ -596,13 +596,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>18.31659979998949</v>
+        <v>9.309766199992737</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1012872193455696</v>
+        <v>0.1012872188687325</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1073098254203796</v>
+        <v>0.1073098242282867</v>
       </c>
       <c r="E10" t="n">
         <v>0.001</v>
@@ -613,13 +613,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>18.19877790000464</v>
+        <v>9.209247799997684</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1016283854842186</v>
+        <v>0.1016283856630325</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1057898300886154</v>
+        <v>0.1057898277044296</v>
       </c>
       <c r="E11" t="n">
         <v>0.001</v>
@@ -630,13 +630,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>18.0861705999996</v>
+        <v>9.393780999991577</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1013164576888084</v>
+        <v>0.1013164567351341</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1045084315538406</v>
+        <v>0.1045084279775619</v>
       </c>
       <c r="E12" t="n">
         <v>0.001</v>
@@ -647,13 +647,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>17.95655840000836</v>
+        <v>9.316150700004073</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1013089990615845</v>
+        <v>0.1013089970946312</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1037200820446014</v>
+        <v>0.1037200725078583</v>
       </c>
       <c r="E13" t="n">
         <v>0.001</v>
@@ -664,13 +664,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>18.04174659999262</v>
+        <v>9.269380900019314</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1014439235925674</v>
+        <v>0.1014439226388931</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1049223810434341</v>
+        <v>0.104922382235527</v>
       </c>
       <c r="E14" t="n">
         <v>0.001</v>
@@ -681,13 +681,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>18.03529980000167</v>
+        <v>9.297047900006874</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1013516746759415</v>
+        <v>0.10135167491436</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1041269972920418</v>
+        <v>0.1041269969940186</v>
       </c>
       <c r="E15" t="n">
         <v>0.001</v>
@@ -698,13 +698,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>17.98253819999809</v>
+        <v>9.477128700003959</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1014174353480339</v>
+        <v>0.1014174367785454</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1033304595947266</v>
+        <v>0.1033304598927498</v>
       </c>
       <c r="E16" t="n">
         <v>0.001</v>
@@ -715,13 +715,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>17.96379399999569</v>
+        <v>9.383252500003437</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1013225288391113</v>
+        <v>0.1013225243091583</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1041988652944565</v>
+        <v>0.1041988602280617</v>
       </c>
       <c r="E17" t="n">
         <v>0.001</v>
@@ -732,13 +732,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>17.9806496000092</v>
+        <v>9.163790300022811</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1013299312591553</v>
+        <v>0.1013299326896668</v>
       </c>
       <c r="D18" t="n">
-        <v>0.103147791326046</v>
+        <v>0.1031477904319763</v>
       </c>
       <c r="E18" t="n">
         <v>0.001</v>
@@ -749,10 +749,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>17.74199599999702</v>
+        <v>9.380293900001561</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1013040853738785</v>
+        <v>0.1013040858507156</v>
       </c>
       <c r="D19" t="n">
         <v>0.1046904775500297</v>
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>18.11590089999663</v>
+        <v>9.296718499972485</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1012675289511681</v>
+        <v>0.1012675287127495</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1037056857347488</v>
+        <v>0.1037056928873062</v>
       </c>
       <c r="E20" t="n">
         <v>0.001</v>
@@ -783,10 +783,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03596770000877</v>
+        <v>9.255595800001174</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1013236382007599</v>
+        <v>0.1013236389160156</v>
       </c>
       <c r="D21" t="n">
         <v>0.1039461728930473</v>
@@ -800,13 +800,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>18.02257239999017</v>
+        <v>9.203425800020341</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1009995576739311</v>
+        <v>0.1009995574355125</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1039314293861389</v>
+        <v>0.103931428194046</v>
       </c>
       <c r="E22" t="n">
         <v>0.001</v>
@@ -817,13 +817,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>18.02763419999974</v>
+        <v>9.319366999989143</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1013678169250488</v>
+        <v>0.1013678142428398</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1049353471398354</v>
+        <v>0.1049353420734405</v>
       </c>
       <c r="E23" t="n">
         <v>0.001</v>
@@ -834,13 +834,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>18.05172760000278</v>
+        <v>9.219214000011561</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1011847307682037</v>
+        <v>0.1011847305297852</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1052902776002884</v>
+        <v>0.1052902689576149</v>
       </c>
       <c r="E24" t="n">
         <v>0.001</v>
@@ -851,10 +851,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>18.34094979999645</v>
+        <v>9.321815000002971</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1012564816474915</v>
+        <v>0.1012564792633057</v>
       </c>
       <c r="D25" t="n">
         <v>0.1036519807577133</v>
@@ -868,13 +868,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>17.94287519999489</v>
+        <v>9.384016800002428</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1011128073334694</v>
+        <v>0.1011128078103065</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1066377347707748</v>
+        <v>0.1066377463936806</v>
       </c>
       <c r="E26" t="n">
         <v>0.001</v>
@@ -885,13 +885,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>18.28685559998848</v>
+        <v>9.416504599998007</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1014386848211288</v>
+        <v>0.101438685297966</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1058364316821098</v>
+        <v>0.1058364191651344</v>
       </c>
       <c r="E27" t="n">
         <v>0.001</v>
@@ -902,13 +902,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>18.16170959999727</v>
+        <v>9.303066299995407</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1013410108685494</v>
+        <v>0.1013410080075264</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1037810862064362</v>
+        <v>0.10378108471632</v>
       </c>
       <c r="E28" t="n">
         <v>0.001</v>
@@ -919,13 +919,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>18.13649359998817</v>
+        <v>9.309941400017124</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1010644196867943</v>
+        <v>0.1010644184947014</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1039299273490906</v>
+        <v>0.1039299321174622</v>
       </c>
       <c r="E29" t="n">
         <v>0.001</v>
@@ -936,10 +936,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>18.02707710000686</v>
+        <v>9.168383999989601</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1009261211752892</v>
+        <v>0.1009261249899864</v>
       </c>
       <c r="D30" t="n">
         <v>0.1055134359002113</v>
@@ -953,13 +953,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>17.98522930000036</v>
+        <v>9.130053200002294</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1010958542227745</v>
+        <v>0.1010958544611931</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1032626685500145</v>
+        <v>0.1032626682519913</v>
       </c>
       <c r="E31" t="n">
         <v>0.001</v>
@@ -970,13 +970,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>18.01495799999975</v>
+        <v>9.081384499993874</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1009730588197708</v>
+        <v>0.100973059296608</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1046406498551369</v>
+        <v>0.1046406483650208</v>
       </c>
       <c r="E32" t="n">
         <v>0.001</v>
@@ -987,13 +987,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>17.84996229999524</v>
+        <v>9.24057829999947</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1010736153125763</v>
+        <v>0.1010736154913902</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1035392701625824</v>
+        <v>0.1035392698645592</v>
       </c>
       <c r="E33" t="n">
         <v>0.001</v>
@@ -1004,13 +1004,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>18.14369440000155</v>
+        <v>9.166130399971735</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1012516459226608</v>
+        <v>0.1012516449689865</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1040234550833702</v>
+        <v>0.1040234541893005</v>
       </c>
       <c r="E34" t="n">
         <v>0.001</v>
@@ -1021,13 +1021,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>18.29705670000112</v>
+        <v>9.142670699977316</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1010828648805618</v>
+        <v>0.1010828639268875</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1052818956971169</v>
+        <v>0.1052818951010704</v>
       </c>
       <c r="E35" t="n">
         <v>0.001</v>
@@ -1038,13 +1038,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>19.34906390000833</v>
+        <v>9.143091400008416</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1014667170643807</v>
+        <v>0.101466717839241</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1048304507136345</v>
+        <v>0.1048304557800293</v>
       </c>
       <c r="E36" t="n">
         <v>0.001</v>
@@ -1055,13 +1055,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>23.86625209999329</v>
+        <v>9.105881099996623</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1011488603949547</v>
+        <v>0.1011488599181175</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1042531231045723</v>
+        <v>0.104253123998642</v>
       </c>
       <c r="E37" t="n">
         <v>0.001</v>
@@ -1072,13 +1072,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>20.8261169000034</v>
+        <v>9.153427099983674</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1009874522686005</v>
+        <v>0.1009874510765076</v>
       </c>
       <c r="D38" t="n">
-        <v>0.103916392326355</v>
+        <v>0.1039163911342621</v>
       </c>
       <c r="E38" t="n">
         <v>0.001</v>
@@ -1089,13 +1089,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>18.60957430000417</v>
+        <v>9.190204300015466</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1012911056280136</v>
+        <v>0.1012911067008972</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1031577005982399</v>
+        <v>0.103157702088356</v>
       </c>
       <c r="E39" t="n">
         <v>0.001</v>
@@ -1106,13 +1106,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>19.23359250000794</v>
+        <v>9.271141300007002</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1011358751654625</v>
+        <v>0.1011358749270439</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1037755054235458</v>
+        <v>0.10377550303936</v>
       </c>
       <c r="E40" t="n">
         <v>0.001</v>
@@ -1123,13 +1123,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>18.47675180000078</v>
+        <v>9.13095940000494</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1010808735489845</v>
+        <v>0.1010808744430542</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1058501353859901</v>
+        <v>0.1058501377701759</v>
       </c>
       <c r="E41" t="n">
         <v>0.001</v>
@@ -1140,13 +1140,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>18.33798589999788</v>
+        <v>9.149111699982313</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1017377883195877</v>
+        <v>0.1017377885580063</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1041299104690552</v>
+        <v>0.1041299080848694</v>
       </c>
       <c r="E42" t="n">
         <v>0.001</v>
@@ -1157,13 +1157,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>18.3575387000019</v>
+        <v>9.190583199990215</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1009965915083885</v>
+        <v>0.1009965912699699</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1045841610431671</v>
+        <v>0.1045841598510742</v>
       </c>
       <c r="E43" t="n">
         <v>0.001</v>
@@ -1174,13 +1174,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>18.30163590000302</v>
+        <v>9.198208499990869</v>
       </c>
       <c r="C44" t="n">
-        <v>0.101083160340786</v>
+        <v>0.1010831617712975</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1034054467082024</v>
+        <v>0.1034054458141327</v>
       </c>
       <c r="E44" t="n">
         <v>0.001</v>
@@ -1191,10 +1191,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>18.28154409999843</v>
+        <v>9.38469229999464</v>
       </c>
       <c r="C45" t="n">
-        <v>0.100970363676548</v>
+        <v>0.1009703627228737</v>
       </c>
       <c r="D45" t="n">
         <v>0.1043431690335274</v>
@@ -1208,13 +1208,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>18.32852179999463</v>
+        <v>9.322147900005803</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1009452632069588</v>
+        <v>0.1009452629685402</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1040112000703812</v>
+        <v>0.1040112087130547</v>
       </c>
       <c r="E46" t="n">
         <v>0.001</v>
@@ -1225,13 +1225,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>18.11228729999857</v>
+        <v>9.315800599986687</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1013076733350754</v>
+        <v>0.1013076761960983</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1041121023893356</v>
+        <v>0.1041121032834053</v>
       </c>
       <c r="E47" t="n">
         <v>0.001</v>
@@ -1242,13 +1242,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>18.38833699999668</v>
+        <v>9.277057700004661</v>
       </c>
       <c r="C48" t="n">
-        <v>0.100956218957901</v>
+        <v>0.1009562194347382</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1040055823326111</v>
+        <v>0.1040055930614471</v>
       </c>
       <c r="E48" t="n">
         <v>0.001</v>
@@ -1259,13 +1259,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>18.42794910000521</v>
+        <v>9.367836499994155</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1009537404179573</v>
+        <v>0.1009537410736084</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1046117326617241</v>
+        <v>0.104611736536026</v>
       </c>
       <c r="E49" t="n">
         <v>0.001</v>
@@ -1276,13 +1276,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>18.13302900000417</v>
+        <v>9.370228199986741</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1010120661258698</v>
+        <v>0.1010120663642883</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1037149232625961</v>
+        <v>0.1037149208784103</v>
       </c>
       <c r="E50" t="n">
         <v>0.001</v>
@@ -1293,13 +1293,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>18.26906659999804</v>
+        <v>9.258974600001238</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1009067121744156</v>
+        <v>0.1009067124128342</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1037676191329956</v>
+        <v>0.1037676179409027</v>
       </c>
       <c r="E51" t="n">
         <v>0.001</v>
@@ -1310,13 +1310,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>18.39832419999584</v>
+        <v>9.230248499981826</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1010582419633865</v>
+        <v>0.1010582405328751</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1045063284039497</v>
+        <v>0.1045063275098801</v>
       </c>
       <c r="E52" t="n">
         <v>0.001</v>
@@ -1327,10 +1327,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>18.22992220000015</v>
+        <v>9.220275200001197</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1010241395831108</v>
+        <v>0.1010241383910179</v>
       </c>
       <c r="D53" t="n">
         <v>0.1044090887904167</v>
@@ -1344,10 +1344,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>18.86296460000449</v>
+        <v>9.300136799982283</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1010111461877823</v>
+        <v>0.1010111459493637</v>
       </c>
       <c r="D54" t="n">
         <v>0.1032546216249466</v>
@@ -1361,13 +1361,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>18.88028709999344</v>
+        <v>9.209644799993839</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1009399046897888</v>
+        <v>0.100939903318882</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1035103908181191</v>
+        <v>0.1035103914141655</v>
       </c>
       <c r="E55" t="n">
         <v>0.001</v>
@@ -1378,13 +1378,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>18.50583520000509</v>
+        <v>9.269881100015482</v>
       </c>
       <c r="C56" t="n">
         <v>0.101236901640892</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1040230202674866</v>
+        <v>0.104023015499115</v>
       </c>
       <c r="E56" t="n">
         <v>0.001</v>
@@ -1395,13 +1395,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>18.48718579999695</v>
+        <v>9.226876600005198</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1010230072140694</v>
+        <v>0.1010230086445808</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1038510516285896</v>
+        <v>0.1038510519266129</v>
       </c>
       <c r="E57" t="n">
         <v>0.001</v>
@@ -1412,13 +1412,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>18.32655410000007</v>
+        <v>9.221028200001456</v>
       </c>
       <c r="C58" t="n">
-        <v>0.100969356238842</v>
+        <v>0.1009693576097488</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1034468042850494</v>
+        <v>0.1034468039870262</v>
       </c>
       <c r="E58" t="n">
         <v>0.001</v>
@@ -1429,13 +1429,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>18.53970259999915</v>
+        <v>9.328556799999205</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1010315962433815</v>
+        <v>0.1010315960049629</v>
       </c>
       <c r="D59" t="n">
-        <v>0.1044855177402496</v>
+        <v>0.1044855165481567</v>
       </c>
       <c r="E59" t="n">
         <v>0.001</v>
@@ -1446,13 +1446,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>18.55628430000797</v>
+        <v>9.593235999986064</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1008952022790909</v>
+        <v>0.1008952013254166</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1041263324022293</v>
+        <v>0.1041263347864151</v>
       </c>
       <c r="E60" t="n">
         <v>0.001</v>
@@ -1463,13 +1463,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>18.36588890000712</v>
+        <v>9.605916200001957</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1007165363430977</v>
+        <v>0.1007165374755859</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1032268941402435</v>
+        <v>0.1032268899679184</v>
       </c>
       <c r="E61" t="n">
         <v>0.001</v>
@@ -1480,13 +1480,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>18.27722709999944</v>
+        <v>9.482507199980319</v>
       </c>
       <c r="C62" t="n">
-        <v>0.100951655626297</v>
+        <v>0.1009516549110413</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1036164665222168</v>
+        <v>0.103616453409195</v>
       </c>
       <c r="E62" t="n">
         <v>0.001</v>
@@ -1497,13 +1497,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>18.31429999999818</v>
+        <v>9.465425000002142</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1011795322299004</v>
+        <v>0.101179531276226</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1035197252035141</v>
+        <v>0.1035197287797928</v>
       </c>
       <c r="E63" t="n">
         <v>0.001</v>
@@ -1514,13 +1514,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>18.07666830001108</v>
+        <v>9.62664799997583</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1009117361903191</v>
+        <v>0.1009117357134819</v>
       </c>
       <c r="D64" t="n">
-        <v>0.1034269690513611</v>
+        <v>0.1034269666671753</v>
       </c>
       <c r="E64" t="n">
         <v>0.001</v>
@@ -1531,13 +1531,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>18.1599048999924</v>
+        <v>9.49562590001733</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1010136067271233</v>
+        <v>0.1010136066675186</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1052242746949196</v>
+        <v>0.1052242761850357</v>
       </c>
       <c r="E65" t="n">
         <v>0.001</v>
@@ -1548,13 +1548,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>18.02405500000168</v>
+        <v>9.451811300008558</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1011700711250305</v>
+        <v>0.1011700727939606</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1030667042732239</v>
+        <v>0.1030667054653168</v>
       </c>
       <c r="E66" t="n">
         <v>0.001</v>
@@ -1565,10 +1565,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>18.21849749999819</v>
+        <v>9.280807300005108</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1011057034730911</v>
+        <v>0.1011057044863701</v>
       </c>
       <c r="D67" t="n">
         <v>0.1030400630831718</v>
@@ -1582,13 +1582,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>18.35737449998851</v>
+        <v>9.278577700024471</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1007410899400711</v>
+        <v>0.1007410902380943</v>
       </c>
       <c r="D68" t="n">
-        <v>0.1024833518266678</v>
+        <v>0.102483352124691</v>
       </c>
       <c r="E68" t="n">
         <v>0.001</v>
@@ -1599,13 +1599,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>18.20142939999641</v>
+        <v>9.151600800018059</v>
       </c>
       <c r="C69" t="n">
-        <v>0.1008338025808334</v>
+        <v>0.1008338030576706</v>
       </c>
       <c r="D69" t="n">
-        <v>0.1039719265699387</v>
+        <v>0.1039719253778458</v>
       </c>
       <c r="E69" t="n">
         <v>0.001</v>
@@ -1616,13 +1616,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>18.37407089999761</v>
+        <v>9.563714699994307</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1009264045953751</v>
+        <v>0.1009264026880264</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1034272575378418</v>
+        <v>0.1034272623062134</v>
       </c>
       <c r="E70" t="n">
         <v>0.001</v>
@@ -1633,13 +1633,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>18.21539320000738</v>
+        <v>9.49026779999258</v>
       </c>
       <c r="C71" t="n">
-        <v>0.100537769973278</v>
+        <v>0.1005377697348595</v>
       </c>
       <c r="D71" t="n">
-        <v>0.1021865981817245</v>
+        <v>0.1021865993738174</v>
       </c>
       <c r="E71" t="n">
         <v>0.001</v>
@@ -1650,13 +1650,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>18.11007710000558</v>
+        <v>9.540585000009742</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1005652282238007</v>
+        <v>0.1005652265548706</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1043123644590378</v>
+        <v>0.1043123653531075</v>
       </c>
       <c r="E72" t="n">
         <v>0.001</v>
@@ -1667,13 +1667,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>18.28130299999611</v>
+        <v>9.42497409999487</v>
       </c>
       <c r="C73" t="n">
         <v>0.1004218720197678</v>
       </c>
       <c r="D73" t="n">
-        <v>0.1017958825826645</v>
+        <v>0.1017958810925484</v>
       </c>
       <c r="E73" t="n">
         <v>0.001</v>
@@ -1684,13 +1684,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>18.0844986000011</v>
+        <v>9.207267399993725</v>
       </c>
       <c r="C74" t="n">
-        <v>0.09958806014060974</v>
+        <v>0.09958805644512177</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1012453252077103</v>
+        <v>0.1012453293800354</v>
       </c>
       <c r="E74" t="n">
         <v>0.001</v>
@@ -1701,13 +1701,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>18.25880619999953</v>
+        <v>9.192282800009707</v>
       </c>
       <c r="C75" t="n">
-        <v>0.09883176654577255</v>
+        <v>0.09883176451921463</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1032276776432991</v>
+        <v>0.1032276672124863</v>
       </c>
       <c r="E75" t="n">
         <v>0.001</v>
@@ -1718,13 +1718,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>18.22341960000631</v>
+        <v>9.235585399990669</v>
       </c>
       <c r="C76" t="n">
-        <v>0.09707366901636123</v>
+        <v>0.09707366251945496</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1013739460706711</v>
+        <v>0.1013739621639252</v>
       </c>
       <c r="E76" t="n">
         <v>0.001</v>
@@ -1735,13 +1735,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>18.22630549999303</v>
+        <v>9.524586199986516</v>
       </c>
       <c r="C77" t="n">
-        <v>0.09366093778610229</v>
+        <v>0.09366092509031296</v>
       </c>
       <c r="D77" t="n">
-        <v>0.09176294386386871</v>
+        <v>0.09176292568445206</v>
       </c>
       <c r="E77" t="n">
         <v>0.001</v>
@@ -1752,13 +1752,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>18.35181949999242</v>
+        <v>9.292349900002591</v>
       </c>
       <c r="C78" t="n">
-        <v>0.08637160611152649</v>
+        <v>0.08637158739566803</v>
       </c>
       <c r="D78" t="n">
-        <v>0.09541149973869324</v>
+        <v>0.09541141629219055</v>
       </c>
       <c r="E78" t="n">
         <v>0.001</v>
@@ -1769,13 +1769,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>18.16445479998947</v>
+        <v>9.240665300021647</v>
       </c>
       <c r="C79" t="n">
-        <v>0.08547844725847244</v>
+        <v>0.08547840487957001</v>
       </c>
       <c r="D79" t="n">
-        <v>0.08673752725124359</v>
+        <v>0.08673758625984192</v>
       </c>
       <c r="E79" t="n">
         <v>0.001</v>
@@ -1786,13 +1786,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>18.15792550001061</v>
+        <v>9.149674500018591</v>
       </c>
       <c r="C80" t="n">
-        <v>0.08026753288507461</v>
+        <v>0.08026745855808258</v>
       </c>
       <c r="D80" t="n">
-        <v>0.08145746111869812</v>
+        <v>0.08145755410194397</v>
       </c>
       <c r="E80" t="n">
         <v>0.001</v>
@@ -1803,13 +1803,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>18.11037480000232</v>
+        <v>9.303600199986249</v>
       </c>
       <c r="C81" t="n">
-        <v>0.07527257835865021</v>
+        <v>0.0752725105881691</v>
       </c>
       <c r="D81" t="n">
-        <v>0.08654089003801346</v>
+        <v>0.08653973877429962</v>
       </c>
       <c r="E81" t="n">
         <v>0.001</v>
@@ -1820,13 +1820,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>18.30872430000454</v>
+        <v>9.259714700019686</v>
       </c>
       <c r="C82" t="n">
-        <v>0.07329757344722748</v>
+        <v>0.07329722666740418</v>
       </c>
       <c r="D82" t="n">
-        <v>0.07204181373119355</v>
+        <v>0.07204134047031402</v>
       </c>
       <c r="E82" t="n">
         <v>0.001</v>
@@ -1837,13 +1837,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>18.24945290001051</v>
+        <v>9.152520300005563</v>
       </c>
       <c r="C83" t="n">
-        <v>0.06857887476682663</v>
+        <v>0.06857879722118378</v>
       </c>
       <c r="D83" t="n">
-        <v>0.06928415119647979</v>
+        <v>0.06928370773792267</v>
       </c>
       <c r="E83" t="n">
         <v>0.001</v>
@@ -1854,13 +1854,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>18.32568969999556</v>
+        <v>9.291520200000377</v>
       </c>
       <c r="C84" t="n">
-        <v>0.06641191613674163</v>
+        <v>0.06641169461607933</v>
       </c>
       <c r="D84" t="n">
-        <v>0.06628178030252457</v>
+        <v>0.06628233671188355</v>
       </c>
       <c r="E84" t="n">
         <v>0.001</v>
@@ -1871,13 +1871,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>18.05442960000073</v>
+        <v>9.294865300005767</v>
       </c>
       <c r="C85" t="n">
-        <v>0.06363645654916764</v>
+        <v>0.0636364024579525</v>
       </c>
       <c r="D85" t="n">
-        <v>0.06601713418960571</v>
+        <v>0.06601768434047699</v>
       </c>
       <c r="E85" t="n">
         <v>0.001</v>
@@ -1888,13 +1888,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>18.18017999999574</v>
+        <v>9.190622299996903</v>
       </c>
       <c r="C86" t="n">
-        <v>0.06085209763050079</v>
+        <v>0.06085210800170898</v>
       </c>
       <c r="D86" t="n">
-        <v>0.06550140649080277</v>
+        <v>0.06550127923488618</v>
       </c>
       <c r="E86" t="n">
         <v>0.001</v>
@@ -1905,13 +1905,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>18.24305689999892</v>
+        <v>9.36846530000912</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0600231753885746</v>
+        <v>0.06002315303683281</v>
       </c>
       <c r="D87" t="n">
-        <v>0.05863518759608269</v>
+        <v>0.05863507375121117</v>
       </c>
       <c r="E87" t="n">
         <v>0.001</v>
@@ -1922,13 +1922,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>18.24801270000171</v>
+        <v>9.45747449999908</v>
       </c>
       <c r="C88" t="n">
-        <v>0.05711125519871712</v>
+        <v>0.05711118993163109</v>
       </c>
       <c r="D88" t="n">
-        <v>0.05611026555299759</v>
+        <v>0.05611026078462601</v>
       </c>
       <c r="E88" t="n">
         <v>0.001</v>
@@ -1939,13 +1939,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>18.52844399999594</v>
+        <v>9.202814300020691</v>
       </c>
       <c r="C89" t="n">
-        <v>0.05335339212417602</v>
+        <v>0.05335340228676796</v>
       </c>
       <c r="D89" t="n">
-        <v>0.07420735716819764</v>
+        <v>0.07420729935169219</v>
       </c>
       <c r="E89" t="n">
         <v>0.001</v>
@@ -1956,13 +1956,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>19.20774130000791</v>
+        <v>9.340817699994659</v>
       </c>
       <c r="C90" t="n">
-        <v>0.05663062396645546</v>
+        <v>0.05663068813085556</v>
       </c>
       <c r="D90" t="n">
-        <v>0.05767605260014534</v>
+        <v>0.05767700970172882</v>
       </c>
       <c r="E90" t="n">
         <v>0.001</v>
@@ -1973,13 +1973,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>18.17659959998855</v>
+        <v>9.185006799991243</v>
       </c>
       <c r="C91" t="n">
-        <v>0.05508954384922981</v>
+        <v>0.05508957999944687</v>
       </c>
       <c r="D91" t="n">
-        <v>0.06638684928417206</v>
+        <v>0.06638789474964142</v>
       </c>
       <c r="E91" t="n">
         <v>0.001</v>
@@ -1990,13 +1990,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>18.34582459999365</v>
+        <v>9.220498799986672</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0530012543797493</v>
+        <v>0.05300149205327034</v>
       </c>
       <c r="D92" t="n">
-        <v>0.05565015166997909</v>
+        <v>0.05564873814582825</v>
       </c>
       <c r="E92" t="n">
         <v>0.001</v>
@@ -2007,13 +2007,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>18.50040200000512</v>
+        <v>9.171811599982902</v>
       </c>
       <c r="C93" t="n">
-        <v>0.05195971128344536</v>
+        <v>0.05195979663729668</v>
       </c>
       <c r="D93" t="n">
-        <v>0.05119746744632721</v>
+        <v>0.05119607403874397</v>
       </c>
       <c r="E93" t="n">
         <v>0.001</v>
@@ -2024,13 +2024,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>18.38002640000195</v>
+        <v>9.211696199985454</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0502878657579422</v>
+        <v>0.05028767761588097</v>
       </c>
       <c r="D94" t="n">
-        <v>0.06325141191482545</v>
+        <v>0.06325147241353989</v>
       </c>
       <c r="E94" t="n">
         <v>0.001</v>
@@ -2041,13 +2041,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>18.75459959999716</v>
+        <v>9.262492200010456</v>
       </c>
       <c r="C95" t="n">
-        <v>0.05022237193584442</v>
+        <v>0.05022242265939712</v>
       </c>
       <c r="D95" t="n">
-        <v>0.04833681210875511</v>
+        <v>0.04833653956651687</v>
       </c>
       <c r="E95" t="n">
         <v>0.001</v>
@@ -2058,13 +2058,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>18.20296369999414</v>
+        <v>9.299911800015252</v>
       </c>
       <c r="C96" t="n">
-        <v>0.04556268095970153</v>
+        <v>0.04556269177794457</v>
       </c>
       <c r="D96" t="n">
-        <v>0.04833538040518761</v>
+        <v>0.04833483129739762</v>
       </c>
       <c r="E96" t="n">
         <v>0.001</v>
@@ -2075,13 +2075,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>18.44603799999459</v>
+        <v>9.200642799987691</v>
       </c>
       <c r="C97" t="n">
-        <v>0.04430756375193596</v>
+        <v>0.04430759507417679</v>
       </c>
       <c r="D97" t="n">
-        <v>0.04445142209529877</v>
+        <v>0.04445186331868171</v>
       </c>
       <c r="E97" t="n">
         <v>0.001</v>
@@ -2092,13 +2092,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>18.43129700000281</v>
+        <v>9.255113999999594</v>
       </c>
       <c r="C98" t="n">
-        <v>0.04327390649914741</v>
+        <v>0.04327393934130669</v>
       </c>
       <c r="D98" t="n">
-        <v>0.05506905928254127</v>
+        <v>0.05507374987006187</v>
       </c>
       <c r="E98" t="n">
         <v>0.001</v>
@@ -2109,13 +2109,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>18.09792030000244</v>
+        <v>9.278313499991782</v>
       </c>
       <c r="C99" t="n">
-        <v>0.04324535438418389</v>
+        <v>0.04324613952636719</v>
       </c>
       <c r="D99" t="n">
-        <v>0.05012939959764481</v>
+        <v>0.05012822046875954</v>
       </c>
       <c r="E99" t="n">
         <v>0.001</v>
@@ -2126,13 +2126,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>18.17470099999628</v>
+        <v>9.440200599987293</v>
       </c>
       <c r="C100" t="n">
-        <v>0.04106324905157089</v>
+        <v>0.04106341427564621</v>
       </c>
       <c r="D100" t="n">
-        <v>0.04080707043409348</v>
+        <v>0.04080950886011123</v>
       </c>
       <c r="E100" t="n">
         <v>0.001</v>
@@ -2143,13 +2143,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>18.40717659999791</v>
+        <v>9.344586399995023</v>
       </c>
       <c r="C101" t="n">
-        <v>0.04025292381644249</v>
+        <v>0.04025303623080254</v>
       </c>
       <c r="D101" t="n">
-        <v>0.04335901737213135</v>
+        <v>0.04336843848228455</v>
       </c>
       <c r="E101" t="n">
         <v>0.001</v>
@@ -2160,13 +2160,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>18.58694359999208</v>
+        <v>9.385097299993504</v>
       </c>
       <c r="C102" t="n">
-        <v>0.03832316488027573</v>
+        <v>0.03832518088817596</v>
       </c>
       <c r="D102" t="n">
-        <v>0.03919594198465347</v>
+        <v>0.03919443890452385</v>
       </c>
       <c r="E102" t="n">
         <v>0.0005</v>
@@ -2177,13 +2177,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>18.37549880000006</v>
+        <v>9.377321600011783</v>
       </c>
       <c r="C103" t="n">
-        <v>0.03638783460855484</v>
+        <v>0.03638772532343865</v>
       </c>
       <c r="D103" t="n">
-        <v>0.03733713269233704</v>
+        <v>0.03733713135123253</v>
       </c>
       <c r="E103" t="n">
         <v>0.0005</v>
@@ -2194,13 +2194,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>18.44873960000405</v>
+        <v>9.472944399982225</v>
       </c>
       <c r="C104" t="n">
-        <v>0.03569641372561455</v>
+        <v>0.03569710753858089</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0361791530251503</v>
+        <v>0.03617949485778808</v>
       </c>
       <c r="E104" t="n">
         <v>0.0005</v>
@@ -2211,13 +2211,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>18.44113279999874</v>
+        <v>9.450040700001409</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0364354222714901</v>
+        <v>0.03643506515026092</v>
       </c>
       <c r="D105" t="n">
-        <v>0.03819937929511071</v>
+        <v>0.03819971144199372</v>
       </c>
       <c r="E105" t="n">
         <v>0.0005</v>
@@ -2228,13 +2228,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>18.61441530000593</v>
+        <v>9.545130100013921</v>
       </c>
       <c r="C106" t="n">
-        <v>0.03566328038275242</v>
+        <v>0.03566322693228722</v>
       </c>
       <c r="D106" t="n">
-        <v>0.03685211509466171</v>
+        <v>0.03685203924775124</v>
       </c>
       <c r="E106" t="n">
         <v>0.0005</v>
@@ -2245,13 +2245,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>18.39856519999739</v>
+        <v>9.523872200021287</v>
       </c>
       <c r="C107" t="n">
-        <v>0.03424330621957779</v>
+        <v>0.03424344426393509</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0380141644179821</v>
+        <v>0.03801330670714378</v>
       </c>
       <c r="E107" t="n">
         <v>0.0005</v>
@@ -2262,13 +2262,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>18.47535300000163</v>
+        <v>9.459303800016642</v>
       </c>
       <c r="C108" t="n">
-        <v>0.03464931711554527</v>
+        <v>0.03464922493696213</v>
       </c>
       <c r="D108" t="n">
-        <v>0.0356191585958004</v>
+        <v>0.03561889722943306</v>
       </c>
       <c r="E108" t="n">
         <v>0.0005</v>
@@ -2279,13 +2279,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>18.19902279999224</v>
+        <v>9.608356799988542</v>
       </c>
       <c r="C109" t="n">
-        <v>0.03362201079726219</v>
+        <v>0.03362215587496758</v>
       </c>
       <c r="D109" t="n">
-        <v>0.03547033652663231</v>
+        <v>0.03546959653496742</v>
       </c>
       <c r="E109" t="n">
         <v>0.0005</v>
@@ -2296,13 +2296,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>18.60755339999741</v>
+        <v>9.452932799991686</v>
       </c>
       <c r="C110" t="n">
-        <v>0.03330289319157601</v>
+        <v>0.03330274078249931</v>
       </c>
       <c r="D110" t="n">
-        <v>0.03349204599857331</v>
+        <v>0.03349215775728226</v>
       </c>
       <c r="E110" t="n">
         <v>0.0005</v>
@@ -2313,13 +2313,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>18.66885210000328</v>
+        <v>9.50774219998857</v>
       </c>
       <c r="C111" t="n">
-        <v>0.03238853941857815</v>
+        <v>0.0323886399269104</v>
       </c>
       <c r="D111" t="n">
-        <v>0.03487465128302574</v>
+        <v>0.03487431854009628</v>
       </c>
       <c r="E111" t="n">
         <v>0.0005</v>
@@ -2330,13 +2330,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>18.35180089999631</v>
+        <v>9.488458400010131</v>
       </c>
       <c r="C112" t="n">
-        <v>0.03205888324975967</v>
+        <v>0.03205891743302345</v>
       </c>
       <c r="D112" t="n">
-        <v>0.03480417177081108</v>
+        <v>0.03480442449450493</v>
       </c>
       <c r="E112" t="n">
         <v>0.0005</v>
@@ -2347,13 +2347,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>18.46214489999693</v>
+        <v>9.567276399990078</v>
       </c>
       <c r="C113" t="n">
-        <v>0.03258386179804802</v>
+        <v>0.0325839738547802</v>
       </c>
       <c r="D113" t="n">
-        <v>0.0363231098651886</v>
+        <v>0.03632308542728424</v>
       </c>
       <c r="E113" t="n">
         <v>0.0005</v>
@@ -2364,13 +2364,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>18.35821760000545</v>
+        <v>9.3328808999795</v>
       </c>
       <c r="C114" t="n">
-        <v>0.03346710336208344</v>
+        <v>0.03346752575039864</v>
       </c>
       <c r="D114" t="n">
-        <v>0.0335937263071537</v>
+        <v>0.0335945725440979</v>
       </c>
       <c r="E114" t="n">
         <v>0.0005</v>
@@ -2381,13 +2381,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>18.39104550000047</v>
+        <v>9.337038800003938</v>
       </c>
       <c r="C115" t="n">
-        <v>0.03068167120218277</v>
+        <v>0.03068226248025894</v>
       </c>
       <c r="D115" t="n">
-        <v>0.03395525023341179</v>
+        <v>0.03395565435290337</v>
       </c>
       <c r="E115" t="n">
         <v>0.0005</v>
@@ -2398,13 +2398,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>18.26184370000556</v>
+        <v>9.233786500000861</v>
       </c>
       <c r="C116" t="n">
-        <v>0.03153876572847367</v>
+        <v>0.0315382781624794</v>
       </c>
       <c r="D116" t="n">
-        <v>0.03117051035165787</v>
+        <v>0.03117083005607128</v>
       </c>
       <c r="E116" t="n">
         <v>0.0005</v>
@@ -2415,13 +2415,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>18.58528119999391</v>
+        <v>9.413940599974012</v>
       </c>
       <c r="C117" t="n">
-        <v>0.03166352137923241</v>
+        <v>0.03166279402375221</v>
       </c>
       <c r="D117" t="n">
-        <v>0.04473908692598343</v>
+        <v>0.04474386900663376</v>
       </c>
       <c r="E117" t="n">
         <v>0.0005</v>
@@ -2432,13 +2432,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>18.3877380000049</v>
+        <v>9.228413600008935</v>
       </c>
       <c r="C118" t="n">
-        <v>0.03191783726215362</v>
+        <v>0.03191873186826706</v>
       </c>
       <c r="D118" t="n">
-        <v>0.03006932988762856</v>
+        <v>0.03006964467465878</v>
       </c>
       <c r="E118" t="n">
         <v>0.0005</v>
@@ -2449,13 +2449,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>18.36457879999944</v>
+        <v>9.351757099997485</v>
       </c>
       <c r="C119" t="n">
-        <v>0.02870724238455296</v>
+        <v>0.02870744462311268</v>
       </c>
       <c r="D119" t="n">
-        <v>0.03198616176843643</v>
+        <v>0.03198705673217773</v>
       </c>
       <c r="E119" t="n">
         <v>0.0005</v>
@@ -2466,13 +2466,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>18.36500069999602</v>
+        <v>9.13542210002197</v>
       </c>
       <c r="C120" t="n">
-        <v>0.02864231297373772</v>
+        <v>0.02864241436123848</v>
       </c>
       <c r="D120" t="n">
-        <v>0.02928378663957119</v>
+        <v>0.02928410455584526</v>
       </c>
       <c r="E120" t="n">
         <v>0.0005</v>
@@ -2483,13 +2483,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>18.39312849999988</v>
+        <v>9.329265000007581</v>
       </c>
       <c r="C121" t="n">
-        <v>0.02882477690279484</v>
+        <v>0.02882485829293728</v>
       </c>
       <c r="D121" t="n">
-        <v>0.03130551844835281</v>
+        <v>0.03130624383687973</v>
       </c>
       <c r="E121" t="n">
         <v>0.0005</v>
@@ -2500,13 +2500,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>18.28186110001116</v>
+        <v>9.224719799996819</v>
       </c>
       <c r="C122" t="n">
-        <v>0.02839313805103302</v>
+        <v>0.02839365988969803</v>
       </c>
       <c r="D122" t="n">
-        <v>0.0295223143696785</v>
+        <v>0.02952281013131142</v>
       </c>
       <c r="E122" t="n">
         <v>0.0005</v>
@@ -2517,13 +2517,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>18.57637959999556</v>
+        <v>9.22414989999379</v>
       </c>
       <c r="C123" t="n">
-        <v>0.02787481559813023</v>
+        <v>0.02787499290704727</v>
       </c>
       <c r="D123" t="n">
-        <v>0.02949617594480515</v>
+        <v>0.0294960243999958</v>
       </c>
       <c r="E123" t="n">
         <v>0.0005</v>
@@ -2534,13 +2534,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>18.58450539999467</v>
+        <v>9.426346499996725</v>
       </c>
       <c r="C124" t="n">
-        <v>0.02765609464049339</v>
+        <v>0.02765612603724003</v>
       </c>
       <c r="D124" t="n">
-        <v>0.03317151412367821</v>
+        <v>0.03317151993513107</v>
       </c>
       <c r="E124" t="n">
         <v>0.0005</v>
@@ -2551,13 +2551,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>18.28568529999757</v>
+        <v>9.440548899990972</v>
       </c>
       <c r="C125" t="n">
-        <v>0.02726971206068993</v>
+        <v>0.02726976718008518</v>
       </c>
       <c r="D125" t="n">
-        <v>0.02931997060775757</v>
+        <v>0.02932018056511879</v>
       </c>
       <c r="E125" t="n">
         <v>0.0005</v>
@@ -2568,13 +2568,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>18.3406607999932</v>
+        <v>9.228498899989063</v>
       </c>
       <c r="C126" t="n">
-        <v>0.02875845392048359</v>
+        <v>0.02875844487547875</v>
       </c>
       <c r="D126" t="n">
-        <v>0.03063629239797592</v>
+        <v>0.03063596591353417</v>
       </c>
       <c r="E126" t="n">
         <v>0.0005</v>
@@ -2585,13 +2585,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>18.52901949999796</v>
+        <v>9.223719400004484</v>
       </c>
       <c r="C127" t="n">
-        <v>0.02741944009065628</v>
+        <v>0.02741968737542629</v>
       </c>
       <c r="D127" t="n">
-        <v>0.02755790859460831</v>
+        <v>0.02755766972899437</v>
       </c>
       <c r="E127" t="n">
         <v>0.0005</v>
@@ -2602,13 +2602,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>18.22468449998996</v>
+        <v>9.206059999996796</v>
       </c>
       <c r="C128" t="n">
-        <v>0.02553580591082573</v>
+        <v>0.02553588542342186</v>
       </c>
       <c r="D128" t="n">
-        <v>0.02857449755072594</v>
+        <v>0.02857384607195854</v>
       </c>
       <c r="E128" t="n">
         <v>0.0005</v>
@@ -2619,13 +2619,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>18.22703080000065</v>
+        <v>9.324318300001323</v>
       </c>
       <c r="C129" t="n">
-        <v>0.02714399421215057</v>
+        <v>0.02714416497945785</v>
       </c>
       <c r="D129" t="n">
-        <v>0.03032071463763714</v>
+        <v>0.0303210224211216</v>
       </c>
       <c r="E129" t="n">
         <v>0.0005</v>
@@ -2636,13 +2636,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>18.18220650000148</v>
+        <v>9.466818399989279</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0269401990622282</v>
+        <v>0.0269423441439867</v>
       </c>
       <c r="D130" t="n">
-        <v>0.02921174190938473</v>
+        <v>0.02920339085161686</v>
       </c>
       <c r="E130" t="n">
         <v>0.0005</v>
@@ -2653,13 +2653,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>18.45793779999076</v>
+        <v>9.553722400014522</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0257617569565773</v>
+        <v>0.0257607287466526</v>
       </c>
       <c r="D131" t="n">
-        <v>0.02763792134821415</v>
+        <v>0.02764507979154587</v>
       </c>
       <c r="E131" t="n">
         <v>0.0005</v>
@@ -2670,13 +2670,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>18.44065170000249</v>
+        <v>9.462758600013331</v>
       </c>
       <c r="C132" t="n">
-        <v>0.02628254964947701</v>
+        <v>0.02628428710997105</v>
       </c>
       <c r="D132" t="n">
-        <v>0.02872800037264824</v>
+        <v>0.0287250879406929</v>
       </c>
       <c r="E132" t="n">
         <v>0.0005</v>
@@ -2687,13 +2687,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>18.3708736999979</v>
+        <v>9.46369269999559</v>
       </c>
       <c r="C133" t="n">
-        <v>0.02718670144677162</v>
+        <v>0.0271860830783844</v>
       </c>
       <c r="D133" t="n">
-        <v>0.02872305534780025</v>
+        <v>0.02871584676206112</v>
       </c>
       <c r="E133" t="n">
         <v>0.0005</v>
@@ -2704,13 +2704,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>18.38214190000144</v>
+        <v>9.45314659998985</v>
       </c>
       <c r="C134" t="n">
-        <v>0.02599755372107029</v>
+        <v>0.02599465243518352</v>
       </c>
       <c r="D134" t="n">
-        <v>0.02869856283068657</v>
+        <v>0.02869945965707302</v>
       </c>
       <c r="E134" t="n">
         <v>0.0005</v>
@@ -2721,13 +2721,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>18.68202580000798</v>
+        <v>9.341253399994457</v>
       </c>
       <c r="C135" t="n">
-        <v>0.02616145594418049</v>
+        <v>0.02616842727363109</v>
       </c>
       <c r="D135" t="n">
-        <v>0.02691844180226326</v>
+        <v>0.02693915635347366</v>
       </c>
       <c r="E135" t="n">
         <v>0.0005</v>
@@ -2738,13 +2738,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>17.99759769999946</v>
+        <v>9.453122099977918</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0247825234234333</v>
+        <v>0.0247844899892807</v>
       </c>
       <c r="D136" t="n">
-        <v>0.0289942666888237</v>
+        <v>0.02897049367427826</v>
       </c>
       <c r="E136" t="n">
         <v>0.0005</v>
@@ -2755,13 +2755,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>18.74801499999012</v>
+        <v>9.45631019998109</v>
       </c>
       <c r="C137" t="n">
-        <v>0.02501756438612938</v>
+        <v>0.02501585680246353</v>
       </c>
       <c r="D137" t="n">
-        <v>0.02783782817423344</v>
+        <v>0.02783504143357277</v>
       </c>
       <c r="E137" t="n">
         <v>0.0005</v>
@@ -2772,13 +2772,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>18.01727050000045</v>
+        <v>9.321028200007277</v>
       </c>
       <c r="C138" t="n">
-        <v>0.02417439261078835</v>
+        <v>0.02417354044318199</v>
       </c>
       <c r="D138" t="n">
-        <v>0.02715658999979496</v>
+        <v>0.02715586319565773</v>
       </c>
       <c r="E138" t="n">
         <v>0.0005</v>
@@ -2789,13 +2789,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>18.08050919999368</v>
+        <v>9.249581900017802</v>
       </c>
       <c r="C139" t="n">
-        <v>0.02439760665595531</v>
+        <v>0.02439743658900261</v>
       </c>
       <c r="D139" t="n">
-        <v>0.02479133754968643</v>
+        <v>0.02479372963309288</v>
       </c>
       <c r="E139" t="n">
         <v>0.0005</v>
@@ -2806,13 +2806,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>17.98600389999046</v>
+        <v>9.550009499973385</v>
       </c>
       <c r="C140" t="n">
-        <v>0.02347145879268646</v>
+        <v>0.02347110097110271</v>
       </c>
       <c r="D140" t="n">
-        <v>0.03005186915397644</v>
+        <v>0.0300454381108284</v>
       </c>
       <c r="E140" t="n">
         <v>0.0005</v>
@@ -2823,13 +2823,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>17.98862809999264</v>
+        <v>9.426476699998602</v>
       </c>
       <c r="C141" t="n">
-        <v>0.02357908117771149</v>
+        <v>0.02357837998867035</v>
       </c>
       <c r="D141" t="n">
-        <v>0.02455502763390541</v>
+        <v>0.02455668523907661</v>
       </c>
       <c r="E141" t="n">
         <v>0.0005</v>
@@ -2840,13 +2840,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>18.17722579999827</v>
+        <v>9.597603200003505</v>
       </c>
       <c r="C142" t="n">
-        <v>0.02310428223013878</v>
+        <v>0.02310419254004955</v>
       </c>
       <c r="D142" t="n">
-        <v>0.02586900129914284</v>
+        <v>0.02587066918611526</v>
       </c>
       <c r="E142" t="n">
         <v>0.0005</v>
@@ -2857,13 +2857,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>17.85555559999193</v>
+        <v>9.418855500000063</v>
       </c>
       <c r="C143" t="n">
-        <v>0.02367774674296379</v>
+        <v>0.02367820228636265</v>
       </c>
       <c r="D143" t="n">
-        <v>0.03104312747716904</v>
+        <v>0.03103739067912102</v>
       </c>
       <c r="E143" t="n">
         <v>0.0005</v>
@@ -2874,13 +2874,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>17.97856460000912</v>
+        <v>9.399470099975588</v>
       </c>
       <c r="C144" t="n">
-        <v>0.02519822517037392</v>
+        <v>0.02519918520748615</v>
       </c>
       <c r="D144" t="n">
-        <v>0.02352789364755154</v>
+        <v>0.02353470057249069</v>
       </c>
       <c r="E144" t="n">
         <v>0.0005</v>
@@ -2891,13 +2891,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>18.07368800000404</v>
+        <v>9.239194699999643</v>
       </c>
       <c r="C145" t="n">
-        <v>0.02353539642691612</v>
+        <v>0.02353310462832451</v>
       </c>
       <c r="D145" t="n">
-        <v>0.02822167932987213</v>
+        <v>0.02824817940592766</v>
       </c>
       <c r="E145" t="n">
         <v>0.0005</v>
@@ -2908,13 +2908,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>18.06567369999539</v>
+        <v>9.21390590001829</v>
       </c>
       <c r="C146" t="n">
-        <v>0.02301878456771374</v>
+        <v>0.02302384367585182</v>
       </c>
       <c r="D146" t="n">
-        <v>0.02455888710916042</v>
+        <v>0.02456187337636948</v>
       </c>
       <c r="E146" t="n">
         <v>0.0005</v>
@@ -2925,13 +2925,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>17.97559490001004</v>
+        <v>9.469136300001992</v>
       </c>
       <c r="C147" t="n">
-        <v>0.02153338292241096</v>
+        <v>0.02153369233012199</v>
       </c>
       <c r="D147" t="n">
-        <v>0.02401805274188519</v>
+        <v>0.0240124562382698</v>
       </c>
       <c r="E147" t="n">
         <v>0.0005</v>
@@ -2942,13 +2942,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>17.88207310000143</v>
+        <v>9.195540100015933</v>
       </c>
       <c r="C148" t="n">
-        <v>0.02278201960027218</v>
+        <v>0.0227864907681942</v>
       </c>
       <c r="D148" t="n">
-        <v>0.02479523077607155</v>
+        <v>0.0247936288267374</v>
       </c>
       <c r="E148" t="n">
         <v>0.0005</v>
@@ -2959,13 +2959,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>17.9619160000002</v>
+        <v>9.341255400009686</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0243615428507328</v>
+        <v>0.02436292085051537</v>
       </c>
       <c r="D149" t="n">
-        <v>0.02910342164337635</v>
+        <v>0.02907446227967739</v>
       </c>
       <c r="E149" t="n">
         <v>0.0005</v>
@@ -2976,13 +2976,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>18.1451769000123</v>
+        <v>9.330880800000159</v>
       </c>
       <c r="C150" t="n">
-        <v>0.02401992999017239</v>
+        <v>0.02402920332551002</v>
       </c>
       <c r="D150" t="n">
-        <v>0.02283899791538715</v>
+        <v>0.02277995400130749</v>
       </c>
       <c r="E150" t="n">
         <v>0.0005</v>
@@ -2993,13 +2993,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>17.98533979999775</v>
+        <v>9.395427999988897</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0219524343162775</v>
+        <v>0.02194534668326378</v>
       </c>
       <c r="D151" t="n">
-        <v>0.0226217520236969</v>
+        <v>0.02262800082564354</v>
       </c>
       <c r="E151" t="n">
         <v>0.0005</v>
@@ -3010,13 +3010,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>17.88272200000938</v>
+        <v>9.269425100006629</v>
       </c>
       <c r="C152" t="n">
-        <v>0.02119990023970604</v>
+        <v>0.0211590758562088</v>
       </c>
       <c r="D152" t="n">
-        <v>0.02616449549794197</v>
+        <v>0.02616938404738903</v>
       </c>
       <c r="E152" t="n">
         <v>0.0005</v>
@@ -3027,13 +3027,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>17.86090919999697</v>
+        <v>9.185919699986698</v>
       </c>
       <c r="C153" t="n">
-        <v>0.02366227629780769</v>
+        <v>0.02398698455095291</v>
       </c>
       <c r="D153" t="n">
-        <v>0.02471661746501923</v>
+        <v>0.02760378330945969</v>
       </c>
       <c r="E153" t="n">
         <v>0.0005</v>
@@ -3044,13 +3044,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>18.08908739998878</v>
+        <v>9.193826399976388</v>
       </c>
       <c r="C154" t="n">
-        <v>0.02395173753798008</v>
+        <v>0.02206903977692127</v>
       </c>
       <c r="D154" t="n">
-        <v>0.02756156377494335</v>
+        <v>0.02156348139047623</v>
       </c>
       <c r="E154" t="n">
         <v>0.0005</v>
@@ -3061,13 +3061,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>18.05360339999606</v>
+        <v>9.322506199998315</v>
       </c>
       <c r="C155" t="n">
-        <v>0.02159026336669922</v>
+        <v>0.02181430840492249</v>
       </c>
       <c r="D155" t="n">
-        <v>0.02309703841805458</v>
+        <v>0.02616150707006454</v>
       </c>
       <c r="E155" t="n">
         <v>0.0005</v>
@@ -3078,13 +3078,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>18.08103129999654</v>
+        <v>9.183077499998035</v>
       </c>
       <c r="C156" t="n">
-        <v>0.02214048498868942</v>
+        <v>0.02139673858880997</v>
       </c>
       <c r="D156" t="n">
-        <v>0.02280773974955082</v>
+        <v>0.02526236228644848</v>
       </c>
       <c r="E156" t="n">
         <v>0.0005</v>
@@ -3095,13 +3095,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>18.04389020000235</v>
+        <v>9.137875800020993</v>
       </c>
       <c r="C157" t="n">
-        <v>0.02199295404553413</v>
+        <v>0.02230737271904945</v>
       </c>
       <c r="D157" t="n">
-        <v>0.03484269708395004</v>
+        <v>0.02277358368039131</v>
       </c>
       <c r="E157" t="n">
         <v>0.0005</v>
@@ -3112,13 +3112,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>17.86361449999094</v>
+        <v>9.207938599982299</v>
       </c>
       <c r="C158" t="n">
-        <v>0.02746935352683067</v>
+        <v>0.02188756914436817</v>
       </c>
       <c r="D158" t="n">
-        <v>0.02184440031647682</v>
+        <v>0.02427712172269821</v>
       </c>
       <c r="E158" t="n">
         <v>0.0005</v>
@@ -3129,13 +3129,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>17.92040230000566</v>
+        <v>9.12490950000938</v>
       </c>
       <c r="C159" t="n">
-        <v>0.02177636808156967</v>
+        <v>0.02098240379989147</v>
       </c>
       <c r="D159" t="n">
-        <v>0.02409498386085034</v>
+        <v>0.02773109450936317</v>
       </c>
       <c r="E159" t="n">
         <v>0.0005</v>
@@ -3146,13 +3146,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>18.04906379999011</v>
+        <v>9.166206800000509</v>
       </c>
       <c r="C160" t="n">
-        <v>0.02232552762329578</v>
+        <v>0.02415396666526794</v>
       </c>
       <c r="D160" t="n">
-        <v>0.02262749001383781</v>
+        <v>0.02480853110551834</v>
       </c>
       <c r="E160" t="n">
         <v>0.0005</v>
@@ -3163,13 +3163,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>18.00178169998981</v>
+        <v>9.185463200003142</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0209686823040247</v>
+        <v>0.02201844951510429</v>
       </c>
       <c r="D161" t="n">
-        <v>0.03597915470600128</v>
+        <v>0.03759411603212356</v>
       </c>
       <c r="E161" t="n">
         <v>0.0005</v>
@@ -3180,13 +3180,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>18.06980810000096</v>
+        <v>9.280999999988126</v>
       </c>
       <c r="C162" t="n">
-        <v>0.02657103550434112</v>
+        <v>0.02610951249301434</v>
       </c>
       <c r="D162" t="n">
-        <v>0.02633473619818687</v>
+        <v>0.03144948989152908</v>
       </c>
       <c r="E162" t="n">
         <v>0.0005</v>
@@ -3197,13 +3197,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>17.90328140000929</v>
+        <v>9.236200599989388</v>
       </c>
       <c r="C163" t="n">
-        <v>0.02140979780256748</v>
+        <v>0.02453055638074875</v>
       </c>
       <c r="D163" t="n">
-        <v>0.02423329673707485</v>
+        <v>0.02382774010300636</v>
       </c>
       <c r="E163" t="n">
         <v>0.0005</v>
@@ -3214,13 +3214,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>18.00590679999732</v>
+        <v>9.144154699984938</v>
       </c>
       <c r="C164" t="n">
-        <v>0.01950258898735046</v>
+        <v>0.02251039171218872</v>
       </c>
       <c r="D164" t="n">
-        <v>0.02015975475311279</v>
+        <v>0.02218065835535526</v>
       </c>
       <c r="E164" t="n">
         <v>0.0005</v>
@@ -3231,13 +3231,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>17.86696210000082</v>
+        <v>9.283454299991718</v>
       </c>
       <c r="C165" t="n">
-        <v>0.02017915132641792</v>
+        <v>0.01987507359683514</v>
       </c>
       <c r="D165" t="n">
-        <v>0.02470402598381043</v>
+        <v>0.02325557500123978</v>
       </c>
       <c r="E165" t="n">
         <v>0.0005</v>
@@ -3248,13 +3248,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>17.8775622999965</v>
+        <v>9.473210199997993</v>
       </c>
       <c r="C166" t="n">
-        <v>0.02024094232916832</v>
+        <v>0.02039426659047604</v>
       </c>
       <c r="D166" t="n">
-        <v>0.02366306282579899</v>
+        <v>0.02306551665067673</v>
       </c>
       <c r="E166" t="n">
         <v>0.0005</v>
@@ -3265,13 +3265,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>17.96173100000306</v>
+        <v>9.50564079999458</v>
       </c>
       <c r="C167" t="n">
-        <v>0.02021130827069283</v>
+        <v>0.01987276484072208</v>
       </c>
       <c r="D167" t="n">
-        <v>0.02349729061126709</v>
+        <v>0.02352170154452324</v>
       </c>
       <c r="E167" t="n">
         <v>0.0005</v>
@@ -3282,13 +3282,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>17.9871426000027</v>
+        <v>9.702172699995572</v>
       </c>
       <c r="C168" t="n">
-        <v>0.01984872716665268</v>
+        <v>0.01969759838283062</v>
       </c>
       <c r="D168" t="n">
-        <v>0.02140057966113091</v>
+        <v>0.0208399598300457</v>
       </c>
       <c r="E168" t="n">
         <v>0.0005</v>
@@ -3299,13 +3299,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>17.88944120000815</v>
+        <v>9.453628799994476</v>
       </c>
       <c r="C169" t="n">
-        <v>0.01954787763953209</v>
+        <v>0.01912317664921284</v>
       </c>
       <c r="D169" t="n">
-        <v>0.02060130015015602</v>
+        <v>0.02045776657760143</v>
       </c>
       <c r="E169" t="n">
         <v>0.0005</v>
@@ -3316,13 +3316,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>18.05342110000493</v>
+        <v>9.258389099995838</v>
       </c>
       <c r="C170" t="n">
-        <v>0.02058894968032837</v>
+        <v>0.01957410857081413</v>
       </c>
       <c r="D170" t="n">
-        <v>0.03072170838713646</v>
+        <v>0.02061084389686585</v>
       </c>
       <c r="E170" t="n">
         <v>0.0005</v>
@@ -3333,13 +3333,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>18.0455343999929</v>
+        <v>9.42488870001398</v>
       </c>
       <c r="C171" t="n">
-        <v>0.02329840733110905</v>
+        <v>0.02140705680847168</v>
       </c>
       <c r="D171" t="n">
-        <v>0.02195991732180119</v>
+        <v>0.02320787370204926</v>
       </c>
       <c r="E171" t="n">
         <v>0.0005</v>
@@ -3350,13 +3350,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>17.97846050000226</v>
+        <v>9.124999799998477</v>
       </c>
       <c r="C172" t="n">
-        <v>0.01934799636900425</v>
+        <v>0.02055019307136536</v>
       </c>
       <c r="D172" t="n">
-        <v>0.02113820761442185</v>
+        <v>0.0219797220826149</v>
       </c>
       <c r="E172" t="n">
         <v>0.0005</v>
@@ -3367,13 +3367,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>18.32617050000408</v>
+        <v>9.301287299982505</v>
       </c>
       <c r="C173" t="n">
-        <v>0.02014090502262116</v>
+        <v>0.02043182748556137</v>
       </c>
       <c r="D173" t="n">
-        <v>0.02020668409764767</v>
+        <v>0.02261153697967529</v>
       </c>
       <c r="E173" t="n">
         <v>0.0005</v>
@@ -3384,13 +3384,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>18.27758870000253</v>
+        <v>9.196091099991463</v>
       </c>
       <c r="C174" t="n">
-        <v>0.01889853863418102</v>
+        <v>0.02037724176049233</v>
       </c>
       <c r="D174" t="n">
-        <v>0.02170972466468811</v>
+        <v>0.01968968346714974</v>
       </c>
       <c r="E174" t="n">
         <v>0.0005</v>
@@ -3401,13 +3401,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>18.26073529999121</v>
+        <v>9.218838899978437</v>
       </c>
       <c r="C175" t="n">
-        <v>0.01857162946462631</v>
+        <v>0.01881044369935989</v>
       </c>
       <c r="D175" t="n">
-        <v>0.01991880156099796</v>
+        <v>0.01985880643129349</v>
       </c>
       <c r="E175" t="n">
         <v>0.0005</v>
@@ -3418,13 +3418,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>18.90118539999821</v>
+        <v>9.246940600016387</v>
       </c>
       <c r="C176" t="n">
-        <v>0.01894026869535446</v>
+        <v>0.018731001034379</v>
       </c>
       <c r="D176" t="n">
-        <v>0.03102911740541458</v>
+        <v>0.02949492156505585</v>
       </c>
       <c r="E176" t="n">
         <v>0.0005</v>
@@ -3435,13 +3435,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>18.05273809999926</v>
+        <v>9.185941900010221</v>
       </c>
       <c r="C177" t="n">
-        <v>0.02088798353075981</v>
+        <v>0.02040160417556763</v>
       </c>
       <c r="D177" t="n">
-        <v>0.02066453278064728</v>
+        <v>0.0214487262070179</v>
       </c>
       <c r="E177" t="n">
         <v>0.0005</v>
@@ -3452,13 +3452,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>18.17199729999993</v>
+        <v>9.3477260999789</v>
       </c>
       <c r="C178" t="n">
-        <v>0.01904759372770786</v>
+        <v>0.01946487213671207</v>
       </c>
       <c r="D178" t="n">
-        <v>0.02145083837211132</v>
+        <v>0.0289058829843998</v>
       </c>
       <c r="E178" t="n">
         <v>0.0005</v>
@@ -3469,13 +3469,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>18.08256470000197</v>
+        <v>9.136033399990993</v>
       </c>
       <c r="C179" t="n">
-        <v>0.01883399580419064</v>
+        <v>0.02084052979946137</v>
       </c>
       <c r="D179" t="n">
-        <v>0.02020065009593964</v>
+        <v>0.02286360822618008</v>
       </c>
       <c r="E179" t="n">
         <v>0.0005</v>
@@ -3486,13 +3486,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>18.06879260001006</v>
+        <v>9.192770699999528</v>
       </c>
       <c r="C180" t="n">
-        <v>0.01884585548937321</v>
+        <v>0.01888763938844204</v>
       </c>
       <c r="D180" t="n">
-        <v>0.02098972372710705</v>
+        <v>0.01900970950722694</v>
       </c>
       <c r="E180" t="n">
         <v>0.0005</v>
@@ -3503,13 +3503,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>18.17030109999178</v>
+        <v>9.180816800013417</v>
       </c>
       <c r="C181" t="n">
-        <v>0.02101513339579105</v>
+        <v>0.02046126800775528</v>
       </c>
       <c r="D181" t="n">
-        <v>0.02065082989633083</v>
+        <v>0.02213346347212792</v>
       </c>
       <c r="E181" t="n">
         <v>0.0005</v>
@@ -3520,13 +3520,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>18.06526719999965</v>
+        <v>9.280160100024659</v>
       </c>
       <c r="C182" t="n">
-        <v>0.01877801258862019</v>
+        <v>0.01911215525865555</v>
       </c>
       <c r="D182" t="n">
-        <v>0.03211154118180275</v>
+        <v>0.03437900722026825</v>
       </c>
       <c r="E182" t="n">
         <v>0.0005</v>
@@ -3537,13 +3537,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>18.06985539999732</v>
+        <v>9.158571600011783</v>
       </c>
       <c r="C183" t="n">
-        <v>0.02281221605837345</v>
+        <v>0.02294970899820328</v>
       </c>
       <c r="D183" t="n">
-        <v>0.01899377755820751</v>
+        <v>0.02037138432264328</v>
       </c>
       <c r="E183" t="n">
         <v>0.0005</v>
@@ -3554,13 +3554,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>17.92746010000701</v>
+        <v>9.376762400002917</v>
       </c>
       <c r="C184" t="n">
-        <v>0.0192179454267025</v>
+        <v>0.01824080075323582</v>
       </c>
       <c r="D184" t="n">
-        <v>0.02285609245300293</v>
+        <v>0.02905629143118858</v>
       </c>
       <c r="E184" t="n">
         <v>0.0005</v>
@@ -3571,13 +3571,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>18.10596799998893</v>
+        <v>9.266438299993752</v>
       </c>
       <c r="C185" t="n">
-        <v>0.01993595811724663</v>
+        <v>0.02041992311179638</v>
       </c>
       <c r="D185" t="n">
-        <v>0.01881932400166988</v>
+        <v>0.02414781533181667</v>
       </c>
       <c r="E185" t="n">
         <v>0.0005</v>
@@ -3588,13 +3588,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>17.86272160000226</v>
+        <v>9.215387799980817</v>
       </c>
       <c r="C186" t="n">
-        <v>0.01803093984723091</v>
+        <v>0.01869038999080658</v>
       </c>
       <c r="D186" t="n">
-        <v>0.02065434612333775</v>
+        <v>0.02052900567650795</v>
       </c>
       <c r="E186" t="n">
         <v>0.0005</v>
@@ -3605,13 +3605,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>18.48067420000734</v>
+        <v>9.145881899981759</v>
       </c>
       <c r="C187" t="n">
-        <v>0.01727498176693916</v>
+        <v>0.01747777370363474</v>
       </c>
       <c r="D187" t="n">
-        <v>0.01906195297837257</v>
+        <v>0.02120595365762711</v>
       </c>
       <c r="E187" t="n">
         <v>0.0005</v>
@@ -3622,13 +3622,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>18.00741900000139</v>
+        <v>9.178489000012632</v>
       </c>
       <c r="C188" t="n">
-        <v>0.01739711339771748</v>
+        <v>0.0175328970849514</v>
       </c>
       <c r="D188" t="n">
-        <v>0.01842916093766689</v>
+        <v>0.01996828600764275</v>
       </c>
       <c r="E188" t="n">
         <v>0.0005</v>
@@ -3639,13 +3639,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>18.14261560000887</v>
+        <v>9.178466299985303</v>
       </c>
       <c r="C189" t="n">
-        <v>0.01958870814740658</v>
+        <v>0.01800037858635187</v>
       </c>
       <c r="D189" t="n">
-        <v>0.03103788554668426</v>
+        <v>0.0212755511701107</v>
       </c>
       <c r="E189" t="n">
         <v>0.0005</v>
@@ -3656,13 +3656,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>18.11074150000059</v>
+        <v>9.084522599994671</v>
       </c>
       <c r="C190" t="n">
-        <v>0.02483092658221722</v>
+        <v>0.01798641806840897</v>
       </c>
       <c r="D190" t="n">
-        <v>0.01879682898521423</v>
+        <v>0.02451339527964592</v>
       </c>
       <c r="E190" t="n">
         <v>0.0005</v>
@@ -3673,13 +3673,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>17.90526939999836</v>
+        <v>9.197468200000003</v>
       </c>
       <c r="C191" t="n">
-        <v>0.01839380390197039</v>
+        <v>0.01922621726989746</v>
       </c>
       <c r="D191" t="n">
-        <v>0.01820391722023487</v>
+        <v>0.02038149908185005</v>
       </c>
       <c r="E191" t="n">
         <v>0.0005</v>
@@ -3690,13 +3690,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>18.1176170000108</v>
+        <v>9.176172800012864</v>
       </c>
       <c r="C192" t="n">
-        <v>0.01779404957592487</v>
+        <v>0.01851348532736301</v>
       </c>
       <c r="D192" t="n">
-        <v>0.01905765675008297</v>
+        <v>0.01862231701612473</v>
       </c>
       <c r="E192" t="n">
         <v>0.0005</v>
@@ -3707,13 +3707,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>18.17774879999342</v>
+        <v>9.062441999994917</v>
       </c>
       <c r="C193" t="n">
-        <v>0.01710645067691803</v>
+        <v>0.01707511553168297</v>
       </c>
       <c r="D193" t="n">
-        <v>0.0188429345190525</v>
+        <v>0.01808954060077667</v>
       </c>
       <c r="E193" t="n">
         <v>0.0005</v>
@@ -3724,13 +3724,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>18.09606300000451</v>
+        <v>9.223130400001537</v>
       </c>
       <c r="C194" t="n">
-        <v>0.01837571002542972</v>
+        <v>0.01833435893058777</v>
       </c>
       <c r="D194" t="n">
-        <v>0.0183793493360281</v>
+        <v>0.01840595573186874</v>
       </c>
       <c r="E194" t="n">
         <v>0.0005</v>
@@ -3741,13 +3741,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>18.00128119999135</v>
+        <v>9.115728300006595</v>
       </c>
       <c r="C195" t="n">
-        <v>0.01986602199822664</v>
+        <v>0.0202197672277689</v>
       </c>
       <c r="D195" t="n">
-        <v>0.01875787764787674</v>
+        <v>0.02354231372475624</v>
       </c>
       <c r="E195" t="n">
         <v>0.0005</v>
@@ -3758,13 +3758,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>18.18130219999875</v>
+        <v>9.067321999988053</v>
       </c>
       <c r="C196" t="n">
-        <v>0.01662133753299713</v>
+        <v>0.01694801695644856</v>
       </c>
       <c r="D196" t="n">
-        <v>0.02123567029833794</v>
+        <v>0.02433623872697353</v>
       </c>
       <c r="E196" t="n">
         <v>0.0005</v>
@@ -3775,13 +3775,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>17.80876739999803</v>
+        <v>9.182184599980246</v>
       </c>
       <c r="C197" t="n">
-        <v>0.01734033697098494</v>
+        <v>0.01806588014960289</v>
       </c>
       <c r="D197" t="n">
-        <v>0.01845306023955345</v>
+        <v>0.02182555839419365</v>
       </c>
       <c r="E197" t="n">
         <v>0.0005</v>
@@ -3792,13 +3792,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>18.13774209999247</v>
+        <v>9.243279600021197</v>
       </c>
       <c r="C198" t="n">
-        <v>0.01817557483911514</v>
+        <v>0.01831432966887951</v>
       </c>
       <c r="D198" t="n">
-        <v>0.02593606047332287</v>
+        <v>0.02378633871674538</v>
       </c>
       <c r="E198" t="n">
         <v>0.0005</v>
@@ -3809,13 +3809,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>18.08156980000786</v>
+        <v>9.148030099982861</v>
       </c>
       <c r="C199" t="n">
-        <v>0.01896918405592441</v>
+        <v>0.01912167529761791</v>
       </c>
       <c r="D199" t="n">
-        <v>0.02116254046559334</v>
+        <v>0.01775649718940258</v>
       </c>
       <c r="E199" t="n">
         <v>0.0005</v>
@@ -3826,13 +3826,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>18.03239069999836</v>
+        <v>9.143242699996335</v>
       </c>
       <c r="C200" t="n">
-        <v>0.0176340087801218</v>
+        <v>0.01717779466509819</v>
       </c>
       <c r="D200" t="n">
-        <v>0.01769038297235966</v>
+        <v>0.0177959106862545</v>
       </c>
       <c r="E200" t="n">
         <v>0.0005</v>
@@ -3843,13 +3843,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>18.04110419999051</v>
+        <v>9.139943000016501</v>
       </c>
       <c r="C201" t="n">
-        <v>0.01675352169573307</v>
+        <v>0.01679693491756916</v>
       </c>
       <c r="D201" t="n">
-        <v>0.02592352636158466</v>
+        <v>0.0265032646805048</v>
       </c>
       <c r="E201" t="n">
         <v>0.0005</v>
@@ -3860,13 +3860,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="n">
-        <v>18.23812339999131</v>
+        <v>9.169531599996844</v>
       </c>
       <c r="C202" t="n">
-        <v>0.01736776430904865</v>
+        <v>0.01764953096956015</v>
       </c>
       <c r="D202" t="n">
-        <v>0.0181686345487833</v>
+        <v>0.01886085882782936</v>
       </c>
       <c r="E202" t="n">
         <v>0.00025</v>
@@ -3877,13 +3877,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>18.44941130001098</v>
+        <v>9.258349000010639</v>
       </c>
       <c r="C203" t="n">
-        <v>0.01554248587042093</v>
+        <v>0.01564643936604261</v>
       </c>
       <c r="D203" t="n">
-        <v>0.01625920873135328</v>
+        <v>0.01619654901325703</v>
       </c>
       <c r="E203" t="n">
         <v>0.00025</v>
@@ -3894,13 +3894,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>17.98219939999399</v>
+        <v>9.086010099999839</v>
       </c>
       <c r="C204" t="n">
-        <v>0.01557310862839222</v>
+        <v>0.01550620222091675</v>
       </c>
       <c r="D204" t="n">
-        <v>0.01860878810286522</v>
+        <v>0.01827034167945385</v>
       </c>
       <c r="E204" t="n">
         <v>0.00025</v>
@@ -3911,13 +3911,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>18.04768730000069</v>
+        <v>9.174133399996208</v>
       </c>
       <c r="C205" t="n">
-        <v>0.01552067323774099</v>
+        <v>0.01546244765073061</v>
       </c>
       <c r="D205" t="n">
-        <v>0.01622625213116407</v>
+        <v>0.01620062664151192</v>
       </c>
       <c r="E205" t="n">
         <v>0.00025</v>
@@ -3928,13 +3928,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>18.22460500001034</v>
+        <v>9.213451200019335</v>
       </c>
       <c r="C206" t="n">
-        <v>0.01531290871649981</v>
+        <v>0.0152730066627264</v>
       </c>
       <c r="D206" t="n">
-        <v>0.01691713079810142</v>
+        <v>0.01699776545166969</v>
       </c>
       <c r="E206" t="n">
         <v>0.00025</v>
@@ -3945,13 +3945,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>18.62497990000702</v>
+        <v>9.195752899977379</v>
       </c>
       <c r="C207" t="n">
-        <v>0.01506536570191383</v>
+        <v>0.01508382353186607</v>
       </c>
       <c r="D207" t="n">
-        <v>0.01807150036096573</v>
+        <v>0.01792190417647362</v>
       </c>
       <c r="E207" t="n">
         <v>0.00025</v>
@@ -3962,13 +3962,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>19.69292249999125</v>
+        <v>9.13442909999867</v>
       </c>
       <c r="C208" t="n">
-        <v>0.01622020764648914</v>
+        <v>0.01616490319371224</v>
       </c>
       <c r="D208" t="n">
-        <v>0.0188730376213789</v>
+        <v>0.01862099878489971</v>
       </c>
       <c r="E208" t="n">
         <v>0.00025</v>
@@ -3979,13 +3979,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>18.94542109999747</v>
+        <v>9.233704399986891</v>
       </c>
       <c r="C209" t="n">
-        <v>0.01541124427318573</v>
+        <v>0.01538795379549265</v>
       </c>
       <c r="D209" t="n">
-        <v>0.01659229315817356</v>
+        <v>0.01642658423632383</v>
       </c>
       <c r="E209" t="n">
         <v>0.00025</v>
@@ -3996,13 +3996,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>18.74597009998979</v>
+        <v>9.198289599997224</v>
       </c>
       <c r="C210" t="n">
-        <v>0.01493304567039013</v>
+        <v>0.01494084504246712</v>
       </c>
       <c r="D210" t="n">
-        <v>0.01591114290058613</v>
+        <v>0.01599066343158484</v>
       </c>
       <c r="E210" t="n">
         <v>0.00025</v>
@@ -4013,13 +4013,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>17.98988850000023</v>
+        <v>9.085864799999399</v>
       </c>
       <c r="C211" t="n">
-        <v>0.01525478473305702</v>
+        <v>0.01521409976482391</v>
       </c>
       <c r="D211" t="n">
-        <v>0.01703085042536259</v>
+        <v>0.0171446567773819</v>
       </c>
       <c r="E211" t="n">
         <v>0.00025</v>
@@ -4030,13 +4030,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>18.08450309999171</v>
+        <v>9.301787800010061</v>
       </c>
       <c r="C212" t="n">
-        <v>0.01543821589648724</v>
+        <v>0.01537558464705944</v>
       </c>
       <c r="D212" t="n">
-        <v>0.01702246829867363</v>
+        <v>0.01670802168548107</v>
       </c>
       <c r="E212" t="n">
         <v>0.00025</v>
@@ -4047,13 +4047,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>17.98573630000465</v>
+        <v>9.089725500001805</v>
       </c>
       <c r="C213" t="n">
-        <v>0.01514284956455231</v>
+        <v>0.01510673855245113</v>
       </c>
       <c r="D213" t="n">
-        <v>0.01557402454316616</v>
+        <v>0.01553946893662214</v>
       </c>
       <c r="E213" t="n">
         <v>0.00025</v>
@@ -4064,13 +4064,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="n">
-        <v>18.05082340000081</v>
+        <v>9.195295600016834</v>
       </c>
       <c r="C214" t="n">
-        <v>0.01468409439176321</v>
+        <v>0.0147478544190526</v>
       </c>
       <c r="D214" t="n">
-        <v>0.01547185227274895</v>
+        <v>0.01557618603110313</v>
       </c>
       <c r="E214" t="n">
         <v>0.00025</v>
@@ -4081,13 +4081,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="n">
-        <v>17.93594209999719</v>
+        <v>9.137474099989049</v>
       </c>
       <c r="C215" t="n">
-        <v>0.0147365685030818</v>
+        <v>0.01473849117010832</v>
       </c>
       <c r="D215" t="n">
-        <v>0.01654454261064529</v>
+        <v>0.01659421756863594</v>
       </c>
       <c r="E215" t="n">
         <v>0.00025</v>
@@ -4098,13 +4098,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>18.43943729999592</v>
+        <v>9.133862999995472</v>
       </c>
       <c r="C216" t="n">
-        <v>0.01480111192166805</v>
+        <v>0.01483707356452942</v>
       </c>
       <c r="D216" t="n">
-        <v>0.01542668901383877</v>
+        <v>0.015466378480196</v>
       </c>
       <c r="E216" t="n">
         <v>0.00025</v>
@@ -4115,13 +4115,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>17.97112149999884</v>
+        <v>9.197924499982037</v>
       </c>
       <c r="C217" t="n">
-        <v>0.01462715461850166</v>
+        <v>0.01465603494644165</v>
       </c>
       <c r="D217" t="n">
-        <v>0.01840857401490211</v>
+        <v>0.01849762633442879</v>
       </c>
       <c r="E217" t="n">
         <v>0.00025</v>
@@ -4132,13 +4132,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="n">
-        <v>17.92320710000058</v>
+        <v>9.296782999997959</v>
       </c>
       <c r="C218" t="n">
-        <v>0.01506247393786907</v>
+        <v>0.01507620514929295</v>
       </c>
       <c r="D218" t="n">
-        <v>0.01558636572211981</v>
+        <v>0.01563503574579954</v>
       </c>
       <c r="E218" t="n">
         <v>0.00025</v>
@@ -4149,13 +4149,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="n">
-        <v>17.84626140000182</v>
+        <v>9.286470099992584</v>
       </c>
       <c r="C219" t="n">
-        <v>0.01507564750313759</v>
+        <v>0.01512905961275101</v>
       </c>
       <c r="D219" t="n">
-        <v>0.01661900877952576</v>
+        <v>0.01670915484428406</v>
       </c>
       <c r="E219" t="n">
         <v>0.00025</v>
@@ -4166,13 +4166,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>18.05474469999899</v>
+        <v>9.348100100003649</v>
       </c>
       <c r="C220" t="n">
-        <v>0.01470665873587131</v>
+        <v>0.01474221286177635</v>
       </c>
       <c r="D220" t="n">
-        <v>0.01892518229782581</v>
+        <v>0.01830629333853722</v>
       </c>
       <c r="E220" t="n">
         <v>0.00025</v>
@@ -4183,13 +4183,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>18.08970700000646</v>
+        <v>9.112053399992874</v>
       </c>
       <c r="C221" t="n">
-        <v>0.01663859140872955</v>
+        <v>0.01665323905646801</v>
       </c>
       <c r="D221" t="n">
-        <v>0.01685381636023521</v>
+        <v>0.01732550352811814</v>
       </c>
       <c r="E221" t="n">
         <v>0.00025</v>
@@ -4200,13 +4200,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>18.17398629999661</v>
+        <v>9.177554100024281</v>
       </c>
       <c r="C222" t="n">
-        <v>0.01488557682931423</v>
+        <v>0.01485001981258392</v>
       </c>
       <c r="D222" t="n">
-        <v>0.01590484790503979</v>
+        <v>0.01593884699046612</v>
       </c>
       <c r="E222" t="n">
         <v>0.00025</v>
@@ -4217,13 +4217,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>18.03509360000317</v>
+        <v>9.255147499992745</v>
       </c>
       <c r="C223" t="n">
-        <v>0.01464681997895241</v>
+        <v>0.01467524786293507</v>
       </c>
       <c r="D223" t="n">
-        <v>0.01645567208528519</v>
+        <v>0.01644922263920307</v>
       </c>
       <c r="E223" t="n">
         <v>0.00025</v>
@@ -4234,13 +4234,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>17.98013830000127</v>
+        <v>9.289429299999028</v>
       </c>
       <c r="C224" t="n">
-        <v>0.01504700513184071</v>
+        <v>0.01504388987272978</v>
       </c>
       <c r="D224" t="n">
-        <v>0.01693695545196533</v>
+        <v>0.01675283126533032</v>
       </c>
       <c r="E224" t="n">
         <v>0.00025</v>
@@ -4251,13 +4251,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="n">
-        <v>18.32130579999648</v>
+        <v>9.053858900006162</v>
       </c>
       <c r="C225" t="n">
-        <v>0.0148461389914155</v>
+        <v>0.01478019633889198</v>
       </c>
       <c r="D225" t="n">
-        <v>0.01693701826035976</v>
+        <v>0.01696204863488674</v>
       </c>
       <c r="E225" t="n">
         <v>0.00025</v>
@@ -4268,13 +4268,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>18.05358950000664</v>
+        <v>9.195436299982248</v>
       </c>
       <c r="C226" t="n">
-        <v>0.01478242483735085</v>
+        <v>0.0148464597761631</v>
       </c>
       <c r="D226" t="n">
-        <v>0.01977035596966743</v>
+        <v>0.01986056841909885</v>
       </c>
       <c r="E226" t="n">
         <v>0.00025</v>
@@ -4285,13 +4285,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="n">
-        <v>17.82272999999986</v>
+        <v>9.236200800020015</v>
       </c>
       <c r="C227" t="n">
-        <v>0.01570640359073877</v>
+        <v>0.01590215784311294</v>
       </c>
       <c r="D227" t="n">
-        <v>0.0166815546900034</v>
+        <v>0.01706331849098205</v>
       </c>
       <c r="E227" t="n">
         <v>0.00025</v>
@@ -4302,13 +4302,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>18.07631419999234</v>
+        <v>9.130261300015263</v>
       </c>
       <c r="C228" t="n">
-        <v>0.01455279962718487</v>
+        <v>0.01477389369904995</v>
       </c>
       <c r="D228" t="n">
-        <v>0.01886148326098919</v>
+        <v>0.01791549041867256</v>
       </c>
       <c r="E228" t="n">
         <v>0.00025</v>
@@ -4319,13 +4319,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>18.02677450000192</v>
+        <v>9.296814000001177</v>
       </c>
       <c r="C229" t="n">
-        <v>0.01555419767647982</v>
+        <v>0.01579642829298973</v>
       </c>
       <c r="D229" t="n">
-        <v>0.02210842974483967</v>
+        <v>0.0223281666636467</v>
       </c>
       <c r="E229" t="n">
         <v>0.00025</v>
@@ -4336,13 +4336,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>17.99903439999616</v>
+        <v>9.505907099985052</v>
       </c>
       <c r="C230" t="n">
-        <v>0.01731714478135109</v>
+        <v>0.01716423641145229</v>
       </c>
       <c r="D230" t="n">
-        <v>0.02373946435749531</v>
+        <v>0.02275710955262184</v>
       </c>
       <c r="E230" t="n">
         <v>0.00025</v>
@@ -4353,13 +4353,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>18.04916049999883</v>
+        <v>9.302616399974795</v>
       </c>
       <c r="C231" t="n">
-        <v>0.01700186857581138</v>
+        <v>0.01691480901092291</v>
       </c>
       <c r="D231" t="n">
-        <v>0.01716183044016361</v>
+        <v>0.01719786673784256</v>
       </c>
       <c r="E231" t="n">
         <v>0.00025</v>
@@ -4370,13 +4370,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>18.09176630000002</v>
+        <v>9.187100300012389</v>
       </c>
       <c r="C232" t="n">
-        <v>0.01437801937013865</v>
+        <v>0.01437125898897648</v>
       </c>
       <c r="D232" t="n">
-        <v>0.01502363160252571</v>
+        <v>0.0150569611042738</v>
       </c>
       <c r="E232" t="n">
         <v>0.00025</v>
@@ -4387,13 +4387,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>18.20488760000444</v>
+        <v>9.224336199986283</v>
       </c>
       <c r="C233" t="n">
-        <v>0.0140896221101284</v>
+        <v>0.01408634999394417</v>
       </c>
       <c r="D233" t="n">
-        <v>0.02227633759379387</v>
+        <v>0.0219432906806469</v>
       </c>
       <c r="E233" t="n">
         <v>0.00025</v>
@@ -4404,13 +4404,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="n">
-        <v>18.09459999999672</v>
+        <v>9.244556299992837</v>
       </c>
       <c r="C234" t="n">
-        <v>0.01486884079873562</v>
+        <v>0.0146790979206562</v>
       </c>
       <c r="D234" t="n">
-        <v>0.01793534964323044</v>
+        <v>0.01687332171946764</v>
       </c>
       <c r="E234" t="n">
         <v>0.00025</v>
@@ -4421,13 +4421,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>17.98350030000438</v>
+        <v>9.29235420000623</v>
       </c>
       <c r="C235" t="n">
-        <v>0.0152544873803854</v>
+        <v>0.01503043035417795</v>
       </c>
       <c r="D235" t="n">
-        <v>0.0152465620264411</v>
+        <v>0.01559036895632744</v>
       </c>
       <c r="E235" t="n">
         <v>0.00025</v>
@@ -4438,13 +4438,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>18.36198919999879</v>
+        <v>9.282394900015788</v>
       </c>
       <c r="C236" t="n">
-        <v>0.01511979366838932</v>
+        <v>0.01512069298326969</v>
       </c>
       <c r="D236" t="n">
-        <v>0.0194758390635252</v>
+        <v>0.01918206259608269</v>
       </c>
       <c r="E236" t="n">
         <v>0.00025</v>
@@ -4455,13 +4455,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>18.62790400000813</v>
+        <v>9.386521600012202</v>
       </c>
       <c r="C237" t="n">
-        <v>0.01546121083199978</v>
+        <v>0.01523405913263559</v>
       </c>
       <c r="D237" t="n">
-        <v>0.01744537070393562</v>
+        <v>0.01576877452433109</v>
       </c>
       <c r="E237" t="n">
         <v>0.00025</v>
@@ -4472,13 +4472,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="n">
-        <v>17.79042469999695</v>
+        <v>9.193999799987068</v>
       </c>
       <c r="C238" t="n">
-        <v>0.01438824676722288</v>
+        <v>0.01413618530333042</v>
       </c>
       <c r="D238" t="n">
-        <v>0.01599385209381581</v>
+        <v>0.01660877890884876</v>
       </c>
       <c r="E238" t="n">
         <v>0.00025</v>
@@ -4489,13 +4489,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>18.20649380001123</v>
+        <v>9.089614299999084</v>
       </c>
       <c r="C239" t="n">
-        <v>0.01430485001206398</v>
+        <v>0.01449696919322014</v>
       </c>
       <c r="D239" t="n">
-        <v>0.01457058362662792</v>
+        <v>0.01454500906169415</v>
       </c>
       <c r="E239" t="n">
         <v>0.00025</v>
@@ -4506,13 +4506,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>18.01262060001318</v>
+        <v>9.11119399999734</v>
       </c>
       <c r="C240" t="n">
-        <v>0.01391381861269474</v>
+        <v>0.01398103754967451</v>
       </c>
       <c r="D240" t="n">
-        <v>0.01507372729480267</v>
+        <v>0.01497290544211865</v>
       </c>
       <c r="E240" t="n">
         <v>0.00025</v>
@@ -4523,13 +4523,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="n">
-        <v>17.96929599999567</v>
+        <v>9.238314899994293</v>
       </c>
       <c r="C241" t="n">
-        <v>0.01453309178352356</v>
+        <v>0.01448161628842354</v>
       </c>
       <c r="D241" t="n">
-        <v>0.01673612616956234</v>
+        <v>0.01671532616019249</v>
       </c>
       <c r="E241" t="n">
         <v>0.00025</v>
@@ -4540,13 +4540,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>18.16377769999963</v>
+        <v>9.03958050001529</v>
       </c>
       <c r="C242" t="n">
-        <v>0.01425903061032295</v>
+        <v>0.01436164131760597</v>
       </c>
       <c r="D242" t="n">
-        <v>0.02053601138293743</v>
+        <v>0.02058981686830521</v>
       </c>
       <c r="E242" t="n">
         <v>0.00025</v>
@@ -4557,13 +4557,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="n">
-        <v>18.18176469999889</v>
+        <v>9.101356900006067</v>
       </c>
       <c r="C243" t="n">
-        <v>0.01546072386205196</v>
+        <v>0.0155127225369215</v>
       </c>
       <c r="D243" t="n">
-        <v>0.01967263713479042</v>
+        <v>0.01996775321662426</v>
       </c>
       <c r="E243" t="n">
         <v>0.00025</v>
@@ -4574,13 +4574,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="n">
-        <v>17.99663400001009</v>
+        <v>9.144842200010316</v>
       </c>
       <c r="C244" t="n">
-        <v>0.01618484812229872</v>
+        <v>0.01622431465983391</v>
       </c>
       <c r="D244" t="n">
-        <v>0.01629482116550207</v>
+        <v>0.01610196173191071</v>
       </c>
       <c r="E244" t="n">
         <v>0.00025</v>
@@ -4591,13 +4591,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>17.96036179999646</v>
+        <v>9.079950499988627</v>
       </c>
       <c r="C245" t="n">
-        <v>0.01378466834127903</v>
+        <v>0.01378228063881397</v>
       </c>
       <c r="D245" t="n">
-        <v>0.01523652002215386</v>
+        <v>0.01526951115578413</v>
       </c>
       <c r="E245" t="n">
         <v>0.00025</v>
@@ -4608,13 +4608,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>17.99837830000615</v>
+        <v>10.15131909999764</v>
       </c>
       <c r="C246" t="n">
-        <v>0.01401479145139456</v>
+        <v>0.01400267798453569</v>
       </c>
       <c r="D246" t="n">
-        <v>0.01551673732697964</v>
+        <v>0.01544505774974823</v>
       </c>
       <c r="E246" t="n">
         <v>0.00025</v>
@@ -4625,13 +4625,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>17.9861910000036</v>
+        <v>9.704669600003399</v>
       </c>
       <c r="C247" t="n">
-        <v>0.01390922506153583</v>
+        <v>0.01389880087226629</v>
       </c>
       <c r="D247" t="n">
-        <v>0.01469638049602509</v>
+        <v>0.01475186437368393</v>
       </c>
       <c r="E247" t="n">
         <v>0.00025</v>
@@ -4642,13 +4642,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>17.90112700000464</v>
+        <v>9.478306000004523</v>
       </c>
       <c r="C248" t="n">
-        <v>0.01346533743292093</v>
+        <v>0.01351280025392771</v>
       </c>
       <c r="D248" t="n">
-        <v>0.01547875307500362</v>
+        <v>0.01535788647830486</v>
       </c>
       <c r="E248" t="n">
         <v>0.00025</v>
@@ -4659,13 +4659,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>18.06503330000851</v>
+        <v>9.475772400008282</v>
       </c>
       <c r="C249" t="n">
-        <v>0.01471781700849533</v>
+        <v>0.01472702877223492</v>
       </c>
       <c r="D249" t="n">
-        <v>0.01449133716523647</v>
+        <v>0.01451545111835003</v>
       </c>
       <c r="E249" t="n">
         <v>0.00025</v>
@@ -4676,13 +4676,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="n">
-        <v>17.90340389999619</v>
+        <v>9.39768140000524</v>
       </c>
       <c r="C250" t="n">
-        <v>0.01421819251030684</v>
+        <v>0.01427183293551207</v>
       </c>
       <c r="D250" t="n">
-        <v>0.01888518750667572</v>
+        <v>0.01878293797373772</v>
       </c>
       <c r="E250" t="n">
         <v>0.00025</v>
@@ -4693,13 +4693,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="n">
-        <v>18.17348760001187</v>
+        <v>9.526029700005893</v>
       </c>
       <c r="C251" t="n">
-        <v>0.01451383350789547</v>
+        <v>0.0144678070768714</v>
       </c>
       <c r="D251" t="n">
-        <v>0.01600492049008608</v>
+        <v>0.01578213073313236</v>
       </c>
       <c r="E251" t="n">
         <v>0.00025</v>
@@ -4710,13 +4710,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="n">
-        <v>17.93522990000201</v>
+        <v>9.561786100006429</v>
       </c>
       <c r="C252" t="n">
-        <v>0.0135958216637373</v>
+        <v>0.01361434496939182</v>
       </c>
       <c r="D252" t="n">
-        <v>0.01446330793201923</v>
+        <v>0.01441356811672449</v>
       </c>
       <c r="E252" t="n">
         <v>0.00025</v>
@@ -4727,13 +4727,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>18.07520620001014</v>
+        <v>9.411975299997721</v>
       </c>
       <c r="C253" t="n">
-        <v>0.01401603417098522</v>
+        <v>0.01402075722813606</v>
       </c>
       <c r="D253" t="n">
-        <v>0.01506505750119686</v>
+        <v>0.01523110650479794</v>
       </c>
       <c r="E253" t="n">
         <v>0.00025</v>
@@ -4744,13 +4744,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>18.1087089000066</v>
+        <v>9.448801500024274</v>
       </c>
       <c r="C254" t="n">
-        <v>0.01349269012361765</v>
+        <v>0.0135314853489399</v>
       </c>
       <c r="D254" t="n">
-        <v>0.01464248400181532</v>
+        <v>0.01484638992697001</v>
       </c>
       <c r="E254" t="n">
         <v>0.00025</v>
@@ -4761,13 +4761,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>18.03748489999271</v>
+        <v>9.392213600018295</v>
       </c>
       <c r="C255" t="n">
-        <v>0.01346422620862722</v>
+        <v>0.0134638436883688</v>
       </c>
       <c r="D255" t="n">
-        <v>0.01520548138767481</v>
+        <v>0.0153924373164773</v>
       </c>
       <c r="E255" t="n">
         <v>0.00025</v>
@@ -4778,13 +4778,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="n">
-        <v>18.01179770000454</v>
+        <v>9.681290600012289</v>
       </c>
       <c r="C256" t="n">
-        <v>0.01337484762072563</v>
+        <v>0.01343486001342535</v>
       </c>
       <c r="D256" t="n">
-        <v>0.01457854725420475</v>
+        <v>0.01444483555853367</v>
       </c>
       <c r="E256" t="n">
         <v>0.00025</v>
@@ -4795,13 +4795,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="n">
-        <v>18.05273260000104</v>
+        <v>10.01074659998994</v>
       </c>
       <c r="C257" t="n">
-        <v>0.01314443811774254</v>
+        <v>0.01314620764553547</v>
       </c>
       <c r="D257" t="n">
-        <v>0.01412757582962513</v>
+        <v>0.01423391528427601</v>
       </c>
       <c r="E257" t="n">
         <v>0.00025</v>
@@ -4812,13 +4812,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>18.04890589999559</v>
+        <v>10.45077610001317</v>
       </c>
       <c r="C258" t="n">
-        <v>0.01352278252691031</v>
+        <v>0.01355807666480541</v>
       </c>
       <c r="D258" t="n">
-        <v>0.01466552954167128</v>
+        <v>0.01467636242508888</v>
       </c>
       <c r="E258" t="n">
         <v>0.00025</v>
@@ -4829,13 +4829,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="n">
-        <v>18.01213879999705</v>
+        <v>9.881997499993304</v>
       </c>
       <c r="C259" t="n">
-        <v>0.01335520113259554</v>
+        <v>0.0133587961345911</v>
       </c>
       <c r="D259" t="n">
-        <v>0.01519701283425093</v>
+        <v>0.01524345990270376</v>
       </c>
       <c r="E259" t="n">
         <v>0.00025</v>
@@ -4846,13 +4846,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="n">
-        <v>18.2219635000074</v>
+        <v>9.888282600004459</v>
       </c>
       <c r="C260" t="n">
-        <v>0.01326891308277845</v>
+        <v>0.01327421689033508</v>
       </c>
       <c r="D260" t="n">
-        <v>0.01635523162782192</v>
+        <v>0.01616203263401985</v>
       </c>
       <c r="E260" t="n">
         <v>0.00025</v>
@@ -4863,13 +4863,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>18.28267299999425</v>
+        <v>9.730192199989688</v>
       </c>
       <c r="C261" t="n">
-        <v>0.0147483724206686</v>
+        <v>0.01446549160778523</v>
       </c>
       <c r="D261" t="n">
-        <v>0.01989125199615955</v>
+        <v>0.01826973490417004</v>
       </c>
       <c r="E261" t="n">
         <v>0.00025</v>
@@ -4880,13 +4880,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="n">
-        <v>18.0289952000021</v>
+        <v>9.656234199996106</v>
       </c>
       <c r="C262" t="n">
-        <v>0.01437875189632177</v>
+        <v>0.01453229412436485</v>
       </c>
       <c r="D262" t="n">
-        <v>0.01630083732306957</v>
+        <v>0.01599933624267578</v>
       </c>
       <c r="E262" t="n">
         <v>0.00025</v>
@@ -4897,13 +4897,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="n">
-        <v>18.01543450000463</v>
+        <v>9.443579300015699</v>
       </c>
       <c r="C263" t="n">
-        <v>0.01342400189489126</v>
+        <v>0.01337845542281866</v>
       </c>
       <c r="D263" t="n">
-        <v>0.01570468246936798</v>
+        <v>0.01562956310808659</v>
       </c>
       <c r="E263" t="n">
         <v>0.00025</v>
@@ -4914,13 +4914,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="n">
-        <v>17.97032999999647</v>
+        <v>10.28709679999156</v>
       </c>
       <c r="C264" t="n">
-        <v>0.01349967424571514</v>
+        <v>0.01348757903277874</v>
       </c>
       <c r="D264" t="n">
-        <v>0.01466391459107399</v>
+        <v>0.01465750627219677</v>
       </c>
       <c r="E264" t="n">
         <v>0.00025</v>
@@ -4931,13 +4931,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="n">
-        <v>18.06890220000059</v>
+        <v>9.927960900007747</v>
       </c>
       <c r="C265" t="n">
-        <v>0.01351868946105242</v>
+        <v>0.01355063077807426</v>
       </c>
       <c r="D265" t="n">
-        <v>0.01619285177439451</v>
+        <v>0.01630741558969021</v>
       </c>
       <c r="E265" t="n">
         <v>0.00025</v>
@@ -4948,13 +4948,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>18.05976040000678</v>
+        <v>9.884814299992286</v>
       </c>
       <c r="C266" t="n">
-        <v>0.01512965461611748</v>
+        <v>0.01518704879283905</v>
       </c>
       <c r="D266" t="n">
-        <v>0.02080817803740501</v>
+        <v>0.02087482482194901</v>
       </c>
       <c r="E266" t="n">
         <v>0.00025</v>
@@ -4965,13 +4965,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="n">
-        <v>17.87447199999588</v>
+        <v>9.507983999996213</v>
       </c>
       <c r="C267" t="n">
-        <v>0.01478133767098188</v>
+        <v>0.01481346383690834</v>
       </c>
       <c r="D267" t="n">
-        <v>0.01970625184476376</v>
+        <v>0.01975353479385376</v>
       </c>
       <c r="E267" t="n">
         <v>0.00025</v>
@@ -4982,13 +4982,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="n">
-        <v>18.03434880000714</v>
+        <v>10.01582890001009</v>
       </c>
       <c r="C268" t="n">
-        <v>0.01485771442204714</v>
+        <v>0.01483885109424591</v>
       </c>
       <c r="D268" t="n">
-        <v>0.02585520952939987</v>
+        <v>0.02529242798686028</v>
       </c>
       <c r="E268" t="n">
         <v>0.00025</v>
@@ -4999,13 +4999,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>17.96450900001219</v>
+        <v>9.510407499998109</v>
       </c>
       <c r="C269" t="n">
-        <v>0.01515068661421537</v>
+        <v>0.01519846283644438</v>
       </c>
       <c r="D269" t="n">
-        <v>0.01556950569152832</v>
+        <v>0.0155682472884655</v>
       </c>
       <c r="E269" t="n">
         <v>0.00025</v>
@@ -5016,13 +5016,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="n">
-        <v>18.11950760000036</v>
+        <v>9.589306100009708</v>
       </c>
       <c r="C270" t="n">
-        <v>0.01314454082399607</v>
+        <v>0.0131725637614727</v>
       </c>
       <c r="D270" t="n">
-        <v>0.01724031914025545</v>
+        <v>0.0171853743493557</v>
       </c>
       <c r="E270" t="n">
         <v>0.00025</v>
@@ -5033,13 +5033,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="n">
-        <v>18.3832579000009</v>
+        <v>9.520423300011316</v>
       </c>
       <c r="C271" t="n">
-        <v>0.01360174833238125</v>
+        <v>0.01359428417682648</v>
       </c>
       <c r="D271" t="n">
-        <v>0.01630883395671845</v>
+        <v>0.01634762711822987</v>
       </c>
       <c r="E271" t="n">
         <v>0.00025</v>
@@ -5050,13 +5050,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="n">
-        <v>18.15483699999459</v>
+        <v>9.605861599993659</v>
       </c>
       <c r="C272" t="n">
-        <v>0.01342598743736744</v>
+        <v>0.01343146362900734</v>
       </c>
       <c r="D272" t="n">
-        <v>0.01422769747674465</v>
+        <v>0.01415459923446178</v>
       </c>
       <c r="E272" t="n">
         <v>0.00025</v>
@@ -5067,13 +5067,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="n">
-        <v>18.05976030000602</v>
+        <v>9.493260899995221</v>
       </c>
       <c r="C273" t="n">
-        <v>0.01337985455989838</v>
+        <v>0.01341190325468779</v>
       </c>
       <c r="D273" t="n">
-        <v>0.0140641812607646</v>
+        <v>0.01403948411345482</v>
       </c>
       <c r="E273" t="n">
         <v>0.00025</v>
@@ -5084,13 +5084,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="n">
-        <v>18.05378970000311</v>
+        <v>9.595144399994751</v>
       </c>
       <c r="C274" t="n">
-        <v>0.01310989175736904</v>
+        <v>0.01308704748749733</v>
       </c>
       <c r="D274" t="n">
-        <v>0.01481325753033161</v>
+        <v>0.01482688292860985</v>
       </c>
       <c r="E274" t="n">
         <v>0.00025</v>
@@ -5101,13 +5101,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="n">
-        <v>18.10817639999732</v>
+        <v>9.624444200017024</v>
       </c>
       <c r="C275" t="n">
-        <v>0.0132526955679059</v>
+        <v>0.01325992043316364</v>
       </c>
       <c r="D275" t="n">
-        <v>0.01621301654726267</v>
+        <v>0.016099070943892</v>
       </c>
       <c r="E275" t="n">
         <v>0.00025</v>
@@ -5118,13 +5118,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="n">
-        <v>18.23775249999017</v>
+        <v>9.481423599994741</v>
       </c>
       <c r="C276" t="n">
-        <v>0.01320920273661613</v>
+        <v>0.01320765978842974</v>
       </c>
       <c r="D276" t="n">
-        <v>0.01451337069272995</v>
+        <v>0.01456889178603888</v>
       </c>
       <c r="E276" t="n">
         <v>0.00025</v>
@@ -5135,13 +5135,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="n">
-        <v>18.01055730000371</v>
+        <v>10.33881499999552</v>
       </c>
       <c r="C277" t="n">
-        <v>0.01293215383589268</v>
+        <v>0.01297561061382294</v>
       </c>
       <c r="D277" t="n">
-        <v>0.01532158687710762</v>
+        <v>0.0153743739798665</v>
       </c>
       <c r="E277" t="n">
         <v>0.00025</v>
@@ -5152,13 +5152,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>17.98244419999537</v>
+        <v>9.541999100008979</v>
       </c>
       <c r="C278" t="n">
-        <v>0.01499127112329006</v>
+        <v>0.01498717731237412</v>
       </c>
       <c r="D278" t="n">
-        <v>0.02413905017077923</v>
+        <v>0.02441162101924419</v>
       </c>
       <c r="E278" t="n">
         <v>0.00025</v>
@@ -5169,13 +5169,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="n">
-        <v>18.10124990000622</v>
+        <v>9.581841300008819</v>
       </c>
       <c r="C279" t="n">
-        <v>0.01580799563229084</v>
+        <v>0.01584683156013489</v>
       </c>
       <c r="D279" t="n">
-        <v>0.01429969429969788</v>
+        <v>0.01425570517778397</v>
       </c>
       <c r="E279" t="n">
         <v>0.00025</v>
@@ -5186,13 +5186,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="n">
-        <v>17.99480280000716</v>
+        <v>9.727374500012957</v>
       </c>
       <c r="C280" t="n">
-        <v>0.01299123707413673</v>
+        <v>0.01304217716306448</v>
       </c>
       <c r="D280" t="n">
-        <v>0.01431347608566284</v>
+        <v>0.01437382113188505</v>
       </c>
       <c r="E280" t="n">
         <v>0.00025</v>
@@ -5203,13 +5203,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>17.97513819999585</v>
+        <v>9.539230399997905</v>
       </c>
       <c r="C281" t="n">
-        <v>0.01282724298536777</v>
+        <v>0.01282202104479075</v>
       </c>
       <c r="D281" t="n">
-        <v>0.01331701513379812</v>
+        <v>0.01331138368695974</v>
       </c>
       <c r="E281" t="n">
         <v>0.00025</v>
@@ -5220,13 +5220,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>17.97311000000627</v>
+        <v>9.976163000013912</v>
       </c>
       <c r="C282" t="n">
-        <v>0.01264063689112663</v>
+        <v>0.01264540722221136</v>
       </c>
       <c r="D282" t="n">
-        <v>0.01393191650509834</v>
+        <v>0.01392697937786579</v>
       </c>
       <c r="E282" t="n">
         <v>0.00025</v>
@@ -5237,13 +5237,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="n">
-        <v>18.08516370000143</v>
+        <v>9.516237300005741</v>
       </c>
       <c r="C283" t="n">
-        <v>0.01253165151178837</v>
+        <v>0.01252229377627373</v>
       </c>
       <c r="D283" t="n">
-        <v>0.01521508581936359</v>
+        <v>0.01539041947573423</v>
       </c>
       <c r="E283" t="n">
         <v>0.00025</v>
@@ -5254,13 +5254,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="n">
-        <v>18.09675739999511</v>
+        <v>9.905057600000873</v>
       </c>
       <c r="C284" t="n">
-        <v>0.01291254492849112</v>
+        <v>0.01296244063973427</v>
       </c>
       <c r="D284" t="n">
-        <v>0.01422942981123924</v>
+        <v>0.01434339568018913</v>
       </c>
       <c r="E284" t="n">
         <v>0.00025</v>
@@ -5271,13 +5271,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="n">
-        <v>17.8696409999975</v>
+        <v>9.520274900016375</v>
       </c>
       <c r="C285" t="n">
-        <v>0.01295422041416168</v>
+        <v>0.01294667040556669</v>
       </c>
       <c r="D285" t="n">
-        <v>0.01580598387867212</v>
+        <v>0.01559678047895431</v>
       </c>
       <c r="E285" t="n">
         <v>0.00025</v>
@@ -5288,13 +5288,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="n">
-        <v>17.83791420000489</v>
+        <v>9.616359600011492</v>
       </c>
       <c r="C286" t="n">
-        <v>0.01305203612148762</v>
+        <v>0.01302280623465777</v>
       </c>
       <c r="D286" t="n">
-        <v>0.01444572597742081</v>
+        <v>0.01447238560765982</v>
       </c>
       <c r="E286" t="n">
         <v>0.00025</v>
@@ -5305,13 +5305,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>18.83620970000629</v>
+        <v>9.669236599991564</v>
       </c>
       <c r="C287" t="n">
-        <v>0.01295104167610407</v>
+        <v>0.01295368520915508</v>
       </c>
       <c r="D287" t="n">
-        <v>0.01876917079091072</v>
+        <v>0.01864458814263344</v>
       </c>
       <c r="E287" t="n">
         <v>0.00025</v>
@@ -5322,13 +5322,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="n">
-        <v>18.21339679999801</v>
+        <v>9.36842980000074</v>
       </c>
       <c r="C288" t="n">
-        <v>0.01401069694757462</v>
+        <v>0.01402948161959648</v>
       </c>
       <c r="D288" t="n">
-        <v>0.01580354027450085</v>
+        <v>0.0159205711632967</v>
       </c>
       <c r="E288" t="n">
         <v>0.00025</v>
@@ -5339,13 +5339,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="n">
-        <v>18.07582100000582</v>
+        <v>9.710250299976906</v>
       </c>
       <c r="C289" t="n">
-        <v>0.0129859990850091</v>
+        <v>0.01299182011187077</v>
       </c>
       <c r="D289" t="n">
-        <v>0.01565129190683365</v>
+        <v>0.01583783239126205</v>
       </c>
       <c r="E289" t="n">
         <v>0.00025</v>
@@ -5356,13 +5356,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="n">
-        <v>18.31732170000032</v>
+        <v>9.735680799989495</v>
       </c>
       <c r="C290" t="n">
-        <v>0.0128786624148488</v>
+        <v>0.0129125359877944</v>
       </c>
       <c r="D290" t="n">
-        <v>0.01614327467978001</v>
+        <v>0.01635340690612793</v>
       </c>
       <c r="E290" t="n">
         <v>0.00025</v>
@@ -5373,13 +5373,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="n">
-        <v>17.92681440000888</v>
+        <v>9.973217299993848</v>
       </c>
       <c r="C291" t="n">
-        <v>0.0129552253484726</v>
+        <v>0.0130683860257268</v>
       </c>
       <c r="D291" t="n">
-        <v>0.01352655414491892</v>
+        <v>0.01360540844500065</v>
       </c>
       <c r="E291" t="n">
         <v>0.00025</v>
@@ -5390,13 +5390,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="n">
-        <v>17.96960570001102</v>
+        <v>9.565691299998434</v>
       </c>
       <c r="C292" t="n">
-        <v>0.01337515370547772</v>
+        <v>0.01340226310491562</v>
       </c>
       <c r="D292" t="n">
-        <v>0.01601835034787655</v>
+        <v>0.01607606127858162</v>
       </c>
       <c r="E292" t="n">
         <v>0.00025</v>
@@ -5407,13 +5407,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="n">
-        <v>18.19908789999317</v>
+        <v>9.669133499992313</v>
       </c>
       <c r="C293" t="n">
-        <v>0.01290454386174679</v>
+        <v>0.01290822939574719</v>
       </c>
       <c r="D293" t="n">
-        <v>0.01613064106553793</v>
+        <v>0.01604494776576757</v>
       </c>
       <c r="E293" t="n">
         <v>0.00025</v>
@@ -5424,13 +5424,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="n">
-        <v>18.15145279999706</v>
+        <v>9.542345599998953</v>
       </c>
       <c r="C294" t="n">
-        <v>0.01338706056773663</v>
+        <v>0.013359912276268</v>
       </c>
       <c r="D294" t="n">
-        <v>0.01657831110060215</v>
+        <v>0.01656160544604063</v>
       </c>
       <c r="E294" t="n">
         <v>0.00025</v>
@@ -5441,13 +5441,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="n">
-        <v>18.00519550000899</v>
+        <v>9.724183600017568</v>
       </c>
       <c r="C295" t="n">
-        <v>0.01287534283101559</v>
+        <v>0.01294235666841268</v>
       </c>
       <c r="D295" t="n">
-        <v>0.01461687877774239</v>
+        <v>0.0143219081312418</v>
       </c>
       <c r="E295" t="n">
         <v>0.00025</v>
@@ -5458,13 +5458,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="n">
-        <v>17.91446379999979</v>
+        <v>9.672149099991657</v>
       </c>
       <c r="C296" t="n">
-        <v>0.01303263206034899</v>
+        <v>0.01305847384035587</v>
       </c>
       <c r="D296" t="n">
-        <v>0.01337857343256474</v>
+        <v>0.01347341477870941</v>
       </c>
       <c r="E296" t="n">
         <v>0.00025</v>
@@ -5475,13 +5475,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="n">
-        <v>17.84116669998912</v>
+        <v>9.761109499988379</v>
       </c>
       <c r="C297" t="n">
-        <v>0.01238299519568682</v>
+        <v>0.01244313496351242</v>
       </c>
       <c r="D297" t="n">
-        <v>0.01653152577579022</v>
+        <v>0.01649554435163736</v>
       </c>
       <c r="E297" t="n">
         <v>0.00025</v>
@@ -5492,13 +5492,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>17.94053249999706</v>
+        <v>9.496786400006386</v>
       </c>
       <c r="C298" t="n">
-        <v>0.01269928818196058</v>
+        <v>0.01270603777468205</v>
       </c>
       <c r="D298" t="n">
-        <v>0.01510596238076687</v>
+        <v>0.0149058298766613</v>
       </c>
       <c r="E298" t="n">
         <v>0.00025</v>
@@ -5509,13 +5509,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="n">
-        <v>17.98936910000339</v>
+        <v>9.503984400012996</v>
       </c>
       <c r="C299" t="n">
-        <v>0.01295805781334639</v>
+        <v>0.01291780891269445</v>
       </c>
       <c r="D299" t="n">
-        <v>0.01447941191494465</v>
+        <v>0.01450551573187113</v>
       </c>
       <c r="E299" t="n">
         <v>0.00025</v>
@@ -5526,13 +5526,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>18.13109139999142</v>
+        <v>9.702355099987471</v>
       </c>
       <c r="C300" t="n">
-        <v>0.01314158322662115</v>
+        <v>0.0131100145727396</v>
       </c>
       <c r="D300" t="n">
-        <v>0.01734685182571411</v>
+        <v>0.01730868555605412</v>
       </c>
       <c r="E300" t="n">
         <v>0.00025</v>
@@ -5543,13 +5543,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>18.19390329999442</v>
+        <v>9.683096199994907</v>
       </c>
       <c r="C301" t="n">
-        <v>0.01427078033983707</v>
+        <v>0.01430995489656925</v>
       </c>
       <c r="D301" t="n">
-        <v>0.01509082403033972</v>
+        <v>0.01536194957792759</v>
       </c>
       <c r="E301" t="n">
         <v>0.00025</v>
@@ -5560,13 +5560,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
-        <v>18.0405582000094</v>
+        <v>9.841655600001104</v>
       </c>
       <c r="C302" t="n">
-        <v>0.01277768783271313</v>
+        <v>0.01282259328663349</v>
       </c>
       <c r="D302" t="n">
-        <v>0.01443101864308119</v>
+        <v>0.01418615996837616</v>
       </c>
       <c r="E302" t="n">
         <v>0.000125</v>
@@ -5577,13 +5577,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="n">
-        <v>18.12536140000157</v>
+        <v>9.673835199995665</v>
       </c>
       <c r="C303" t="n">
-        <v>0.01207828582823276</v>
+        <v>0.01207232397049665</v>
       </c>
       <c r="D303" t="n">
-        <v>0.01303931079804897</v>
+        <v>0.0130412346124649</v>
       </c>
       <c r="E303" t="n">
         <v>0.000125</v>
@@ -5594,13 +5594,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="n">
-        <v>18.06669219999458</v>
+        <v>9.712781100010034</v>
       </c>
       <c r="C304" t="n">
-        <v>0.0115607513859868</v>
+        <v>0.01156518769264221</v>
       </c>
       <c r="D304" t="n">
-        <v>0.01316374972462654</v>
+        <v>0.01316003549844027</v>
       </c>
       <c r="E304" t="n">
         <v>0.000125</v>
@@ -5611,13 +5611,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="n">
-        <v>18.59342790000665</v>
+        <v>9.679346899996744</v>
       </c>
       <c r="C305" t="n">
-        <v>0.01187144841998816</v>
+        <v>0.01187478587031364</v>
       </c>
       <c r="D305" t="n">
-        <v>0.01388699769973755</v>
+        <v>0.01386145316064358</v>
       </c>
       <c r="E305" t="n">
         <v>0.000125</v>
@@ -5628,13 +5628,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="n">
-        <v>18.10486910000327</v>
+        <v>9.992003199993633</v>
       </c>
       <c r="C306" t="n">
-        <v>0.01216315492987633</v>
+        <v>0.0121676772236824</v>
       </c>
       <c r="D306" t="n">
-        <v>0.01314059242606163</v>
+        <v>0.01312452457845211</v>
       </c>
       <c r="E306" t="n">
         <v>0.000125</v>
@@ -5645,13 +5645,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="n">
-        <v>18.19174270000076</v>
+        <v>10.2687944000063</v>
       </c>
       <c r="C307" t="n">
-        <v>0.01181363172829151</v>
+        <v>0.01181477905064821</v>
       </c>
       <c r="D307" t="n">
-        <v>0.01313893795013428</v>
+        <v>0.01313690651208162</v>
       </c>
       <c r="E307" t="n">
         <v>0.000125</v>
@@ -5662,13 +5662,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="n">
-        <v>18.16999579999538</v>
+        <v>9.761251300020376</v>
       </c>
       <c r="C308" t="n">
-        <v>0.0116757654696703</v>
+        <v>0.01168025878071785</v>
       </c>
       <c r="D308" t="n">
-        <v>0.01313925743103027</v>
+        <v>0.01314495086669922</v>
       </c>
       <c r="E308" t="n">
         <v>0.000125</v>
@@ -5679,13 +5679,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="n">
-        <v>18.10074980001082</v>
+        <v>9.883514599991031</v>
       </c>
       <c r="C309" t="n">
-        <v>0.01183686021715403</v>
+        <v>0.0118470653295517</v>
       </c>
       <c r="D309" t="n">
-        <v>0.01297212012112141</v>
+        <v>0.0129899275302887</v>
       </c>
       <c r="E309" t="n">
         <v>0.000125</v>
@@ -5696,13 +5696,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>18.330686900008</v>
+        <v>9.696254499984207</v>
       </c>
       <c r="C310" t="n">
-        <v>0.01214293222874403</v>
+        <v>0.01216618889570236</v>
       </c>
       <c r="D310" t="n">
-        <v>0.01293608218431473</v>
+        <v>0.01296600997447967</v>
       </c>
       <c r="E310" t="n">
         <v>0.000125</v>
@@ -5713,13 +5713,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="n">
-        <v>18.25274749999517</v>
+        <v>9.660491000016918</v>
       </c>
       <c r="C311" t="n">
-        <v>0.01154951494932175</v>
+        <v>0.01156903003156185</v>
       </c>
       <c r="D311" t="n">
-        <v>0.01246536392718554</v>
+        <v>0.01248075220733881</v>
       </c>
       <c r="E311" t="n">
         <v>0.000125</v>
@@ -5730,13 +5730,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="n">
-        <v>18.39541639998788</v>
+        <v>9.57770170000731</v>
       </c>
       <c r="C312" t="n">
-        <v>0.01157340721786022</v>
+        <v>0.01157374107837677</v>
       </c>
       <c r="D312" t="n">
-        <v>0.01397908188402653</v>
+        <v>0.01397884976118803</v>
       </c>
       <c r="E312" t="n">
         <v>0.000125</v>
@@ -5747,13 +5747,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="n">
-        <v>18.05579450000369</v>
+        <v>9.648514399974374</v>
       </c>
       <c r="C313" t="n">
-        <v>0.01200930348038673</v>
+        <v>0.01201609372347593</v>
       </c>
       <c r="D313" t="n">
-        <v>0.01341892298310995</v>
+        <v>0.01343111883848905</v>
       </c>
       <c r="E313" t="n">
         <v>0.000125</v>
@@ -5764,13 +5764,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>18.0330219999887</v>
+        <v>9.603979499981506</v>
       </c>
       <c r="C314" t="n">
-        <v>0.01188667039573193</v>
+        <v>0.01189415016025305</v>
       </c>
       <c r="D314" t="n">
-        <v>0.01284356947988272</v>
+        <v>0.01283278562128544</v>
       </c>
       <c r="E314" t="n">
         <v>0.000125</v>
@@ -5781,13 +5781,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>18.01491019999958</v>
+        <v>9.611415000021225</v>
       </c>
       <c r="C315" t="n">
-        <v>0.01155768027156591</v>
+        <v>0.0115532211586833</v>
       </c>
       <c r="D315" t="n">
-        <v>0.01297850303351879</v>
+        <v>0.01297430884093046</v>
       </c>
       <c r="E315" t="n">
         <v>0.000125</v>
@@ -5798,13 +5798,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="n">
-        <v>18.29739880000125</v>
+        <v>9.756634999997914</v>
       </c>
       <c r="C316" t="n">
-        <v>0.01146047869324684</v>
+        <v>0.0114654413163662</v>
       </c>
       <c r="D316" t="n">
-        <v>0.01305225551128388</v>
+        <v>0.0130551229044795</v>
       </c>
       <c r="E316" t="n">
         <v>0.000125</v>
@@ -5815,13 +5815,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="n">
-        <v>18.05353360000299</v>
+        <v>9.699585099995602</v>
       </c>
       <c r="C317" t="n">
-        <v>0.01175473549962044</v>
+        <v>0.01176226731389761</v>
       </c>
       <c r="D317" t="n">
-        <v>0.01436527922749519</v>
+        <v>0.01439084973186255</v>
       </c>
       <c r="E317" t="n">
         <v>0.000125</v>
@@ -5832,13 +5832,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="n">
-        <v>17.94454660000338</v>
+        <v>9.406026100012241</v>
       </c>
       <c r="C318" t="n">
-        <v>0.01267636390030384</v>
+        <v>0.01267785814404488</v>
       </c>
       <c r="D318" t="n">
-        <v>0.01270779520273209</v>
+        <v>0.01269716452807188</v>
       </c>
       <c r="E318" t="n">
         <v>0.000125</v>
@@ -5849,13 +5849,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="n">
-        <v>18.2103982000117</v>
+        <v>9.474955100013176</v>
       </c>
       <c r="C319" t="n">
-        <v>0.01177781684696674</v>
+        <v>0.01179187636077404</v>
       </c>
       <c r="D319" t="n">
-        <v>0.01362661276012659</v>
+        <v>0.01355753544718027</v>
       </c>
       <c r="E319" t="n">
         <v>0.000125</v>
@@ -5866,13 +5866,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>17.92324809999263</v>
+        <v>9.565176300005987</v>
       </c>
       <c r="C320" t="n">
-        <v>0.01190296953171492</v>
+        <v>0.01190432713925839</v>
       </c>
       <c r="D320" t="n">
-        <v>0.01277114134281874</v>
+        <v>0.01273024171590805</v>
       </c>
       <c r="E320" t="n">
         <v>0.000125</v>
@@ -5883,13 +5883,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="n">
-        <v>17.86238060001051</v>
+        <v>9.664810600021156</v>
       </c>
       <c r="C321" t="n">
-        <v>0.01167545221745968</v>
+        <v>0.01166265150159597</v>
       </c>
       <c r="D321" t="n">
-        <v>0.01406688801944256</v>
+        <v>0.0141784405708313</v>
       </c>
       <c r="E321" t="n">
         <v>0.000125</v>
@@ -5900,13 +5900,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>18.00290789999417</v>
+        <v>9.566800000000512</v>
       </c>
       <c r="C322" t="n">
-        <v>0.01151761925965548</v>
+        <v>0.01153625291585922</v>
       </c>
       <c r="D322" t="n">
-        <v>0.01290622811764479</v>
+        <v>0.01290615692734718</v>
       </c>
       <c r="E322" t="n">
         <v>0.000125</v>
@@ -5917,13 +5917,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="n">
-        <v>18.10040650000155</v>
+        <v>9.582804200006649</v>
       </c>
       <c r="C323" t="n">
-        <v>0.01167446118593216</v>
+        <v>0.01168688621371984</v>
       </c>
       <c r="D323" t="n">
-        <v>0.01404798932373524</v>
+        <v>0.01404264651238918</v>
       </c>
       <c r="E323" t="n">
         <v>0.000125</v>
@@ -5934,13 +5934,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="n">
-        <v>18.05467169999611</v>
+        <v>9.550214200018672</v>
       </c>
       <c r="C324" t="n">
-        <v>0.01158305432647467</v>
+        <v>0.01159437768906355</v>
       </c>
       <c r="D324" t="n">
-        <v>0.01308012679219246</v>
+        <v>0.01308292649686336</v>
       </c>
       <c r="E324" t="n">
         <v>0.000125</v>
@@ -5951,13 +5951,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="n">
-        <v>18.33505690000311</v>
+        <v>9.650107299996307</v>
       </c>
       <c r="C325" t="n">
-        <v>0.01139416062086821</v>
+        <v>0.01139868596941233</v>
       </c>
       <c r="D325" t="n">
-        <v>0.01274217590689659</v>
+        <v>0.01274067167192697</v>
       </c>
       <c r="E325" t="n">
         <v>0.000125</v>
@@ -5968,13 +5968,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="n">
-        <v>18.44254910000018</v>
+        <v>9.552604099997552</v>
       </c>
       <c r="C326" t="n">
-        <v>0.01158642498403788</v>
+        <v>0.01159935469180346</v>
       </c>
       <c r="D326" t="n">
-        <v>0.0159622298926115</v>
+        <v>0.01598391205072403</v>
       </c>
       <c r="E326" t="n">
         <v>0.000125</v>
@@ -5985,13 +5985,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="n">
-        <v>18.25957059999928</v>
+        <v>9.600240100000519</v>
       </c>
       <c r="C327" t="n">
-        <v>0.01266837479919195</v>
+        <v>0.01269139238446951</v>
       </c>
       <c r="D327" t="n">
-        <v>0.01254917122423649</v>
+        <v>0.01253108125180006</v>
       </c>
       <c r="E327" t="n">
         <v>0.000125</v>
@@ -6002,13 +6002,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="n">
-        <v>18.17921799999021</v>
+        <v>9.557049199996982</v>
       </c>
       <c r="C328" t="n">
-        <v>0.01138284082710743</v>
+        <v>0.01138363009691238</v>
       </c>
       <c r="D328" t="n">
-        <v>0.01242683004587889</v>
+        <v>0.01243443567305803</v>
       </c>
       <c r="E328" t="n">
         <v>0.000125</v>
@@ -6019,13 +6019,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="n">
-        <v>18.17967369999678</v>
+        <v>9.789841299992986</v>
       </c>
       <c r="C329" t="n">
-        <v>0.01142515581846237</v>
+        <v>0.01142852978408337</v>
       </c>
       <c r="D329" t="n">
-        <v>0.01321224737912416</v>
+        <v>0.01321922887116671</v>
       </c>
       <c r="E329" t="n">
         <v>0.000125</v>
@@ -6036,13 +6036,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="n">
-        <v>18.21861180000997</v>
+        <v>9.730743699998129</v>
       </c>
       <c r="C330" t="n">
-        <v>0.01196901109069586</v>
+        <v>0.01197278238087893</v>
       </c>
       <c r="D330" t="n">
-        <v>0.01405960164964199</v>
+        <v>0.01405203692615032</v>
       </c>
       <c r="E330" t="n">
         <v>0.000125</v>
@@ -6053,13 +6053,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="n">
-        <v>18.26737100000901</v>
+        <v>9.651947500009555</v>
       </c>
       <c r="C331" t="n">
-        <v>0.01186337344348431</v>
+        <v>0.01185628502815962</v>
       </c>
       <c r="D331" t="n">
-        <v>0.01356073178350926</v>
+        <v>0.01356403030455113</v>
       </c>
       <c r="E331" t="n">
         <v>0.000125</v>
@@ -6070,13 +6070,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="n">
-        <v>17.99931289999222</v>
+        <v>9.711461200000485</v>
       </c>
       <c r="C332" t="n">
-        <v>0.01135846535861492</v>
+        <v>0.0113653477281332</v>
       </c>
       <c r="D332" t="n">
-        <v>0.01226845290511847</v>
+        <v>0.01226475398987532</v>
       </c>
       <c r="E332" t="n">
         <v>0.000125</v>
@@ -6087,13 +6087,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="n">
-        <v>18.12188120000064</v>
+        <v>10.00560999999288</v>
       </c>
       <c r="C333" t="n">
-        <v>0.01144318622350693</v>
+        <v>0.01145881717652082</v>
       </c>
       <c r="D333" t="n">
-        <v>0.01270923715084791</v>
+        <v>0.01271616138517857</v>
       </c>
       <c r="E333" t="n">
         <v>0.000125</v>
@@ -6104,13 +6104,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="n">
-        <v>18.2881011999998</v>
+        <v>9.899671899998793</v>
       </c>
       <c r="C334" t="n">
-        <v>0.01140227282047272</v>
+        <v>0.01139956571161747</v>
       </c>
       <c r="D334" t="n">
-        <v>0.0148534607514739</v>
+        <v>0.01486848551779985</v>
       </c>
       <c r="E334" t="n">
         <v>0.000125</v>
@@ -6121,13 +6121,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="n">
-        <v>18.07181480000145</v>
+        <v>9.827498200000264</v>
       </c>
       <c r="C335" t="n">
-        <v>0.01183297055959702</v>
+        <v>0.01184588214755058</v>
       </c>
       <c r="D335" t="n">
-        <v>0.01274200670421123</v>
+        <v>0.01270561281591654</v>
       </c>
       <c r="E335" t="n">
         <v>0.000125</v>
@@ -6138,13 +6138,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="n">
-        <v>18.25588950001111</v>
+        <v>9.74943839997286</v>
       </c>
       <c r="C336" t="n">
-        <v>0.01155778929591179</v>
+        <v>0.01155901350080967</v>
       </c>
       <c r="D336" t="n">
-        <v>0.01470712307840586</v>
+        <v>0.01470741808414459</v>
       </c>
       <c r="E336" t="n">
         <v>0.000125</v>
@@ -6155,13 +6155,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="n">
-        <v>18.82693450000079</v>
+        <v>9.854133399989223</v>
       </c>
       <c r="C337" t="n">
-        <v>0.0115227535367012</v>
+        <v>0.01153307789564133</v>
       </c>
       <c r="D337" t="n">
-        <v>0.01263756096363068</v>
+        <v>0.01269030816853046</v>
       </c>
       <c r="E337" t="n">
         <v>0.000125</v>
@@ -6172,13 +6172,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="n">
-        <v>18.26804059999995</v>
+        <v>9.79196060000686</v>
       </c>
       <c r="C338" t="n">
-        <v>0.01128536346554756</v>
+        <v>0.01129704434424639</v>
       </c>
       <c r="D338" t="n">
-        <v>0.01365668557584286</v>
+        <v>0.01365171119570732</v>
       </c>
       <c r="E338" t="n">
         <v>0.000125</v>
@@ -6189,13 +6189,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="n">
-        <v>18.03256039999542</v>
+        <v>9.741351299977396</v>
       </c>
       <c r="C339" t="n">
-        <v>0.01156724245846272</v>
+        <v>0.01157380430400372</v>
       </c>
       <c r="D339" t="n">
-        <v>0.01279857099056244</v>
+        <v>0.01282166317105293</v>
       </c>
       <c r="E339" t="n">
         <v>0.000125</v>
@@ -6206,13 +6206,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="n">
-        <v>18.13162510000984</v>
+        <v>9.705709700006992</v>
       </c>
       <c r="C340" t="n">
-        <v>0.01148767779767513</v>
+        <v>0.01149991180002689</v>
       </c>
       <c r="D340" t="n">
-        <v>0.01282728124409914</v>
+        <v>0.01279652819037437</v>
       </c>
       <c r="E340" t="n">
         <v>0.000125</v>
@@ -6223,13 +6223,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="n">
-        <v>18.28036289999727</v>
+        <v>9.516484599997057</v>
       </c>
       <c r="C341" t="n">
-        <v>0.01144429793953896</v>
+        <v>0.01143717586994171</v>
       </c>
       <c r="D341" t="n">
-        <v>0.0125245026871562</v>
+        <v>0.01253317553550005</v>
       </c>
       <c r="E341" t="n">
         <v>0.000125</v>
@@ -6240,13 +6240,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="n">
-        <v>18.08805859999848</v>
+        <v>9.532835399993928</v>
       </c>
       <c r="C342" t="n">
-        <v>0.01183235996216535</v>
+        <v>0.01184349521994591</v>
       </c>
       <c r="D342" t="n">
-        <v>0.01516027934849262</v>
+        <v>0.01519131477922201</v>
       </c>
       <c r="E342" t="n">
         <v>0.000125</v>
@@ -6257,13 +6257,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="n">
-        <v>18.17146009999851</v>
+        <v>9.474113000003854</v>
       </c>
       <c r="C343" t="n">
-        <v>0.01212621948868036</v>
+        <v>0.01218362429738045</v>
       </c>
       <c r="D343" t="n">
-        <v>0.01491474606096745</v>
+        <v>0.0152687281370163</v>
       </c>
       <c r="E343" t="n">
         <v>0.000125</v>
@@ -6274,13 +6274,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="n">
-        <v>18.49605019998853</v>
+        <v>9.585079100012081</v>
       </c>
       <c r="C344" t="n">
-        <v>0.01156969963014126</v>
+        <v>0.01158294051885605</v>
       </c>
       <c r="D344" t="n">
-        <v>0.01255749300122261</v>
+        <v>0.01254922114312649</v>
       </c>
       <c r="E344" t="n">
         <v>0.000125</v>
@@ -6291,13 +6291,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="n">
-        <v>18.17921110001043</v>
+        <v>9.746424300014041</v>
       </c>
       <c r="C345" t="n">
-        <v>0.01117980168014765</v>
+        <v>0.01118268904089928</v>
       </c>
       <c r="D345" t="n">
-        <v>0.01218069944530725</v>
+        <v>0.01217587057501078</v>
       </c>
       <c r="E345" t="n">
         <v>0.000125</v>
@@ -6308,13 +6308,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="n">
-        <v>18.09558829999878</v>
+        <v>9.551284100016346</v>
       </c>
       <c r="C346" t="n">
-        <v>0.0110797960832715</v>
+        <v>0.01108378403633833</v>
       </c>
       <c r="D346" t="n">
-        <v>0.01248335663229227</v>
+        <v>0.01244128707796335</v>
       </c>
       <c r="E346" t="n">
         <v>0.000125</v>
@@ -6325,13 +6325,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="n">
-        <v>18.31963589999941</v>
+        <v>9.873915000003763</v>
       </c>
       <c r="C347" t="n">
-        <v>0.01149987770617008</v>
+        <v>0.01151418567448854</v>
       </c>
       <c r="D347" t="n">
-        <v>0.01310954682528973</v>
+        <v>0.01313579484820366</v>
       </c>
       <c r="E347" t="n">
         <v>0.000125</v>
@@ -6342,13 +6342,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="n">
-        <v>18.51600220000546</v>
+        <v>9.568605499982368</v>
       </c>
       <c r="C348" t="n">
-        <v>0.0112765985801816</v>
+        <v>0.01129139596968889</v>
       </c>
       <c r="D348" t="n">
-        <v>0.01222568396478891</v>
+        <v>0.01223050378262997</v>
       </c>
       <c r="E348" t="n">
         <v>0.000125</v>
@@ -6359,13 +6359,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="n">
-        <v>18.22822849999648</v>
+        <v>9.877000599983148</v>
       </c>
       <c r="C349" t="n">
-        <v>0.01107505805790424</v>
+        <v>0.01107373800128698</v>
       </c>
       <c r="D349" t="n">
-        <v>0.01327595792710781</v>
+        <v>0.01325390364974737</v>
       </c>
       <c r="E349" t="n">
         <v>0.000125</v>
@@ -6376,13 +6376,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="n">
-        <v>18.14765539999644</v>
+        <v>9.614188299980015</v>
       </c>
       <c r="C350" t="n">
-        <v>0.01201042576134205</v>
+        <v>0.0119978841394186</v>
       </c>
       <c r="D350" t="n">
-        <v>0.01421396609395742</v>
+        <v>0.0142201017588377</v>
       </c>
       <c r="E350" t="n">
         <v>0.000125</v>
@@ -6393,13 +6393,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="n">
-        <v>18.27551009999297</v>
+        <v>9.842067299992777</v>
       </c>
       <c r="C351" t="n">
-        <v>0.01182712735980749</v>
+        <v>0.01183939123898745</v>
       </c>
       <c r="D351" t="n">
-        <v>0.01277393009513617</v>
+        <v>0.01277246773242951</v>
       </c>
       <c r="E351" t="n">
         <v>0.000125</v>
@@ -6410,13 +6410,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="n">
-        <v>18.56123619999562</v>
+        <v>10.12465519999387</v>
       </c>
       <c r="C352" t="n">
-        <v>0.01137905031442642</v>
+        <v>0.01139334890246391</v>
       </c>
       <c r="D352" t="n">
-        <v>0.0124249517545104</v>
+        <v>0.0124547067284584</v>
       </c>
       <c r="E352" t="n">
         <v>0.000125</v>
@@ -6427,13 +6427,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="n">
-        <v>18.11132399999769</v>
+        <v>10.31581450000522</v>
       </c>
       <c r="C353" t="n">
-        <v>0.01138448376953602</v>
+        <v>0.01139061273634434</v>
       </c>
       <c r="D353" t="n">
-        <v>0.0152708512544632</v>
+        <v>0.01528487630188465</v>
       </c>
       <c r="E353" t="n">
         <v>0.000125</v>
@@ -6444,13 +6444,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="n">
-        <v>18.14862809999613</v>
+        <v>9.976692299998831</v>
       </c>
       <c r="C354" t="n">
-        <v>0.01168064136058092</v>
+        <v>0.01168269889056683</v>
       </c>
       <c r="D354" t="n">
-        <v>0.0125259268656373</v>
+        <v>0.01252994611859322</v>
       </c>
       <c r="E354" t="n">
         <v>0.000125</v>
@@ -6461,13 +6461,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="n">
-        <v>18.55469389999053</v>
+        <v>9.94096159999026</v>
       </c>
       <c r="C355" t="n">
-        <v>0.01107859716564417</v>
+        <v>0.01108195276558399</v>
       </c>
       <c r="D355" t="n">
-        <v>0.01366618722677231</v>
+        <v>0.0137231956794858</v>
       </c>
       <c r="E355" t="n">
         <v>0.000125</v>
@@ -6478,13 +6478,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="n">
-        <v>18.26080410000577</v>
+        <v>10.04355099998065</v>
       </c>
       <c r="C356" t="n">
-        <v>0.01119655833393335</v>
+        <v>0.01120607149600983</v>
       </c>
       <c r="D356" t="n">
-        <v>0.01289939183741808</v>
+        <v>0.0129244951158762</v>
       </c>
       <c r="E356" t="n">
         <v>0.000125</v>
@@ -6495,13 +6495,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="n">
-        <v>18.0234644000011</v>
+        <v>9.996425699995598</v>
       </c>
       <c r="C357" t="n">
-        <v>0.01129727786034346</v>
+        <v>0.01130327823758125</v>
       </c>
       <c r="D357" t="n">
-        <v>0.01246918648481369</v>
+        <v>0.0124872376024723</v>
       </c>
       <c r="E357" t="n">
         <v>0.000125</v>
@@ -6512,13 +6512,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="n">
-        <v>18.08602930000052</v>
+        <v>9.777940300002228</v>
       </c>
       <c r="C358" t="n">
-        <v>0.01123870425671339</v>
+        <v>0.01125896970927715</v>
       </c>
       <c r="D358" t="n">
-        <v>0.01258462384343147</v>
+        <v>0.01264103267341852</v>
       </c>
       <c r="E358" t="n">
         <v>0.000125</v>
@@ -6529,13 +6529,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="n">
-        <v>18.6835912999959</v>
+        <v>9.683403999981238</v>
       </c>
       <c r="C359" t="n">
-        <v>0.0110866461917758</v>
+        <v>0.01110618140548468</v>
       </c>
       <c r="D359" t="n">
-        <v>0.01312330849468708</v>
+        <v>0.0131858029589057</v>
       </c>
       <c r="E359" t="n">
         <v>0.000125</v>
@@ -6546,13 +6546,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="n">
-        <v>18.33580749999965</v>
+        <v>9.620999000006123</v>
       </c>
       <c r="C360" t="n">
-        <v>0.01117751349508762</v>
+        <v>0.01119563602656126</v>
       </c>
       <c r="D360" t="n">
-        <v>0.01273404773324728</v>
+        <v>0.01274603385478258</v>
       </c>
       <c r="E360" t="n">
         <v>0.000125</v>
@@ -6563,13 +6563,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="n">
-        <v>18.129697700002</v>
+        <v>9.405207099975087</v>
       </c>
       <c r="C361" t="n">
-        <v>0.0115705591738224</v>
+        <v>0.01157571107149124</v>
       </c>
       <c r="D361" t="n">
-        <v>0.01225770674645901</v>
+        <v>0.01232224747538567</v>
       </c>
       <c r="E361" t="n">
         <v>0.000125</v>
@@ -6580,13 +6580,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="n">
-        <v>18.20567840000149</v>
+        <v>9.593817200016929</v>
       </c>
       <c r="C362" t="n">
-        <v>0.01098739651590586</v>
+        <v>0.01100928755104542</v>
       </c>
       <c r="D362" t="n">
-        <v>0.01289565648883581</v>
+        <v>0.01294690150767565</v>
       </c>
       <c r="E362" t="n">
         <v>0.000125</v>
@@ -6597,13 +6597,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="n">
-        <v>18.27196890000778</v>
+        <v>10.525887900003</v>
       </c>
       <c r="C363" t="n">
-        <v>0.01128098891675472</v>
+        <v>0.01128533551096916</v>
       </c>
       <c r="D363" t="n">
-        <v>0.01341036718338728</v>
+        <v>0.01342919573187828</v>
       </c>
       <c r="E363" t="n">
         <v>0.000125</v>
@@ -6614,13 +6614,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="n">
-        <v>18.24162649999198</v>
+        <v>9.922840500017628</v>
       </c>
       <c r="C364" t="n">
-        <v>0.01101505640894175</v>
+        <v>0.01102204048633575</v>
       </c>
       <c r="D364" t="n">
-        <v>0.01222649563103914</v>
+        <v>0.01220079869031906</v>
       </c>
       <c r="E364" t="n">
         <v>0.000125</v>
@@ -6631,13 +6631,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="n">
-        <v>18.02808679999725</v>
+        <v>9.909284299996216</v>
       </c>
       <c r="C365" t="n">
-        <v>0.01095610481500626</v>
+        <v>0.01097436962276697</v>
       </c>
       <c r="D365" t="n">
-        <v>0.01247705284506083</v>
+        <v>0.01249437473714352</v>
       </c>
       <c r="E365" t="n">
         <v>0.000125</v>
@@ -6648,13 +6648,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="n">
-        <v>18.37144339999941</v>
+        <v>10.08906759999809</v>
       </c>
       <c r="C366" t="n">
-        <v>0.01115485872328281</v>
+        <v>0.01116441098600626</v>
       </c>
       <c r="D366" t="n">
-        <v>0.01592880450189114</v>
+        <v>0.0159207409247756</v>
       </c>
       <c r="E366" t="n">
         <v>0.000125</v>
@@ -6665,13 +6665,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="n">
-        <v>17.92091960000107</v>
+        <v>9.988321500015445</v>
       </c>
       <c r="C367" t="n">
-        <v>0.01184326153993607</v>
+        <v>0.0118477081283927</v>
       </c>
       <c r="D367" t="n">
-        <v>0.01305092439055443</v>
+        <v>0.01310242049396038</v>
       </c>
       <c r="E367" t="n">
         <v>0.000125</v>
@@ -6682,13 +6682,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="n">
-        <v>18.17156790000445</v>
+        <v>9.795576700009406</v>
       </c>
       <c r="C368" t="n">
-        <v>0.01109045001119375</v>
+        <v>0.01109864296764135</v>
       </c>
       <c r="D368" t="n">
-        <v>0.01180037148296833</v>
+        <v>0.01179425939917564</v>
       </c>
       <c r="E368" t="n">
         <v>0.000125</v>
@@ -6699,13 +6699,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="n">
-        <v>18.39058720000321</v>
+        <v>9.803139600000577</v>
       </c>
       <c r="C369" t="n">
-        <v>0.01072917319834232</v>
+        <v>0.01072839950025082</v>
       </c>
       <c r="D369" t="n">
-        <v>0.01374903794378042</v>
+        <v>0.01368827730417252</v>
       </c>
       <c r="E369" t="n">
         <v>0.000125</v>
@@ -6716,13 +6716,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="n">
-        <v>18.46989180000674</v>
+        <v>9.730305500008399</v>
       </c>
       <c r="C370" t="n">
-        <v>0.01099522014707327</v>
+        <v>0.01098759961128235</v>
       </c>
       <c r="D370" t="n">
-        <v>0.01340795334428549</v>
+        <v>0.01336045935750008</v>
       </c>
       <c r="E370" t="n">
         <v>0.000125</v>
@@ -6733,13 +6733,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="n">
-        <v>18.28097760000674</v>
+        <v>9.792364599998109</v>
       </c>
       <c r="C371" t="n">
-        <v>0.01120335961133242</v>
+        <v>0.0112051854133606</v>
       </c>
       <c r="D371" t="n">
-        <v>0.01254672165960074</v>
+        <v>0.01255860634148121</v>
       </c>
       <c r="E371" t="n">
         <v>0.000125</v>
@@ -6750,13 +6750,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="n">
-        <v>18.22222490000422</v>
+        <v>9.682817099994281</v>
       </c>
       <c r="C372" t="n">
-        <v>0.01089851845800877</v>
+        <v>0.01090858582407236</v>
       </c>
       <c r="D372" t="n">
-        <v>0.01359409712255001</v>
+        <v>0.01361076164990663</v>
       </c>
       <c r="E372" t="n">
         <v>0.000125</v>
@@ -6767,13 +6767,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="n">
-        <v>18.17962079998688</v>
+        <v>9.413282299996354</v>
       </c>
       <c r="C373" t="n">
-        <v>0.0110434353351593</v>
+        <v>0.01105272667855024</v>
       </c>
       <c r="D373" t="n">
-        <v>0.01215985499322414</v>
+        <v>0.01215706717222929</v>
       </c>
       <c r="E373" t="n">
         <v>0.000125</v>
@@ -6784,13 +6784,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="n">
-        <v>18.15123629999289</v>
+        <v>9.64068720000796</v>
       </c>
       <c r="C374" t="n">
-        <v>0.01161855821311474</v>
+        <v>0.01161839933693409</v>
       </c>
       <c r="D374" t="n">
-        <v>0.01467333529144526</v>
+        <v>0.01467392303049564</v>
       </c>
       <c r="E374" t="n">
         <v>0.000125</v>
@@ -6801,13 +6801,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="n">
-        <v>18.26517810000223</v>
+        <v>9.850433300016448</v>
       </c>
       <c r="C375" t="n">
-        <v>0.01159565615653992</v>
+        <v>0.01160512055456638</v>
       </c>
       <c r="D375" t="n">
-        <v>0.01638528231531382</v>
+        <v>0.01635875970125198</v>
       </c>
       <c r="E375" t="n">
         <v>0.000125</v>
@@ -6818,13 +6818,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="n">
-        <v>18.2518279000069</v>
+        <v>9.874742999993032</v>
       </c>
       <c r="C376" t="n">
-        <v>0.0120517431050539</v>
+        <v>0.01204232262820005</v>
       </c>
       <c r="D376" t="n">
-        <v>0.01337316159158945</v>
+        <v>0.01337989382445812</v>
       </c>
       <c r="E376" t="n">
         <v>0.000125</v>
@@ -6835,13 +6835,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="n">
-        <v>18.60163720000128</v>
+        <v>9.618519999989076</v>
       </c>
       <c r="C377" t="n">
-        <v>0.01135783034563064</v>
+        <v>0.01137058021873236</v>
       </c>
       <c r="D377" t="n">
-        <v>0.01311600685119629</v>
+        <v>0.01311740599572658</v>
       </c>
       <c r="E377" t="n">
         <v>0.000125</v>
@@ -6852,13 +6852,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="n">
-        <v>18.35351610000362</v>
+        <v>9.837658000004012</v>
       </c>
       <c r="C378" t="n">
-        <v>0.01111282449215651</v>
+        <v>0.01113150790333748</v>
       </c>
       <c r="D378" t="n">
-        <v>0.01238285899162292</v>
+        <v>0.01235552038997412</v>
       </c>
       <c r="E378" t="n">
         <v>0.000125</v>
@@ -6869,13 +6869,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="n">
-        <v>18.27665909999632</v>
+        <v>9.725273699994432</v>
       </c>
       <c r="C379" t="n">
-        <v>0.01133311675488949</v>
+        <v>0.01133962995558977</v>
       </c>
       <c r="D379" t="n">
-        <v>0.01465124733746052</v>
+        <v>0.01475310273468494</v>
       </c>
       <c r="E379" t="n">
         <v>0.000125</v>
@@ -6886,13 +6886,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="n">
-        <v>18.39396649999253</v>
+        <v>9.714279100007843</v>
       </c>
       <c r="C380" t="n">
-        <v>0.01120175584405661</v>
+        <v>0.01122002033144236</v>
       </c>
       <c r="D380" t="n">
-        <v>0.01265544645488262</v>
+        <v>0.01275151181966066</v>
       </c>
       <c r="E380" t="n">
         <v>0.000125</v>
@@ -6903,13 +6903,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>18.59637110000767</v>
+        <v>9.547760899993591</v>
       </c>
       <c r="C381" t="n">
-        <v>0.01090908466279507</v>
+        <v>0.01091602559387684</v>
       </c>
       <c r="D381" t="n">
-        <v>0.0124455364793539</v>
+        <v>0.01250652108341455</v>
       </c>
       <c r="E381" t="n">
         <v>0.000125</v>
@@ -6920,13 +6920,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="n">
-        <v>18.37527370000316</v>
+        <v>9.62612000000081</v>
       </c>
       <c r="C382" t="n">
-        <v>0.01109008226543665</v>
+        <v>0.01109668556600809</v>
       </c>
       <c r="D382" t="n">
-        <v>0.01277562394738197</v>
+        <v>0.01281739473342896</v>
       </c>
       <c r="E382" t="n">
         <v>0.000125</v>
@@ -6937,13 +6937,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="n">
-        <v>18.27395479999541</v>
+        <v>9.570271099975798</v>
       </c>
       <c r="C383" t="n">
-        <v>0.01111121843010187</v>
+        <v>0.01112235845625401</v>
       </c>
       <c r="D383" t="n">
-        <v>0.01223606463521719</v>
+        <v>0.01226022347807884</v>
       </c>
       <c r="E383" t="n">
         <v>0.000125</v>
@@ -6954,13 +6954,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="n">
-        <v>18.3098941000062</v>
+        <v>9.625430299987784</v>
       </c>
       <c r="C384" t="n">
-        <v>0.01077445778250694</v>
+        <v>0.01078492265194654</v>
       </c>
       <c r="D384" t="n">
-        <v>0.01216873656958342</v>
+        <v>0.01217304386198521</v>
       </c>
       <c r="E384" t="n">
         <v>0.000125</v>
@@ -6971,13 +6971,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="n">
-        <v>18.75310040000477</v>
+        <v>9.670138899993617</v>
       </c>
       <c r="C385" t="n">
-        <v>0.01070414935797453</v>
+        <v>0.01070718397200108</v>
       </c>
       <c r="D385" t="n">
-        <v>0.01367723140865564</v>
+        <v>0.01366136450320482</v>
       </c>
       <c r="E385" t="n">
         <v>0.000125</v>
@@ -6988,13 +6988,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="n">
-        <v>18.62187289999565</v>
+        <v>9.942260699986946</v>
       </c>
       <c r="C386" t="n">
-        <v>0.01109868415445089</v>
+        <v>0.01110199532657862</v>
       </c>
       <c r="D386" t="n">
-        <v>0.01175650522112846</v>
+        <v>0.01175382401794195</v>
       </c>
       <c r="E386" t="n">
         <v>0.000125</v>
@@ -7005,13 +7005,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="n">
-        <v>17.95323810000264</v>
+        <v>9.522557899996173</v>
       </c>
       <c r="C387" t="n">
-        <v>0.01088001545518637</v>
+        <v>0.01088757910579443</v>
       </c>
       <c r="D387" t="n">
-        <v>0.01420904789119959</v>
+        <v>0.01421292074024677</v>
       </c>
       <c r="E387" t="n">
         <v>0.000125</v>
@@ -7022,13 +7022,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="n">
-        <v>18.39799329999369</v>
+        <v>10.06922730000224</v>
       </c>
       <c r="C388" t="n">
-        <v>0.01134805491566658</v>
+        <v>0.01135121697932482</v>
       </c>
       <c r="D388" t="n">
-        <v>0.01238399051129818</v>
+        <v>0.01235152699053287</v>
       </c>
       <c r="E388" t="n">
         <v>0.000125</v>
@@ -7039,13 +7039,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="n">
-        <v>18.66594160000386</v>
+        <v>10.19092350002029</v>
       </c>
       <c r="C389" t="n">
-        <v>0.01090007493644953</v>
+        <v>0.01089720023423433</v>
       </c>
       <c r="D389" t="n">
-        <v>0.01180903218686581</v>
+        <v>0.01177657295018435</v>
       </c>
       <c r="E389" t="n">
         <v>0.000125</v>
@@ -7056,13 +7056,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="n">
-        <v>18.07614920000196</v>
+        <v>9.723253100004513</v>
       </c>
       <c r="C390" t="n">
-        <v>0.0107318359464407</v>
+        <v>0.01074111774563789</v>
       </c>
       <c r="D390" t="n">
-        <v>0.0140147627145052</v>
+        <v>0.01410963147878647</v>
       </c>
       <c r="E390" t="n">
         <v>0.000125</v>
@@ -7073,13 +7073,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="n">
-        <v>18.50321270000131</v>
+        <v>9.768736700003501</v>
       </c>
       <c r="C391" t="n">
-        <v>0.01100716319680214</v>
+        <v>0.01104432269185781</v>
       </c>
       <c r="D391" t="n">
-        <v>0.01184140808880329</v>
+        <v>0.01186719942837954</v>
       </c>
       <c r="E391" t="n">
         <v>0.000125</v>
@@ -7090,13 +7090,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="n">
-        <v>18.20806660001108</v>
+        <v>9.814248999988195</v>
       </c>
       <c r="C392" t="n">
-        <v>0.01065452779829502</v>
+        <v>0.01066761765629053</v>
       </c>
       <c r="D392" t="n">
-        <v>0.01222150154411793</v>
+        <v>0.01221544921398163</v>
       </c>
       <c r="E392" t="n">
         <v>0.000125</v>
@@ -7107,13 +7107,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="n">
-        <v>18.03461230000539</v>
+        <v>9.66875360000995</v>
       </c>
       <c r="C393" t="n">
-        <v>0.01075638226419687</v>
+        <v>0.01075901510566473</v>
       </c>
       <c r="D393" t="n">
-        <v>0.01299221407622099</v>
+        <v>0.0129234529286623</v>
       </c>
       <c r="E393" t="n">
         <v>0.000125</v>
@@ -7124,13 +7124,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="n">
-        <v>18.41157020001265</v>
+        <v>9.541258699988248</v>
       </c>
       <c r="C394" t="n">
-        <v>0.01133206721395254</v>
+        <v>0.01131938926130533</v>
       </c>
       <c r="D394" t="n">
-        <v>0.012339753434062</v>
+        <v>0.01231145571917295</v>
       </c>
       <c r="E394" t="n">
         <v>0.000125</v>
@@ -7141,13 +7141,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="n">
-        <v>18.60055039999133</v>
+        <v>9.488526100001764</v>
       </c>
       <c r="C395" t="n">
-        <v>0.01112553339451551</v>
+        <v>0.01112979566305876</v>
       </c>
       <c r="D395" t="n">
-        <v>0.01345529306679964</v>
+        <v>0.01340694591403008</v>
       </c>
       <c r="E395" t="n">
         <v>0.000125</v>
@@ -7158,13 +7158,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="n">
-        <v>18.24998520000372</v>
+        <v>9.944710600015242</v>
       </c>
       <c r="C396" t="n">
-        <v>0.01106794808804989</v>
+        <v>0.01107727884501219</v>
       </c>
       <c r="D396" t="n">
-        <v>0.01298362150788307</v>
+        <v>0.01299630545079708</v>
       </c>
       <c r="E396" t="n">
         <v>0.000125</v>
@@ -7175,13 +7175,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="n">
-        <v>18.31005749999895</v>
+        <v>9.79869029999827</v>
       </c>
       <c r="C397" t="n">
-        <v>0.01130781207978725</v>
+        <v>0.01131137162446976</v>
       </c>
       <c r="D397" t="n">
-        <v>0.01228371020406485</v>
+        <v>0.01234063636511564</v>
       </c>
       <c r="E397" t="n">
         <v>0.000125</v>
@@ -7192,13 +7192,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="n">
-        <v>18.35722890000034</v>
+        <v>9.588290199986659</v>
       </c>
       <c r="C398" t="n">
-        <v>0.01067238560318947</v>
+        <v>0.01068672897666693</v>
       </c>
       <c r="D398" t="n">
-        <v>0.01174906488507986</v>
+        <v>0.0117529484629631</v>
       </c>
       <c r="E398" t="n">
         <v>0.000125</v>
@@ -7209,13 +7209,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="n">
-        <v>18.38259670000116</v>
+        <v>9.696085300005507</v>
       </c>
       <c r="C399" t="n">
-        <v>0.01057172550261021</v>
+        <v>0.01057624265551567</v>
       </c>
       <c r="D399" t="n">
-        <v>0.01181991223245859</v>
+        <v>0.01182468071579933</v>
       </c>
       <c r="E399" t="n">
         <v>0.000125</v>
@@ -7226,13 +7226,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="n">
-        <v>18.83083829999669</v>
+        <v>9.616474500013283</v>
       </c>
       <c r="C400" t="n">
-        <v>0.01151164238899946</v>
+        <v>0.01153359153866768</v>
       </c>
       <c r="D400" t="n">
-        <v>0.01710234984755516</v>
+        <v>0.0169493779540062</v>
       </c>
       <c r="E400" t="n">
         <v>0.000125</v>
@@ -7243,13 +7243,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="n">
-        <v>18.04659600000014</v>
+        <v>9.666874499991536</v>
       </c>
       <c r="C401" t="n">
-        <v>0.01220893558114767</v>
+        <v>0.01213616979122162</v>
       </c>
       <c r="D401" t="n">
-        <v>0.01221739508211613</v>
+        <v>0.0122937099263072</v>
       </c>
       <c r="E401" t="n">
         <v>0.000125</v>
@@ -7260,13 +7260,13 @@
         <v>401</v>
       </c>
       <c r="B402" t="n">
-        <v>18.21251140000822</v>
+        <v>9.698453799996059</v>
       </c>
       <c r="C402" t="n">
-        <v>0.01042003943771124</v>
+        <v>0.01043412865698337</v>
       </c>
       <c r="D402" t="n">
-        <v>0.01156371243298054</v>
+        <v>0.01156172189861536</v>
       </c>
       <c r="E402" t="n">
         <v>6.25e-05</v>
@@ -7277,13 +7277,13 @@
         <v>402</v>
       </c>
       <c r="B403" t="n">
-        <v>18.6503045999998</v>
+        <v>9.552812600013567</v>
       </c>
       <c r="C403" t="n">
-        <v>0.0101951856687665</v>
+        <v>0.01020118903368711</v>
       </c>
       <c r="D403" t="n">
-        <v>0.01205031353980303</v>
+        <v>0.01206331953406334</v>
       </c>
       <c r="E403" t="n">
         <v>6.25e-05</v>
@@ -7294,13 +7294,13 @@
         <v>403</v>
       </c>
       <c r="B404" t="n">
-        <v>18.130393799991</v>
+        <v>9.449053399992408</v>
       </c>
       <c r="C404" t="n">
-        <v>0.01033000679314136</v>
+        <v>0.0103376891836524</v>
       </c>
       <c r="D404" t="n">
-        <v>0.01142592012882233</v>
+        <v>0.0114325213432312</v>
       </c>
       <c r="E404" t="n">
         <v>6.25e-05</v>
@@ -7311,13 +7311,13 @@
         <v>404</v>
       </c>
       <c r="B405" t="n">
-        <v>18.35279980000632</v>
+        <v>9.589393000002019</v>
       </c>
       <c r="C405" t="n">
-        <v>0.01042575991898775</v>
+        <v>0.01043345991522074</v>
       </c>
       <c r="D405" t="n">
-        <v>0.01155600588768721</v>
+        <v>0.01156907811760902</v>
       </c>
       <c r="E405" t="n">
         <v>6.25e-05</v>
@@ -7328,13 +7328,13 @@
         <v>405</v>
       </c>
       <c r="B406" t="n">
-        <v>18.41431910000392</v>
+        <v>10.01592510001501</v>
       </c>
       <c r="C406" t="n">
-        <v>0.01028011881560087</v>
+        <v>0.01028701554238796</v>
       </c>
       <c r="D406" t="n">
-        <v>0.01158669002354145</v>
+        <v>0.01158913876861334</v>
       </c>
       <c r="E406" t="n">
         <v>6.25e-05</v>
@@ -7345,13 +7345,13 @@
         <v>406</v>
       </c>
       <c r="B407" t="n">
-        <v>18.17358960000274</v>
+        <v>10.10054509999463</v>
       </c>
       <c r="C407" t="n">
-        <v>0.01041104992479086</v>
+        <v>0.01041604468971491</v>
       </c>
       <c r="D407" t="n">
-        <v>0.01184609230607748</v>
+        <v>0.01185435753315687</v>
       </c>
       <c r="E407" t="n">
         <v>6.25e-05</v>
@@ -7362,13 +7362,13 @@
         <v>407</v>
       </c>
       <c r="B408" t="n">
-        <v>18.28039269999135</v>
+        <v>9.786213099985616</v>
       </c>
       <c r="C408" t="n">
-        <v>0.0105079180970788</v>
+        <v>0.01051826068758964</v>
       </c>
       <c r="D408" t="n">
-        <v>0.01183494083583355</v>
+        <v>0.01184378888458014</v>
       </c>
       <c r="E408" t="n">
         <v>6.25e-05</v>
@@ -7379,13 +7379,13 @@
         <v>408</v>
       </c>
       <c r="B409" t="n">
-        <v>18.46784060000209</v>
+        <v>9.878421500005061</v>
       </c>
       <c r="C409" t="n">
-        <v>0.01038763628900051</v>
+        <v>0.01039766097813845</v>
       </c>
       <c r="D409" t="n">
-        <v>0.01160948235541582</v>
+        <v>0.01163109634071588</v>
       </c>
       <c r="E409" t="n">
         <v>6.25e-05</v>
@@ -7396,13 +7396,13 @@
         <v>409</v>
       </c>
       <c r="B410" t="n">
-        <v>18.22650409999187</v>
+        <v>9.89868139999453</v>
       </c>
       <c r="C410" t="n">
-        <v>0.0102099639326334</v>
+        <v>0.01021959401667118</v>
       </c>
       <c r="D410" t="n">
-        <v>0.01146542727947235</v>
+        <v>0.01148265805095434</v>
       </c>
       <c r="E410" t="n">
         <v>6.25e-05</v>
@@ -7413,13 +7413,13 @@
         <v>410</v>
       </c>
       <c r="B411" t="n">
-        <v>18.6212658000004</v>
+        <v>9.661906900000758</v>
       </c>
       <c r="C411" t="n">
-        <v>0.01024734093248844</v>
+        <v>0.01025776720046997</v>
       </c>
       <c r="D411" t="n">
-        <v>0.01151905126869678</v>
+        <v>0.01152543567121029</v>
       </c>
       <c r="E411" t="n">
         <v>6.25e-05</v>
@@ -7430,13 +7430,13 @@
         <v>411</v>
       </c>
       <c r="B412" t="n">
-        <v>18.03212040000653</v>
+        <v>9.676605900021968</v>
       </c>
       <c r="C412" t="n">
-        <v>0.01018268427252769</v>
+        <v>0.01018914917111397</v>
       </c>
       <c r="D412" t="n">
-        <v>0.01199308887124062</v>
+        <v>0.01199985913932324</v>
       </c>
       <c r="E412" t="n">
         <v>6.25e-05</v>
@@ -7447,13 +7447,13 @@
         <v>412</v>
       </c>
       <c r="B413" t="n">
-        <v>17.84332680000807</v>
+        <v>9.991588800010504</v>
       </c>
       <c r="C413" t="n">
-        <v>0.0103292144164443</v>
+        <v>0.01033536293357611</v>
       </c>
       <c r="D413" t="n">
-        <v>0.01170488152652979</v>
+        <v>0.01171416111290455</v>
       </c>
       <c r="E413" t="n">
         <v>6.25e-05</v>
@@ -7464,13 +7464,13 @@
         <v>413</v>
       </c>
       <c r="B414" t="n">
-        <v>18.39572749999934</v>
+        <v>9.595110800000839</v>
       </c>
       <c r="C414" t="n">
-        <v>0.01029433988779783</v>
+        <v>0.01030172669142485</v>
       </c>
       <c r="D414" t="n">
-        <v>0.01317382596433163</v>
+        <v>0.01317979324609041</v>
       </c>
       <c r="E414" t="n">
         <v>6.25e-05</v>
@@ -7481,13 +7481,13 @@
         <v>414</v>
       </c>
       <c r="B415" t="n">
-        <v>18.39883540000301</v>
+        <v>9.46142969999346</v>
       </c>
       <c r="C415" t="n">
-        <v>0.01050672233104706</v>
+        <v>0.01051298353075981</v>
       </c>
       <c r="D415" t="n">
-        <v>0.01167153157293797</v>
+        <v>0.01167088162153959</v>
       </c>
       <c r="E415" t="n">
         <v>6.25e-05</v>
@@ -7498,13 +7498,13 @@
         <v>415</v>
       </c>
       <c r="B416" t="n">
-        <v>18.0880790999945</v>
+        <v>9.560755799990147</v>
       </c>
       <c r="C416" t="n">
-        <v>0.01020288322865963</v>
+        <v>0.01020685158669949</v>
       </c>
       <c r="D416" t="n">
-        <v>0.01198714543133974</v>
+        <v>0.01198495090007782</v>
       </c>
       <c r="E416" t="n">
         <v>6.25e-05</v>
@@ -7515,13 +7515,13 @@
         <v>416</v>
       </c>
       <c r="B417" t="n">
-        <v>18.41358899998886</v>
+        <v>9.302548899984686</v>
       </c>
       <c r="C417" t="n">
-        <v>0.01021849685907364</v>
+        <v>0.01022408770024776</v>
       </c>
       <c r="D417" t="n">
-        <v>0.01164022218436003</v>
+        <v>0.01164979197084904</v>
       </c>
       <c r="E417" t="n">
         <v>6.25e-05</v>
@@ -7532,13 +7532,13 @@
         <v>417</v>
       </c>
       <c r="B418" t="n">
-        <v>18.33422730000166</v>
+        <v>9.203205799974967</v>
       </c>
       <c r="C418" t="n">
-        <v>0.01045542521029711</v>
+        <v>0.01046738247573376</v>
       </c>
       <c r="D418" t="n">
-        <v>0.01152240611612797</v>
+        <v>0.01152727209031582</v>
       </c>
       <c r="E418" t="n">
         <v>6.25e-05</v>
@@ -7549,13 +7549,13 @@
         <v>418</v>
       </c>
       <c r="B419" t="n">
-        <v>18.20857899999828</v>
+        <v>9.763675399997737</v>
       </c>
       <c r="C419" t="n">
-        <v>0.01023888155817985</v>
+        <v>0.01024506850540638</v>
       </c>
       <c r="D419" t="n">
-        <v>0.01178024809807539</v>
+        <v>0.01178023390471935</v>
       </c>
       <c r="E419" t="n">
         <v>6.25e-05</v>
@@ -7566,13 +7566,13 @@
         <v>419</v>
       </c>
       <c r="B420" t="n">
-        <v>18.43652760000259</v>
+        <v>9.866211199987447</v>
       </c>
       <c r="C420" t="n">
-        <v>0.01032229302078485</v>
+        <v>0.01032729911804199</v>
       </c>
       <c r="D420" t="n">
-        <v>0.01156055096536875</v>
+        <v>0.01156441017985344</v>
       </c>
       <c r="E420" t="n">
         <v>6.25e-05</v>
@@ -7583,13 +7583,13 @@
         <v>420</v>
       </c>
       <c r="B421" t="n">
-        <v>17.9941312999872</v>
+        <v>9.642979900003411</v>
       </c>
       <c r="C421" t="n">
-        <v>0.01018781308084726</v>
+        <v>0.01019744484126568</v>
       </c>
       <c r="D421" t="n">
-        <v>0.01136936068534851</v>
+        <v>0.01137885004281998</v>
       </c>
       <c r="E421" t="n">
         <v>6.25e-05</v>
@@ -7600,13 +7600,13 @@
         <v>421</v>
       </c>
       <c r="B422" t="n">
-        <v>18.38990349999222</v>
+        <v>9.622537099989131</v>
       </c>
       <c r="C422" t="n">
-        <v>0.01031317839771509</v>
+        <v>0.01032063863426447</v>
       </c>
       <c r="D422" t="n">
-        <v>0.01236809030175209</v>
+        <v>0.01238229647278786</v>
       </c>
       <c r="E422" t="n">
         <v>6.25e-05</v>
@@ -7617,13 +7617,13 @@
         <v>422</v>
       </c>
       <c r="B423" t="n">
-        <v>18.71875080000609</v>
+        <v>10.19291509999312</v>
       </c>
       <c r="C423" t="n">
-        <v>0.01042833542078733</v>
+        <v>0.01043173833936453</v>
       </c>
       <c r="D423" t="n">
-        <v>0.01149644695222378</v>
+        <v>0.01149914942681789</v>
       </c>
       <c r="E423" t="n">
         <v>6.25e-05</v>
@@ -7634,13 +7634,13 @@
         <v>423</v>
       </c>
       <c r="B424" t="n">
-        <v>18.357033399996</v>
+        <v>9.976046299998416</v>
       </c>
       <c r="C424" t="n">
-        <v>0.01019961456954479</v>
+        <v>0.01020424100756645</v>
       </c>
       <c r="D424" t="n">
-        <v>0.01158261463046074</v>
+        <v>0.01158189304172993</v>
       </c>
       <c r="E424" t="n">
         <v>6.25e-05</v>
@@ -7651,13 +7651,13 @@
         <v>424</v>
       </c>
       <c r="B425" t="n">
-        <v>18.34390800000983</v>
+        <v>10.20423719999962</v>
       </c>
       <c r="C425" t="n">
-        <v>0.01017611703276634</v>
+        <v>0.01017979050427675</v>
       </c>
       <c r="D425" t="n">
-        <v>0.01230002373456955</v>
+        <v>0.01227645337581634</v>
       </c>
       <c r="E425" t="n">
         <v>6.25e-05</v>
@@ -7668,13 +7668,13 @@
         <v>425</v>
       </c>
       <c r="B426" t="n">
-        <v>18.64411000000837</v>
+        <v>10.13498830000754</v>
       </c>
       <c r="C426" t="n">
-        <v>0.01025473076850176</v>
+        <v>0.01025591446459293</v>
       </c>
       <c r="D426" t="n">
-        <v>0.01128927905112505</v>
+        <v>0.01129431840032339</v>
       </c>
       <c r="E426" t="n">
         <v>6.25e-05</v>
@@ -7685,13 +7685,13 @@
         <v>426</v>
       </c>
       <c r="B427" t="n">
-        <v>18.23306830000365</v>
+        <v>9.947225499985507</v>
       </c>
       <c r="C427" t="n">
-        <v>0.01033176417648792</v>
+        <v>0.01033480937033892</v>
       </c>
       <c r="D427" t="n">
-        <v>0.0116311801224947</v>
+        <v>0.01163931787014008</v>
       </c>
       <c r="E427" t="n">
         <v>6.25e-05</v>
@@ -7702,13 +7702,13 @@
         <v>427</v>
       </c>
       <c r="B428" t="n">
-        <v>18.24030360000324</v>
+        <v>9.671027500007767</v>
       </c>
       <c r="C428" t="n">
-        <v>0.01014464676380157</v>
+        <v>0.01015062186866999</v>
       </c>
       <c r="D428" t="n">
-        <v>0.01143349427729845</v>
+        <v>0.01144485916942358</v>
       </c>
       <c r="E428" t="n">
         <v>6.25e-05</v>
@@ -7719,13 +7719,13 @@
         <v>428</v>
       </c>
       <c r="B429" t="n">
-        <v>18.94836150000629</v>
+        <v>9.872732999996515</v>
       </c>
       <c r="C429" t="n">
-        <v>0.01034937109053135</v>
+        <v>0.01035780036449432</v>
       </c>
       <c r="D429" t="n">
-        <v>0.01156572241336107</v>
+        <v>0.01157075621187687</v>
       </c>
       <c r="E429" t="n">
         <v>6.25e-05</v>
@@ -7736,13 +7736,13 @@
         <v>429</v>
       </c>
       <c r="B430" t="n">
-        <v>18.19974569999613</v>
+        <v>10.08358890001546</v>
       </c>
       <c r="C430" t="n">
-        <v>0.01012912189215422</v>
+        <v>0.0101360430419445</v>
       </c>
       <c r="D430" t="n">
-        <v>0.01154740497469902</v>
+        <v>0.01155209608376026</v>
       </c>
       <c r="E430" t="n">
         <v>6.25e-05</v>
@@ -7753,13 +7753,13 @@
         <v>430</v>
       </c>
       <c r="B431" t="n">
-        <v>18.765121000004</v>
+        <v>9.968662600003881</v>
       </c>
       <c r="C431" t="n">
-        <v>0.01014064884930849</v>
+        <v>0.01014584589004517</v>
       </c>
       <c r="D431" t="n">
-        <v>0.01224446605890989</v>
+        <v>0.01223943684250116</v>
       </c>
       <c r="E431" t="n">
         <v>6.25e-05</v>
@@ -7770,13 +7770,13 @@
         <v>431</v>
       </c>
       <c r="B432" t="n">
-        <v>18.28179899998941</v>
+        <v>10.22196250001434</v>
       </c>
       <c r="C432" t="n">
-        <v>0.01060927787423134</v>
+        <v>0.01061277153342962</v>
       </c>
       <c r="D432" t="n">
-        <v>0.01153647128492594</v>
+        <v>0.01154739357531071</v>
       </c>
       <c r="E432" t="n">
         <v>6.25e-05</v>
@@ -7787,13 +7787,13 @@
         <v>432</v>
       </c>
       <c r="B433" t="n">
-        <v>18.01767040000414</v>
+        <v>10.28671109999414</v>
       </c>
       <c r="C433" t="n">
-        <v>0.01022359002381563</v>
+        <v>0.01022971270978451</v>
       </c>
       <c r="D433" t="n">
-        <v>0.01146653864532709</v>
+        <v>0.01146440718322992</v>
       </c>
       <c r="E433" t="n">
         <v>6.25e-05</v>
@@ -7804,13 +7804,13 @@
         <v>433</v>
       </c>
       <c r="B434" t="n">
-        <v>18.22868990000279</v>
+        <v>10.34700489998795</v>
       </c>
       <c r="C434" t="n">
-        <v>0.01006500461697578</v>
+        <v>0.01006966961175203</v>
       </c>
       <c r="D434" t="n">
-        <v>0.01137188278138638</v>
+        <v>0.01138042215257883</v>
       </c>
       <c r="E434" t="n">
         <v>6.25e-05</v>
@@ -7821,13 +7821,13 @@
         <v>434</v>
       </c>
       <c r="B435" t="n">
-        <v>19.10986370001046</v>
+        <v>10.19679250000627</v>
       </c>
       <c r="C435" t="n">
-        <v>0.01016110388189554</v>
+        <v>0.01016884525120258</v>
       </c>
       <c r="D435" t="n">
-        <v>0.01146384671330452</v>
+        <v>0.01147418305277824</v>
       </c>
       <c r="E435" t="n">
         <v>6.25e-05</v>
@@ -7838,13 +7838,13 @@
         <v>435</v>
       </c>
       <c r="B436" t="n">
-        <v>18.49713699999847</v>
+        <v>10.26829670000006</v>
       </c>
       <c r="C436" t="n">
-        <v>0.01008619254082441</v>
+        <v>0.01009266262501478</v>
       </c>
       <c r="D436" t="n">
-        <v>0.01137231312692165</v>
+        <v>0.01137727491557598</v>
       </c>
       <c r="E436" t="n">
         <v>6.25e-05</v>
@@ -7855,13 +7855,13 @@
         <v>436</v>
       </c>
       <c r="B437" t="n">
-        <v>18.04955919999338</v>
+        <v>10.16747149999719</v>
       </c>
       <c r="C437" t="n">
-        <v>0.01004599276185036</v>
+        <v>0.01005331559479237</v>
       </c>
       <c r="D437" t="n">
-        <v>0.01283384546637535</v>
+        <v>0.01286835812032223</v>
       </c>
       <c r="E437" t="n">
         <v>6.25e-05</v>
@@ -7872,13 +7872,13 @@
         <v>437</v>
       </c>
       <c r="B438" t="n">
-        <v>18.67725860000064</v>
+        <v>11.81436119999853</v>
       </c>
       <c r="C438" t="n">
-        <v>0.01029319978505373</v>
+        <v>0.01029959407448769</v>
       </c>
       <c r="D438" t="n">
-        <v>0.01136275485157967</v>
+        <v>0.0113725608959794</v>
       </c>
       <c r="E438" t="n">
         <v>6.25e-05</v>
@@ -7889,13 +7889,13 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>18.07710629999929</v>
+        <v>10.28722430000198</v>
       </c>
       <c r="C439" t="n">
-        <v>0.01011409437656403</v>
+        <v>0.01012313057482243</v>
       </c>
       <c r="D439" t="n">
-        <v>0.01153427101671696</v>
+        <v>0.01153880700469017</v>
       </c>
       <c r="E439" t="n">
         <v>6.25e-05</v>
@@ -7906,13 +7906,13 @@
         <v>439</v>
       </c>
       <c r="B440" t="n">
-        <v>17.92607630000566</v>
+        <v>10.19604359997902</v>
       </c>
       <c r="C440" t="n">
-        <v>0.01021568597108126</v>
+        <v>0.01022397843003273</v>
       </c>
       <c r="D440" t="n">
-        <v>0.01166740156710148</v>
+        <v>0.01167747557163239</v>
       </c>
       <c r="E440" t="n">
         <v>6.25e-05</v>
@@ -7923,13 +7923,13 @@
         <v>440</v>
       </c>
       <c r="B441" t="n">
-        <v>18.55704200000037</v>
+        <v>9.706196400016779</v>
       </c>
       <c r="C441" t="n">
-        <v>0.01038512111455202</v>
+        <v>0.01039127041399479</v>
       </c>
       <c r="D441" t="n">
-        <v>0.01175021078437567</v>
+        <v>0.01174634858965874</v>
       </c>
       <c r="E441" t="n">
         <v>6.25e-05</v>
@@ -7940,13 +7940,13 @@
         <v>441</v>
       </c>
       <c r="B442" t="n">
-        <v>18.20635120000225</v>
+        <v>9.697536299994681</v>
       </c>
       <c r="C442" t="n">
-        <v>0.01074085381627083</v>
+        <v>0.01074136524647474</v>
       </c>
       <c r="D442" t="n">
-        <v>0.01198791623115539</v>
+        <v>0.01198886901140213</v>
       </c>
       <c r="E442" t="n">
         <v>6.25e-05</v>
@@ -7957,13 +7957,13 @@
         <v>442</v>
       </c>
       <c r="B443" t="n">
-        <v>18.27308340001036</v>
+        <v>9.52258879999863</v>
       </c>
       <c r="C443" t="n">
-        <v>0.0100259098559618</v>
+        <v>0.01003063185885549</v>
       </c>
       <c r="D443" t="n">
-        <v>0.01152414012700319</v>
+        <v>0.01152471162378788</v>
       </c>
       <c r="E443" t="n">
         <v>6.25e-05</v>
@@ -7974,13 +7974,13 @@
         <v>443</v>
       </c>
       <c r="B444" t="n">
-        <v>18.13938010000857</v>
+        <v>9.625577200000407</v>
       </c>
       <c r="C444" t="n">
-        <v>0.01008978371322155</v>
+        <v>0.01009452992677689</v>
       </c>
       <c r="D444" t="n">
-        <v>0.01135742738842964</v>
+        <v>0.01136310964822769</v>
       </c>
       <c r="E444" t="n">
         <v>6.25e-05</v>
@@ -7991,13 +7991,13 @@
         <v>444</v>
       </c>
       <c r="B445" t="n">
-        <v>18.20092299999669</v>
+        <v>9.577401699993061</v>
       </c>
       <c r="C445" t="n">
-        <v>0.01035516796261072</v>
+        <v>0.01036246490478516</v>
       </c>
       <c r="D445" t="n">
-        <v>0.01177990481257439</v>
+        <v>0.01179549761116505</v>
       </c>
       <c r="E445" t="n">
         <v>6.25e-05</v>
@@ -8008,13 +8008,13 @@
         <v>445</v>
       </c>
       <c r="B446" t="n">
-        <v>18.22447120001016</v>
+        <v>9.507118700013962</v>
       </c>
       <c r="C446" t="n">
-        <v>0.01018573258817196</v>
+        <v>0.01019638573378324</v>
       </c>
       <c r="D446" t="n">
-        <v>0.01146010845899582</v>
+        <v>0.01146560117602348</v>
       </c>
       <c r="E446" t="n">
         <v>6.25e-05</v>
@@ -8025,13 +8025,13 @@
         <v>446</v>
       </c>
       <c r="B447" t="n">
-        <v>18.09229960000084</v>
+        <v>9.650709399982588</v>
       </c>
       <c r="C447" t="n">
-        <v>0.0100348090454936</v>
+        <v>0.01003954001516104</v>
       </c>
       <c r="D447" t="n">
-        <v>0.01222203079611063</v>
+        <v>0.01222359292209148</v>
       </c>
       <c r="E447" t="n">
         <v>6.25e-05</v>
@@ -8042,13 +8042,13 @@
         <v>447</v>
       </c>
       <c r="B448" t="n">
-        <v>18.2325514999975</v>
+        <v>9.489527799974894</v>
       </c>
       <c r="C448" t="n">
-        <v>0.01035333260148764</v>
+        <v>0.01035510737448931</v>
       </c>
       <c r="D448" t="n">
-        <v>0.01126765392720699</v>
+        <v>0.01126902468502521</v>
       </c>
       <c r="E448" t="n">
         <v>6.25e-05</v>
@@ -8059,13 +8059,13 @@
         <v>448</v>
       </c>
       <c r="B449" t="n">
-        <v>17.98114499999792</v>
+        <v>9.559452100016642</v>
       </c>
       <c r="C449" t="n">
-        <v>0.0101126096919179</v>
+        <v>0.01011857852339745</v>
       </c>
       <c r="D449" t="n">
-        <v>0.01130154170095921</v>
+        <v>0.01130688667297363</v>
       </c>
       <c r="E449" t="n">
         <v>6.25e-05</v>
@@ -8076,13 +8076,13 @@
         <v>449</v>
       </c>
       <c r="B450" t="n">
-        <v>18.21870589999889</v>
+        <v>9.605524700018577</v>
       </c>
       <c r="C450" t="n">
-        <v>0.01003585134446621</v>
+        <v>0.01004204519093037</v>
       </c>
       <c r="D450" t="n">
-        <v>0.0134545348584652</v>
+        <v>0.01346656635403633</v>
       </c>
       <c r="E450" t="n">
         <v>6.25e-05</v>
@@ -8093,13 +8093,13 @@
         <v>450</v>
       </c>
       <c r="B451" t="n">
-        <v>18.32916609999666</v>
+        <v>9.495368400006555</v>
       </c>
       <c r="C451" t="n">
-        <v>0.01050062361359596</v>
+        <v>0.01050752311944961</v>
       </c>
       <c r="D451" t="n">
-        <v>0.01159905835986137</v>
+        <v>0.01160780768841505</v>
       </c>
       <c r="E451" t="n">
         <v>6.25e-05</v>
@@ -8110,13 +8110,13 @@
         <v>451</v>
       </c>
       <c r="B452" t="n">
-        <v>18.26871679999749</v>
+        <v>9.45956479999586</v>
       </c>
       <c r="C452" t="n">
-        <v>0.01014583785831928</v>
+        <v>0.01015420314669609</v>
       </c>
       <c r="D452" t="n">
-        <v>0.01167090255767107</v>
+        <v>0.01167839158326387</v>
       </c>
       <c r="E452" t="n">
         <v>6.25e-05</v>
@@ -8127,13 +8127,13 @@
         <v>452</v>
       </c>
       <c r="B453" t="n">
-        <v>18.01319799998601</v>
+        <v>9.761070399981691</v>
       </c>
       <c r="C453" t="n">
-        <v>0.01015533120185137</v>
+        <v>0.01016236297041178</v>
       </c>
       <c r="D453" t="n">
-        <v>0.01159433320164681</v>
+        <v>0.01161241266876459</v>
       </c>
       <c r="E453" t="n">
         <v>6.25e-05</v>
@@ -8144,13 +8144,13 @@
         <v>453</v>
       </c>
       <c r="B454" t="n">
-        <v>18.43952040000295</v>
+        <v>10.25480090000201</v>
       </c>
       <c r="C454" t="n">
-        <v>0.01035284750163555</v>
+        <v>0.01036132054030895</v>
       </c>
       <c r="D454" t="n">
-        <v>0.01239356394857168</v>
+        <v>0.01242941912263632</v>
       </c>
       <c r="E454" t="n">
         <v>6.25e-05</v>
@@ -8161,13 +8161,13 @@
         <v>454</v>
       </c>
       <c r="B455" t="n">
-        <v>18.13424400000076</v>
+        <v>9.77665220000199</v>
       </c>
       <c r="C455" t="n">
-        <v>0.01037382131814957</v>
+        <v>0.01038623549044132</v>
       </c>
       <c r="D455" t="n">
-        <v>0.01145418312400579</v>
+        <v>0.01145812336355448</v>
       </c>
       <c r="E455" t="n">
         <v>6.25e-05</v>
@@ -8178,13 +8178,13 @@
         <v>455</v>
       </c>
       <c r="B456" t="n">
-        <v>18.39271230000304</v>
+        <v>9.669055999984266</v>
       </c>
       <c r="C456" t="n">
-        <v>0.01004108239710331</v>
+        <v>0.01004720965027809</v>
       </c>
       <c r="D456" t="n">
-        <v>0.01177753765136003</v>
+        <v>0.01179304778575897</v>
       </c>
       <c r="E456" t="n">
         <v>6.25e-05</v>
@@ -8195,13 +8195,13 @@
         <v>456</v>
       </c>
       <c r="B457" t="n">
-        <v>18.12505470000906</v>
+        <v>9.631686300010188</v>
       </c>
       <c r="C457" t="n">
-        <v>0.01014452484250069</v>
+        <v>0.01015548515319824</v>
       </c>
       <c r="D457" t="n">
-        <v>0.01190007615834475</v>
+        <v>0.01190574791282415</v>
       </c>
       <c r="E457" t="n">
         <v>6.25e-05</v>
@@ -8212,13 +8212,13 @@
         <v>457</v>
       </c>
       <c r="B458" t="n">
-        <v>18.31143890001113</v>
+        <v>9.681925400014734</v>
       </c>
       <c r="C458" t="n">
-        <v>0.01032411689311266</v>
+        <v>0.01033537026494741</v>
       </c>
       <c r="D458" t="n">
-        <v>0.01149449534714222</v>
+        <v>0.0115072724968195</v>
       </c>
       <c r="E458" t="n">
         <v>6.25e-05</v>
@@ -8229,13 +8229,13 @@
         <v>458</v>
       </c>
       <c r="B459" t="n">
-        <v>18.06497249999666</v>
+        <v>9.624594900000375</v>
       </c>
       <c r="C459" t="n">
-        <v>0.009991323255002498</v>
+        <v>0.009998028643429279</v>
       </c>
       <c r="D459" t="n">
-        <v>0.01183816440403461</v>
+        <v>0.01183913514018059</v>
       </c>
       <c r="E459" t="n">
         <v>6.25e-05</v>
@@ -8246,13 +8246,13 @@
         <v>459</v>
       </c>
       <c r="B460" t="n">
-        <v>18.18647390000115</v>
+        <v>9.612730599998031</v>
       </c>
       <c r="C460" t="n">
-        <v>0.01015994060784578</v>
+        <v>0.01016677866131067</v>
       </c>
       <c r="D460" t="n">
-        <v>0.01129206161946058</v>
+        <v>0.01130552466958761</v>
       </c>
       <c r="E460" t="n">
         <v>6.25e-05</v>
@@ -8263,13 +8263,13 @@
         <v>460</v>
       </c>
       <c r="B461" t="n">
-        <v>18.1001671999984</v>
+        <v>9.816233099991223</v>
       </c>
       <c r="C461" t="n">
-        <v>0.01005476835370064</v>
+        <v>0.01006357023864985</v>
       </c>
       <c r="D461" t="n">
-        <v>0.01114648040384054</v>
+        <v>0.01115159600973129</v>
       </c>
       <c r="E461" t="n">
         <v>6.25e-05</v>
@@ -8280,13 +8280,13 @@
         <v>461</v>
       </c>
       <c r="B462" t="n">
-        <v>18.15844150001067</v>
+        <v>9.931459300016286</v>
       </c>
       <c r="C462" t="n">
-        <v>0.010142946600914</v>
+        <v>0.01015075634047389</v>
       </c>
       <c r="D462" t="n">
-        <v>0.011449294090271</v>
+        <v>0.01144529908895493</v>
       </c>
       <c r="E462" t="n">
         <v>6.25e-05</v>
@@ -8297,13 +8297,13 @@
         <v>462</v>
       </c>
       <c r="B463" t="n">
-        <v>18.55319439999585</v>
+        <v>9.793881399993552</v>
       </c>
       <c r="C463" t="n">
-        <v>0.01022412744909525</v>
+        <v>0.01023098290711641</v>
       </c>
       <c r="D463" t="n">
-        <v>0.01138980567455292</v>
+        <v>0.01140036545693874</v>
       </c>
       <c r="E463" t="n">
         <v>6.25e-05</v>
@@ -8314,13 +8314,13 @@
         <v>463</v>
       </c>
       <c r="B464" t="n">
-        <v>18.26606840000022</v>
+        <v>9.669991999980994</v>
       </c>
       <c r="C464" t="n">
-        <v>0.009947645939886569</v>
+        <v>0.009954682908952236</v>
       </c>
       <c r="D464" t="n">
-        <v>0.01134937629103661</v>
+        <v>0.01135926850140095</v>
       </c>
       <c r="E464" t="n">
         <v>6.25e-05</v>
@@ -8331,13 +8331,13 @@
         <v>464</v>
       </c>
       <c r="B465" t="n">
-        <v>17.83331289999478</v>
+        <v>10.09389129999909</v>
       </c>
       <c r="C465" t="n">
-        <v>0.01003134357184172</v>
+        <v>0.01003814268857241</v>
       </c>
       <c r="D465" t="n">
-        <v>0.0123171117156744</v>
+        <v>0.01233025651425123</v>
       </c>
       <c r="E465" t="n">
         <v>6.25e-05</v>
@@ -8348,13 +8348,13 @@
         <v>465</v>
       </c>
       <c r="B466" t="n">
-        <v>18.49215020000702</v>
+        <v>10.0564251000178</v>
       </c>
       <c r="C466" t="n">
-        <v>0.01038788627833128</v>
+        <v>0.01039375387132168</v>
       </c>
       <c r="D466" t="n">
-        <v>0.01137990061193705</v>
+        <v>0.0113839927688241</v>
       </c>
       <c r="E466" t="n">
         <v>6.25e-05</v>
@@ -8365,13 +8365,13 @@
         <v>466</v>
       </c>
       <c r="B467" t="n">
-        <v>18.5544258000009</v>
+        <v>9.653347199986456</v>
       </c>
       <c r="C467" t="n">
-        <v>0.0100761803239584</v>
+        <v>0.01008173053711653</v>
       </c>
       <c r="D467" t="n">
-        <v>0.01131918869912624</v>
+        <v>0.01131705664098263</v>
       </c>
       <c r="E467" t="n">
         <v>6.25e-05</v>
@@ -8382,13 +8382,13 @@
         <v>467</v>
       </c>
       <c r="B468" t="n">
-        <v>18.20977590000257</v>
+        <v>9.867971400002716</v>
       </c>
       <c r="C468" t="n">
-        <v>0.009965885259211063</v>
+        <v>0.009970837771892548</v>
       </c>
       <c r="D468" t="n">
-        <v>0.01128650467842817</v>
+        <v>0.01129005156457424</v>
       </c>
       <c r="E468" t="n">
         <v>6.25e-05</v>
@@ -8399,13 +8399,13 @@
         <v>468</v>
       </c>
       <c r="B469" t="n">
-        <v>18.34123120000004</v>
+        <v>9.610652300005313</v>
       </c>
       <c r="C469" t="n">
-        <v>0.01000441717356443</v>
+        <v>0.01001021041721106</v>
       </c>
       <c r="D469" t="n">
-        <v>0.01133991245180368</v>
+        <v>0.01135731734335423</v>
       </c>
       <c r="E469" t="n">
         <v>6.25e-05</v>
@@ -8416,13 +8416,13 @@
         <v>469</v>
       </c>
       <c r="B470" t="n">
-        <v>18.49717410000449</v>
+        <v>9.659073999995599</v>
       </c>
       <c r="C470" t="n">
-        <v>0.009979548081755638</v>
+        <v>0.009990920811891556</v>
       </c>
       <c r="D470" t="n">
-        <v>0.0123230205103755</v>
+        <v>0.01236190587282181</v>
       </c>
       <c r="E470" t="n">
         <v>6.25e-05</v>
@@ -8433,13 +8433,13 @@
         <v>470</v>
       </c>
       <c r="B471" t="n">
-        <v>18.21150400000624</v>
+        <v>9.595833600003971</v>
       </c>
       <c r="C471" t="n">
-        <v>0.01016493041068315</v>
+        <v>0.01017413645982742</v>
       </c>
       <c r="D471" t="n">
-        <v>0.01131376095116138</v>
+        <v>0.01131533607840538</v>
       </c>
       <c r="E471" t="n">
         <v>6.25e-05</v>
@@ -8450,13 +8450,13 @@
         <v>471</v>
       </c>
       <c r="B472" t="n">
-        <v>18.1454417000059</v>
+        <v>9.345931800024118</v>
       </c>
       <c r="C472" t="n">
-        <v>0.01011088973283768</v>
+        <v>0.01011594369262457</v>
       </c>
       <c r="D472" t="n">
-        <v>0.0121135401725769</v>
+        <v>0.01211641419678926</v>
       </c>
       <c r="E472" t="n">
         <v>6.25e-05</v>
@@ -8467,13 +8467,13 @@
         <v>472</v>
       </c>
       <c r="B473" t="n">
-        <v>18.41255799999635</v>
+        <v>9.494676400005119</v>
       </c>
       <c r="C473" t="n">
-        <v>0.01031600227952004</v>
+        <v>0.01032513025403023</v>
       </c>
       <c r="D473" t="n">
-        <v>0.01154499899595976</v>
+        <v>0.01156593300402164</v>
       </c>
       <c r="E473" t="n">
         <v>6.25e-05</v>
@@ -8484,13 +8484,13 @@
         <v>473</v>
       </c>
       <c r="B474" t="n">
-        <v>18.36547509999946</v>
+        <v>9.733434099995065</v>
       </c>
       <c r="C474" t="n">
-        <v>0.01014241702109575</v>
+        <v>0.01015347112715244</v>
       </c>
       <c r="D474" t="n">
-        <v>0.01146033998578787</v>
+        <v>0.01147027865052223</v>
       </c>
       <c r="E474" t="n">
         <v>6.25e-05</v>
@@ -8501,13 +8501,13 @@
         <v>474</v>
       </c>
       <c r="B475" t="n">
-        <v>18.06784869999683</v>
+        <v>9.456195000006119</v>
       </c>
       <c r="C475" t="n">
-        <v>0.00996930354833603</v>
+        <v>0.009976553633809089</v>
       </c>
       <c r="D475" t="n">
-        <v>0.01146790005266666</v>
+        <v>0.01148169692605734</v>
       </c>
       <c r="E475" t="n">
         <v>6.25e-05</v>
@@ -8518,13 +8518,13 @@
         <v>475</v>
       </c>
       <c r="B476" t="n">
-        <v>18.2071477999998</v>
+        <v>9.89838040000177</v>
       </c>
       <c r="C476" t="n">
-        <v>0.01000341144949198</v>
+        <v>0.01001368192583323</v>
       </c>
       <c r="D476" t="n">
-        <v>0.01165838379412889</v>
+        <v>0.01166846424341202</v>
       </c>
       <c r="E476" t="n">
         <v>6.25e-05</v>
@@ -8535,13 +8535,13 @@
         <v>476</v>
       </c>
       <c r="B477" t="n">
-        <v>18.09870760000194</v>
+        <v>9.525115800002823</v>
       </c>
       <c r="C477" t="n">
-        <v>0.0100841281414032</v>
+        <v>0.01009374532103539</v>
       </c>
       <c r="D477" t="n">
-        <v>0.01131527777761221</v>
+        <v>0.01133249033242464</v>
       </c>
       <c r="E477" t="n">
         <v>6.25e-05</v>
@@ -8552,13 +8552,13 @@
         <v>477</v>
       </c>
       <c r="B478" t="n">
-        <v>18.56781259999843</v>
+        <v>9.809647400019458</v>
       </c>
       <c r="C478" t="n">
-        <v>0.01029053752869368</v>
+        <v>0.01030367371439934</v>
       </c>
       <c r="D478" t="n">
-        <v>0.01155967082828283</v>
+        <v>0.01156428322196007</v>
       </c>
       <c r="E478" t="n">
         <v>6.25e-05</v>
@@ -8569,13 +8569,13 @@
         <v>478</v>
       </c>
       <c r="B479" t="n">
-        <v>18.16312760001165</v>
+        <v>9.945543700014241</v>
       </c>
       <c r="C479" t="n">
-        <v>0.0100146244391799</v>
+        <v>0.01001985626667738</v>
       </c>
       <c r="D479" t="n">
-        <v>0.01226508982479572</v>
+        <v>0.01226874522864819</v>
       </c>
       <c r="E479" t="n">
         <v>6.25e-05</v>
@@ -8586,13 +8586,13 @@
         <v>479</v>
       </c>
       <c r="B480" t="n">
-        <v>17.89676319999853</v>
+        <v>9.66634769999655</v>
       </c>
       <c r="C480" t="n">
-        <v>0.01008532603830099</v>
+        <v>0.01009101468324661</v>
       </c>
       <c r="D480" t="n">
-        <v>0.01141429129987955</v>
+        <v>0.0114138463512063</v>
       </c>
       <c r="E480" t="n">
         <v>6.25e-05</v>
@@ -8603,13 +8603,13 @@
         <v>480</v>
       </c>
       <c r="B481" t="n">
-        <v>18.56475210000644</v>
+        <v>9.996382800018182</v>
       </c>
       <c r="C481" t="n">
-        <v>0.009981744185090066</v>
+        <v>0.009982612237334251</v>
       </c>
       <c r="D481" t="n">
-        <v>0.01205205537378788</v>
+        <v>0.01206966370344162</v>
       </c>
       <c r="E481" t="n">
         <v>6.25e-05</v>
@@ -8620,13 +8620,13 @@
         <v>481</v>
       </c>
       <c r="B482" t="n">
-        <v>18.40711719999672</v>
+        <v>9.700509399990551</v>
       </c>
       <c r="C482" t="n">
-        <v>0.01029038578271866</v>
+        <v>0.01030024294555187</v>
       </c>
       <c r="D482" t="n">
-        <v>0.01220592074096203</v>
+        <v>0.01221040669828653</v>
       </c>
       <c r="E482" t="n">
         <v>6.25e-05</v>
@@ -8637,13 +8637,13 @@
         <v>482</v>
       </c>
       <c r="B483" t="n">
-        <v>18.15669489999709</v>
+        <v>9.380747500021243</v>
       </c>
       <c r="C483" t="n">
-        <v>0.0100796676799655</v>
+        <v>0.01008735199272633</v>
       </c>
       <c r="D483" t="n">
-        <v>0.01136685725301504</v>
+        <v>0.01137192811816931</v>
       </c>
       <c r="E483" t="n">
         <v>6.25e-05</v>
@@ -8654,13 +8654,13 @@
         <v>483</v>
       </c>
       <c r="B484" t="n">
-        <v>18.80592830000387</v>
+        <v>9.389538899995387</v>
       </c>
       <c r="C484" t="n">
-        <v>0.009878803797066212</v>
+        <v>0.009887132242321968</v>
       </c>
       <c r="D484" t="n">
-        <v>0.01112754881381989</v>
+        <v>0.01113188039511442</v>
       </c>
       <c r="E484" t="n">
         <v>6.25e-05</v>
@@ -8671,13 +8671,13 @@
         <v>484</v>
       </c>
       <c r="B485" t="n">
-        <v>18.40410219998739</v>
+        <v>9.709570700011682</v>
       </c>
       <c r="C485" t="n">
-        <v>0.009909940987825393</v>
+        <v>0.009918240666389464</v>
       </c>
       <c r="D485" t="n">
-        <v>0.01114309437572956</v>
+        <v>0.01114823382347822</v>
       </c>
       <c r="E485" t="n">
         <v>6.25e-05</v>
@@ -8688,13 +8688,13 @@
         <v>485</v>
       </c>
       <c r="B486" t="n">
-        <v>18.45248449999781</v>
+        <v>9.510426199994981</v>
       </c>
       <c r="C486" t="n">
-        <v>0.009787578269839286</v>
+        <v>0.009794638372957706</v>
       </c>
       <c r="D486" t="n">
-        <v>0.01114830985665321</v>
+        <v>0.01115558955818415</v>
       </c>
       <c r="E486" t="n">
         <v>6.25e-05</v>
@@ -8705,13 +8705,13 @@
         <v>486</v>
       </c>
       <c r="B487" t="n">
-        <v>18.43930870000622</v>
+        <v>9.554286200000206</v>
       </c>
       <c r="C487" t="n">
-        <v>0.009864207543432712</v>
+        <v>0.009871180973947048</v>
       </c>
       <c r="D487" t="n">
-        <v>0.01112520281225443</v>
+        <v>0.01113261718302965</v>
       </c>
       <c r="E487" t="n">
         <v>6.25e-05</v>
@@ -8722,13 +8722,13 @@
         <v>487</v>
       </c>
       <c r="B488" t="n">
-        <v>18.56428560000495</v>
+        <v>10.22077559999889</v>
       </c>
       <c r="C488" t="n">
-        <v>0.01004368709027767</v>
+        <v>0.01005105485767126</v>
       </c>
       <c r="D488" t="n">
-        <v>0.01157318662852049</v>
+        <v>0.01158775798976421</v>
       </c>
       <c r="E488" t="n">
         <v>6.25e-05</v>
@@ -8739,13 +8739,13 @@
         <v>488</v>
       </c>
       <c r="B489" t="n">
-        <v>18.41220059999614</v>
+        <v>9.952882500016131</v>
       </c>
       <c r="C489" t="n">
-        <v>0.01023919172585011</v>
+        <v>0.01024806602299213</v>
       </c>
       <c r="D489" t="n">
-        <v>0.01204712864011526</v>
+        <v>0.01205523669719696</v>
       </c>
       <c r="E489" t="n">
         <v>6.25e-05</v>
@@ -8756,13 +8756,13 @@
         <v>489</v>
       </c>
       <c r="B490" t="n">
-        <v>18.04468340000312</v>
+        <v>9.572719000017969</v>
       </c>
       <c r="C490" t="n">
-        <v>0.0102063766643405</v>
+        <v>0.01020738185197115</v>
       </c>
       <c r="D490" t="n">
-        <v>0.01224306620657444</v>
+        <v>0.01223161973059177</v>
       </c>
       <c r="E490" t="n">
         <v>6.25e-05</v>
@@ -8773,13 +8773,13 @@
         <v>490</v>
       </c>
       <c r="B491" t="n">
-        <v>17.93356929998845</v>
+        <v>9.429305899975589</v>
       </c>
       <c r="C491" t="n">
-        <v>0.01013521638512611</v>
+        <v>0.01013724161684513</v>
       </c>
       <c r="D491" t="n">
-        <v>0.01140950843691826</v>
+        <v>0.01142054334282875</v>
       </c>
       <c r="E491" t="n">
         <v>6.25e-05</v>
@@ -8790,13 +8790,13 @@
         <v>491</v>
       </c>
       <c r="B492" t="n">
-        <v>18.55965619999915</v>
+        <v>9.472471299988683</v>
       </c>
       <c r="C492" t="n">
-        <v>0.009925160482525825</v>
+        <v>0.009931999385356903</v>
       </c>
       <c r="D492" t="n">
-        <v>0.01133678652346134</v>
+        <v>0.01134464774280786</v>
       </c>
       <c r="E492" t="n">
         <v>6.25e-05</v>
@@ -8807,13 +8807,13 @@
         <v>492</v>
       </c>
       <c r="B493" t="n">
-        <v>18.37147329999425</v>
+        <v>9.320003300003009</v>
       </c>
       <c r="C493" t="n">
-        <v>0.009832280084490776</v>
+        <v>0.009840478762984276</v>
       </c>
       <c r="D493" t="n">
-        <v>0.01184575397521257</v>
+        <v>0.01185272991657257</v>
       </c>
       <c r="E493" t="n">
         <v>6.25e-05</v>
@@ -8824,13 +8824,13 @@
         <v>493</v>
       </c>
       <c r="B494" t="n">
-        <v>17.96883369999705</v>
+        <v>9.591160600015428</v>
       </c>
       <c r="C494" t="n">
-        <v>0.01016152547299862</v>
+        <v>0.01017145799100399</v>
       </c>
       <c r="D494" t="n">
-        <v>0.0111409617960453</v>
+        <v>0.0111424407735467</v>
       </c>
       <c r="E494" t="n">
         <v>6.25e-05</v>
@@ -8841,13 +8841,13 @@
         <v>494</v>
       </c>
       <c r="B495" t="n">
-        <v>18.35730489999696</v>
+        <v>9.762961900007213</v>
       </c>
       <c r="C495" t="n">
-        <v>0.009950513549149036</v>
+        <v>0.009954996488988399</v>
       </c>
       <c r="D495" t="n">
-        <v>0.01194333489984274</v>
+        <v>0.01194610986858606</v>
       </c>
       <c r="E495" t="n">
         <v>6.25e-05</v>
@@ -8858,13 +8858,13 @@
         <v>495</v>
       </c>
       <c r="B496" t="n">
-        <v>18.05916020000586</v>
+        <v>9.486545899999328</v>
       </c>
       <c r="C496" t="n">
-        <v>0.009908025808632374</v>
+        <v>0.009914202950894832</v>
       </c>
       <c r="D496" t="n">
-        <v>0.01156631626188755</v>
+        <v>0.01157131191343069</v>
       </c>
       <c r="E496" t="n">
         <v>6.25e-05</v>
@@ -8875,13 +8875,13 @@
         <v>496</v>
       </c>
       <c r="B497" t="n">
-        <v>18.34632599999895</v>
+        <v>9.253113199985819</v>
       </c>
       <c r="C497" t="n">
-        <v>0.00984696913510561</v>
+        <v>0.009854179643094539</v>
       </c>
       <c r="D497" t="n">
-        <v>0.01119043491780758</v>
+        <v>0.01119179286062717</v>
       </c>
       <c r="E497" t="n">
         <v>6.25e-05</v>
@@ -8892,13 +8892,13 @@
         <v>497</v>
       </c>
       <c r="B498" t="n">
-        <v>18.18923810000706</v>
+        <v>9.167339799983893</v>
       </c>
       <c r="C498" t="n">
-        <v>0.009741526864469051</v>
+        <v>0.009748274236917496</v>
       </c>
       <c r="D498" t="n">
-        <v>0.01107364609837532</v>
+        <v>0.01107966840267181</v>
       </c>
       <c r="E498" t="n">
         <v>6.25e-05</v>
@@ -8909,13 +8909,13 @@
         <v>498</v>
       </c>
       <c r="B499" t="n">
-        <v>18.47126249999565</v>
+        <v>9.160045500000706</v>
       </c>
       <c r="C499" t="n">
-        <v>0.009763333223760128</v>
+        <v>0.009771079048514366</v>
       </c>
       <c r="D499" t="n">
-        <v>0.01115352440625429</v>
+        <v>0.01116044156253338</v>
       </c>
       <c r="E499" t="n">
         <v>6.25e-05</v>
@@ -8926,13 +8926,13 @@
         <v>499</v>
       </c>
       <c r="B500" t="n">
-        <v>18.07076829999278</v>
+        <v>9.714061399979983</v>
       </c>
       <c r="C500" t="n">
-        <v>0.009881939463317394</v>
+        <v>0.009889829955995083</v>
       </c>
       <c r="D500" t="n">
-        <v>0.01172547698020935</v>
+        <v>0.01173374742269516</v>
       </c>
       <c r="E500" t="n">
         <v>6.25e-05</v>
@@ -8943,13 +8943,13 @@
         <v>500</v>
       </c>
       <c r="B501" t="n">
-        <v>18.07589310000185</v>
+        <v>9.627017599996179</v>
       </c>
       <c r="C501" t="n">
-        <v>0.01002499061077833</v>
+        <v>0.01003057746589184</v>
       </c>
       <c r="D501" t="n">
-        <v>0.01141846530139446</v>
+        <v>0.01143038246780634</v>
       </c>
       <c r="E501" t="n">
         <v>6.25e-05</v>
@@ -8960,13 +8960,13 @@
         <v>501</v>
       </c>
       <c r="B502" t="n">
-        <v>18.51642159999756</v>
+        <v>9.535624999989523</v>
       </c>
       <c r="C502" t="n">
-        <v>0.00969779796898365</v>
+        <v>0.009705139920115471</v>
       </c>
       <c r="D502" t="n">
-        <v>0.01153976228088141</v>
+        <v>0.0115405461192131</v>
       </c>
       <c r="E502" t="n">
         <v>3.125e-05</v>
